--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="G2" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J2" t="n">
         <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-19 01:31:12</t>
+          <t>2026-07-19 03:44:22</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>2.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
         <v>3.4</v>
@@ -1144,7 +1144,7 @@
         <v>1.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-19 01:31:12</t>
+          <t>2026-07-19 03:44:22</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G4" t="n">
         <v>2.48</v>
@@ -1377,7 +1377,7 @@
         <v>3.85</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K4" t="n">
         <v>3.55</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-19 01:31:12</t>
+          <t>2026-07-19 03:44:22</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-19 01:31:12</t>
+          <t>2026-07-19 03:44:22</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>2.42</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H6" t="n">
         <v>3.15</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-19 01:31:12</t>
+          <t>2026-07-19 03:44:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -860,7 +860,7 @@
         <v>1.91</v>
       </c>
       <c r="G2" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H2" t="n">
         <v>4.3</v>
@@ -869,7 +869,7 @@
         <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
         <v>3.85</v>
@@ -887,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q2" t="n">
         <v>1.98</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-19 03:44:22</t>
+          <t>2026-07-19 05:58:00</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>2.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
         <v>3.4</v>
@@ -1144,7 +1144,7 @@
         <v>1.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-19 03:44:22</t>
+          <t>2026-07-19 05:58:00</t>
         </is>
       </c>
     </row>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-19 03:44:22</t>
+          <t>2026-07-19 05:58:00</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-19 03:44:22</t>
+          <t>2026-07-19 05:58:00</t>
         </is>
       </c>
     </row>
@@ -1873,16 +1873,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="G6" t="n">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="H6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I6" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="J6" t="n">
         <v>3.1</v>
@@ -1903,7 +1903,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q6" t="n">
         <v>2.38</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-19 03:44:22</t>
+          <t>2026-07-19 05:58:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="G2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H2" t="n">
         <v>4.3</v>
@@ -872,215 +872,215 @@
         <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-19 05:58:00</t>
+          <t>2026-07-19 08:11:46</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G3" t="n">
         <v>4.1</v>
       </c>
       <c r="H3" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J3" t="n">
         <v>3.2</v>
@@ -1129,212 +1129,212 @@
         <v>3.4</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P3" t="n">
         <v>1.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-19 05:58:00</t>
+          <t>2026-07-19 08:11:46</t>
         </is>
       </c>
     </row>
@@ -1368,10 +1368,10 @@
         <v>2.28</v>
       </c>
       <c r="G4" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I4" t="n">
         <v>3.85</v>
@@ -1380,215 +1380,215 @@
         <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P4" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-19 05:58:00</t>
+          <t>2026-07-19 08:11:46</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>2.04</v>
       </c>
       <c r="G5" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H5" t="n">
         <v>3.55</v>
@@ -1649,7 +1649,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q5" t="n">
         <v>1.65</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-19 05:58:00</t>
+          <t>2026-07-19 08:11:46</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-19 05:58:00</t>
+          <t>2026-07-19 08:11:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -860,55 +860,55 @@
         <v>1.93</v>
       </c>
       <c r="G2" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I2" t="n">
         <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
         <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O2" t="n">
         <v>1.33</v>
       </c>
       <c r="P2" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
         <v>3.55</v>
       </c>
       <c r="T2" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V2" t="n">
         <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X2" t="n">
         <v>16.5</v>
@@ -950,7 +950,7 @@
         <v>26</v>
       </c>
       <c r="AK2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL2" t="n">
         <v>44</v>
@@ -965,28 +965,28 @@
         <v>80</v>
       </c>
       <c r="AP2" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>13.5</v>
+        <v>4.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AX2" t="n">
         <v>10.5</v>
@@ -995,55 +995,55 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB2" t="n">
         <v>5.1</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="BC2" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE2" t="n">
         <v>6</v>
       </c>
-      <c r="BB2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BF2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>10.5</v>
       </c>
-      <c r="BG2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BK2" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BL2" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="BM2" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BP2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BQ2" t="n">
         <v>10</v>
@@ -1052,35 +1052,35 @@
         <v>34</v>
       </c>
       <c r="BS2" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BU2" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BV2" t="n">
         <v>46</v>
       </c>
       <c r="BW2" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
         <v>60</v>
       </c>
       <c r="BY2" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
         <v>29</v>
       </c>
       <c r="CA2" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-19 08:11:46</t>
+          <t>2026-07-19 10:24:45</t>
         </is>
       </c>
     </row>
@@ -1120,16 +1120,16 @@
         <v>2.24</v>
       </c>
       <c r="I3" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J3" t="n">
         <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="M3" t="n">
         <v>1.12</v>
@@ -1141,13 +1141,13 @@
         <v>1.5</v>
       </c>
       <c r="P3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1156,16 +1156,16 @@
         <v>2.08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W3" t="n">
         <v>1.33</v>
       </c>
       <c r="X3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y3" t="n">
         <v>7.6</v>
@@ -1174,19 +1174,19 @@
         <v>13</v>
       </c>
       <c r="AA3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB3" t="n">
         <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD3" t="n">
         <v>12</v>
       </c>
       <c r="AE3" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AF3" t="n">
         <v>26</v>
@@ -1204,19 +1204,19 @@
         <v>110</v>
       </c>
       <c r="AK3" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AL3" t="n">
         <v>100</v>
       </c>
       <c r="AM3" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN3" t="n">
         <v>100</v>
       </c>
       <c r="AO3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP3" t="n">
         <v>8.4</v>
@@ -1237,13 +1237,13 @@
         <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>21</v>
+        <v>9.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>17.5</v>
+        <v>9</v>
       </c>
       <c r="AY3" t="n">
         <v>14.5</v>
@@ -1252,64 +1252,64 @@
         <v>19.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC3" t="n">
         <v>11.5</v>
       </c>
-      <c r="BC3" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BD3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BE3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF3" t="n">
         <v>12</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>11</v>
       </c>
       <c r="BG3" t="n">
         <v>21</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BJ3" t="n">
         <v>13.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
         <v>230</v>
       </c>
       <c r="BM3" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BO3" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
         <v>46</v>
       </c>
       <c r="BQ3" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
         <v>70</v>
       </c>
       <c r="BS3" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BU3" t="n">
         <v>3.75</v>
@@ -1318,23 +1318,23 @@
         <v>23</v>
       </c>
       <c r="BW3" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
         <v>50</v>
       </c>
       <c r="BY3" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
         <v>55</v>
       </c>
       <c r="CA3" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-19 08:11:46</t>
+          <t>2026-07-19 10:24:45</t>
         </is>
       </c>
     </row>
@@ -1374,46 +1374,46 @@
         <v>3.45</v>
       </c>
       <c r="I4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J4" t="n">
         <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.41</v>
       </c>
       <c r="P4" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U4" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
         <v>1.7</v>
@@ -1431,10 +1431,10 @@
         <v>85</v>
       </c>
       <c r="AB4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD4" t="n">
         <v>17.5</v>
@@ -1476,28 +1476,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR4" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU4" t="n">
         <v>6.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AY4" t="n">
         <v>10</v>
@@ -1506,25 +1506,25 @@
         <v>16.5</v>
       </c>
       <c r="BA4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD4" t="n">
         <v>5.5</v>
       </c>
-      <c r="BB4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BE4" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BF4" t="n">
         <v>19</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BH4" t="n">
         <v>3.4</v>
@@ -1536,13 +1536,13 @@
         <v>11.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>170</v>
       </c>
       <c r="BM4" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
         <v>5.7</v>
@@ -1554,13 +1554,13 @@
         <v>22</v>
       </c>
       <c r="BQ4" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
         <v>42</v>
       </c>
       <c r="BS4" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
         <v>7.6</v>
@@ -1572,23 +1572,23 @@
         <v>36</v>
       </c>
       <c r="BW4" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
         <v>55</v>
       </c>
       <c r="BY4" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
         <v>40</v>
       </c>
       <c r="CA4" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-19 08:11:46</t>
+          <t>2026-07-19 10:24:45</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>2.04</v>
       </c>
       <c r="G5" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H5" t="n">
         <v>3.55</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-19 08:11:46</t>
+          <t>2026-07-19 10:24:45</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G6" t="n">
         <v>2.56</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="I6" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K6" t="n">
         <v>3.35</v>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-19 08:11:46</t>
+          <t>2026-07-19 10:24:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -881,7 +881,7 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O2" t="n">
         <v>1.33</v>
@@ -893,10 +893,10 @@
         <v>1.98</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S2" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T2" t="n">
         <v>1.85</v>
@@ -911,7 +911,7 @@
         <v>2.04</v>
       </c>
       <c r="X2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y2" t="n">
         <v>18</v>
@@ -971,7 +971,7 @@
         <v>13.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AS2" t="n">
         <v>6</v>
@@ -983,19 +983,19 @@
         <v>7.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AX2" t="n">
         <v>10.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BA2" t="n">
         <v>5.8</v>
@@ -1007,7 +1007,7 @@
         <v>18</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE2" t="n">
         <v>6</v>
@@ -1034,7 +1034,7 @@
         <v>160</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BN2" t="n">
         <v>4.6</v>
@@ -1052,7 +1052,7 @@
         <v>34</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BT2" t="n">
         <v>8</v>
@@ -1064,23 +1064,23 @@
         <v>46</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BX2" t="n">
         <v>60</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BZ2" t="n">
         <v>29</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-19 10:24:45</t>
+          <t>2026-07-19 12:37:19</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G3" t="n">
         <v>4.1</v>
@@ -1135,13 +1135,13 @@
         <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="O3" t="n">
         <v>1.5</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q3" t="n">
         <v>2.48</v>
@@ -1282,34 +1282,34 @@
         <v>13.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BL3" t="n">
         <v>230</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BN3" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BP3" t="n">
         <v>46</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BR3" t="n">
         <v>70</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BT3" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BU3" t="n">
         <v>3.75</v>
@@ -1318,23 +1318,23 @@
         <v>23</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BX3" t="n">
         <v>50</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BZ3" t="n">
         <v>55</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-19 10:24:45</t>
+          <t>2026-07-19 12:37:19</t>
         </is>
       </c>
     </row>
@@ -1368,16 +1368,16 @@
         <v>2.28</v>
       </c>
       <c r="G4" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H4" t="n">
         <v>3.45</v>
       </c>
       <c r="I4" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
         <v>3.4</v>
@@ -1389,34 +1389,34 @@
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O4" t="n">
         <v>1.41</v>
       </c>
       <c r="P4" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S4" t="n">
         <v>4.1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U4" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X4" t="n">
         <v>13</v>
@@ -1446,19 +1446,19 @@
         <v>16.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ4" t="n">
         <v>38</v>
       </c>
       <c r="AK4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL4" t="n">
         <v>55</v>
@@ -1467,7 +1467,7 @@
         <v>140</v>
       </c>
       <c r="AN4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO4" t="n">
         <v>65</v>
@@ -1482,19 +1482,19 @@
         <v>21</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT4" t="n">
         <v>7.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV4" t="n">
         <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AX4" t="n">
         <v>12.5</v>
@@ -1506,43 +1506,43 @@
         <v>16.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF4" t="n">
         <v>19</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BH4" t="n">
         <v>3.4</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ4" t="n">
         <v>11.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BL4" t="n">
         <v>170</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BN4" t="n">
         <v>5.7</v>
@@ -1551,44 +1551,44 @@
         <v>4</v>
       </c>
       <c r="BP4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BR4" t="n">
         <v>42</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BT4" t="n">
         <v>7.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV4" t="n">
         <v>36</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BX4" t="n">
         <v>55</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BZ4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-19 10:24:45</t>
+          <t>2026-07-19 12:37:19</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-19 10:24:45</t>
+          <t>2026-07-19 12:37:19</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-19 10:24:45</t>
+          <t>2026-07-19 12:37:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="G2" t="n">
         <v>1.96</v>
@@ -866,13 +866,13 @@
         <v>4.4</v>
       </c>
       <c r="I2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
         <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
         <v>1.43</v>
@@ -881,19 +881,19 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O2" t="n">
         <v>1.33</v>
       </c>
       <c r="P2" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q2" t="n">
         <v>1.98</v>
       </c>
       <c r="R2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
         <v>3.5</v>
@@ -947,7 +947,7 @@
         <v>75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK2" t="n">
         <v>24</v>
@@ -971,7 +971,7 @@
         <v>13.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AS2" t="n">
         <v>6</v>
@@ -998,7 +998,7 @@
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BB2" t="n">
         <v>5.1</v>
@@ -1010,16 +1010,16 @@
         <v>5.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF2" t="n">
         <v>12</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="BI2" t="n">
         <v>2.72</v>
@@ -1031,10 +1031,10 @@
         <v>8</v>
       </c>
       <c r="BL2" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BN2" t="n">
         <v>4.6</v>
@@ -1049,10 +1049,10 @@
         <v>10</v>
       </c>
       <c r="BR2" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT2" t="n">
         <v>8</v>
@@ -1061,26 +1061,26 @@
         <v>5.5</v>
       </c>
       <c r="BV2" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BX2" t="n">
         <v>60</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="BZ2" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G3" t="n">
         <v>4.1</v>
@@ -1228,7 +1228,7 @@
         <v>11.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>22</v>
+        <v>9.6</v>
       </c>
       <c r="AT3" t="n">
         <v>9.800000000000001</v>
@@ -1240,10 +1240,10 @@
         <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.4</v>
+        <v>21</v>
       </c>
       <c r="AX3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AY3" t="n">
         <v>14.5</v>
@@ -1273,25 +1273,25 @@
         <v>21</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="BI3" t="n">
         <v>2.28</v>
       </c>
       <c r="BJ3" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL3" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="BN3" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="BO3" t="n">
         <v>5.3</v>
@@ -1300,41 +1300,41 @@
         <v>46</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="BR3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BS3" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="BT3" t="n">
         <v>4.9</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="BV3" t="n">
         <v>23</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX3" t="n">
         <v>50</v>
       </c>
       <c r="BY3" t="n">
-        <v>5.3</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
         <v>55</v>
       </c>
       <c r="CA3" t="n">
-        <v>5.3</v>
+        <v>10</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
         <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L4" t="n">
         <v>1.47</v>
@@ -1389,31 +1389,31 @@
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P4" t="n">
         <v>1.76</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="R4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S4" t="n">
         <v>4.1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U4" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
         <v>1.71</v>
@@ -1440,7 +1440,7 @@
         <v>17.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF4" t="n">
         <v>16.5</v>
@@ -1467,7 +1467,7 @@
         <v>140</v>
       </c>
       <c r="AN4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO4" t="n">
         <v>65</v>
@@ -1506,16 +1506,16 @@
         <v>16.5</v>
       </c>
       <c r="BA4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD4" t="n">
         <v>5.9</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>5.8</v>
       </c>
       <c r="BE4" t="n">
         <v>6.2</v>
@@ -1524,71 +1524,71 @@
         <v>19</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="BI4" t="n">
         <v>2.58</v>
       </c>
       <c r="BJ4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
         <v>11.5</v>
       </c>
-      <c r="BK4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>170</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BN4" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BO4" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BP4" t="n">
         <v>21</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="BR4" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BS4" t="n">
-        <v>5.4</v>
+        <v>9.4</v>
       </c>
       <c r="BT4" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU4" t="n">
         <v>5.3</v>
       </c>
       <c r="BV4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="BX4" t="n">
         <v>55</v>
       </c>
       <c r="BY4" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="BZ4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G5" t="n">
         <v>2.16</v>
@@ -1637,16 +1637,16 @@
         <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P5" t="n">
         <v>2.34</v>
@@ -1655,194 +1655,194 @@
         <v>1.65</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -860,7 +860,7 @@
         <v>1.9</v>
       </c>
       <c r="G2" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H2" t="n">
         <v>4.4</v>
@@ -899,7 +899,7 @@
         <v>3.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U2" t="n">
         <v>2.06</v>
@@ -908,7 +908,7 @@
         <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X2" t="n">
         <v>16</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
         <v>2.24</v>
@@ -1138,7 +1138,7 @@
         <v>2.84</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P3" t="n">
         <v>1.61</v>
@@ -1153,7 +1153,7 @@
         <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U3" t="n">
         <v>1.83</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>2.28</v>
       </c>
       <c r="G4" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H4" t="n">
         <v>3.45</v>
@@ -1392,13 +1392,13 @@
         <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P4" t="n">
         <v>1.76</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R4" t="n">
         <v>1.29</v>
@@ -1407,7 +1407,7 @@
         <v>4.1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U4" t="n">
         <v>2</v>
@@ -1416,7 +1416,7 @@
         <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X4" t="n">
         <v>13</v>
@@ -1473,13 +1473,13 @@
         <v>65</v>
       </c>
       <c r="AP4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
         <v>10</v>
       </c>
       <c r="AR4" t="n">
-        <v>21</v>
+        <v>5.4</v>
       </c>
       <c r="AS4" t="n">
         <v>6</v>
@@ -1488,22 +1488,22 @@
         <v>7.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AW4" t="n">
         <v>5.9</v>
       </c>
       <c r="AX4" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AY4" t="n">
         <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA4" t="n">
         <v>6</v>
@@ -1512,7 +1512,7 @@
         <v>5.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.5</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
         <v>5.9</v>
@@ -1521,7 +1521,7 @@
         <v>6.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BG4" t="n">
         <v>6</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -1655,16 +1655,16 @@
         <v>1.65</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
         <v>2.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
         <v>1.35</v>
@@ -1721,13 +1721,13 @@
         <v>70</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="AQ5" t="n">
         <v>13.5</v>
@@ -1736,7 +1736,7 @@
         <v>21</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="AT5" t="n">
         <v>9.6</v>
@@ -1748,43 +1748,43 @@
         <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.98</v>
+        <v>3.85</v>
       </c>
       <c r="AX5" t="n">
         <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>2.54</v>
+        <v>3.15</v>
       </c>
       <c r="AZ5" t="n">
         <v>11</v>
       </c>
       <c r="BA5" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="BD5" t="n">
         <v>20</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.2</v>
+        <v>7.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BJ5" t="n">
         <v>11.5</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>22</v>
+        <v>2.12</v>
       </c>
       <c r="BN5" t="n">
         <v>6.8</v>
@@ -1814,7 +1814,7 @@
         <v>30</v>
       </c>
       <c r="BS5" t="n">
-        <v>15.5</v>
+        <v>2.02</v>
       </c>
       <c r="BT5" t="n">
         <v>9.199999999999999</v>
@@ -1826,23 +1826,23 @@
         <v>32</v>
       </c>
       <c r="BW5" t="n">
-        <v>16.5</v>
+        <v>2.02</v>
       </c>
       <c r="BX5" t="n">
         <v>42</v>
       </c>
       <c r="BY5" t="n">
-        <v>20</v>
+        <v>2.06</v>
       </c>
       <c r="BZ5" t="n">
         <v>23</v>
       </c>
       <c r="CA5" t="n">
-        <v>11.5</v>
+        <v>1.98</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="Q6" t="n">
         <v>2.48</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H3" t="n">
         <v>2.24</v>
@@ -1135,37 +1135,37 @@
         <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="O3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="R3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U3" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="V3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W3" t="n">
         <v>1.33</v>
       </c>
       <c r="X3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y3" t="n">
         <v>7.6</v>
@@ -1228,13 +1228,13 @@
         <v>11.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV3" t="n">
         <v>10.5</v>
@@ -1252,43 +1252,43 @@
         <v>19.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC3" t="n">
         <v>12</v>
       </c>
-      <c r="BC3" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BD3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BE3" t="n">
         <v>13</v>
       </c>
       <c r="BF3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG3" t="n">
         <v>21</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN3" t="n">
         <v>7</v>
@@ -1297,7 +1297,7 @@
         <v>5.3</v>
       </c>
       <c r="BP3" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
         <v>10</v>
@@ -1306,7 +1306,7 @@
         <v>60</v>
       </c>
       <c r="BS3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT3" t="n">
         <v>4.9</v>
@@ -1318,23 +1318,23 @@
         <v>23</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>55</v>
       </c>
       <c r="CA3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>2.28</v>
       </c>
       <c r="G4" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H4" t="n">
         <v>3.45</v>
@@ -1407,7 +1407,7 @@
         <v>4.1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U4" t="n">
         <v>2</v>
@@ -1479,7 +1479,7 @@
         <v>10</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.4</v>
+        <v>21</v>
       </c>
       <c r="AS4" t="n">
         <v>6</v>
@@ -1488,7 +1488,7 @@
         <v>7.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV4" t="n">
         <v>11.5</v>
@@ -1503,7 +1503,7 @@
         <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA4" t="n">
         <v>6</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -1622,16 +1622,16 @@
         <v>2.06</v>
       </c>
       <c r="G5" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K5" t="n">
         <v>4.1</v>
@@ -1640,13 +1640,13 @@
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P5" t="n">
         <v>2.34</v>
@@ -1655,130 +1655,130 @@
         <v>1.65</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="S5" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>2.46</v>
       </c>
       <c r="V5" t="n">
         <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X5" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="Y5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Z5" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AA5" t="n">
         <v>75</v>
       </c>
       <c r="AB5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AC5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG5" t="n">
         <v>11</v>
       </c>
-      <c r="AD5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AH5" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AJ5" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AL5" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AM5" t="n">
         <v>70</v>
       </c>
       <c r="AN5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>13</v>
       </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR5" t="n">
+      <c r="BA5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG5" t="n">
         <v>21</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>4.2</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
@@ -1790,7 +1790,7 @@
         <v>11.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>6</v>
+        <v>1.82</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1802,13 +1802,13 @@
         <v>6.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BP5" t="n">
         <v>18.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>9.199999999999999</v>
+        <v>1.94</v>
       </c>
       <c r="BR5" t="n">
         <v>30</v>
@@ -1820,7 +1820,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BU5" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BV5" t="n">
         <v>32</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -1876,227 +1876,227 @@
         <v>2.34</v>
       </c>
       <c r="G6" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H6" t="n">
         <v>3.45</v>
       </c>
       <c r="I6" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="J6" t="n">
         <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P6" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,7 +866,7 @@
         <v>4.4</v>
       </c>
       <c r="I2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J2" t="n">
         <v>3.7</v>
@@ -875,7 +875,7 @@
         <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -884,19 +884,19 @@
         <v>3.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P2" t="n">
         <v>1.94</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
         <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T2" t="n">
         <v>1.86</v>
@@ -914,10 +914,10 @@
         <v>16</v>
       </c>
       <c r="Y2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA2" t="n">
         <v>120</v>
@@ -971,10 +971,10 @@
         <v>13.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT2" t="n">
         <v>8</v>
@@ -983,10 +983,10 @@
         <v>7.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.9</v>
+        <v>15.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AX2" t="n">
         <v>10.5</v>
@@ -995,34 +995,34 @@
         <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="BA2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB2" t="n">
         <v>5.9</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>5.1</v>
       </c>
       <c r="BC2" t="n">
         <v>18</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF2" t="n">
         <v>12</v>
       </c>
       <c r="BG2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="BJ2" t="n">
         <v>10.5</v>
@@ -1049,7 +1049,7 @@
         <v>10</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS2" t="n">
         <v>9.199999999999999</v>
@@ -1070,17 +1070,17 @@
         <v>60</v>
       </c>
       <c r="BY2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 21:18:54</t>
         </is>
       </c>
     </row>
@@ -1114,16 +1114,16 @@
         <v>3.75</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="H3" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I3" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K3" t="n">
         <v>3.3</v>
@@ -1138,58 +1138,58 @@
         <v>2.78</v>
       </c>
       <c r="O3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P3" t="n">
         <v>1.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="R3" t="n">
         <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U3" t="n">
         <v>1.81</v>
       </c>
       <c r="V3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AB3" t="n">
         <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD3" t="n">
         <v>12</v>
       </c>
       <c r="AE3" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AF3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG3" t="n">
         <v>17</v>
@@ -1201,25 +1201,25 @@
         <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK3" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL3" t="n">
         <v>100</v>
       </c>
       <c r="AM3" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AO3" t="n">
         <v>29</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ3" t="n">
         <v>6.8</v>
@@ -1228,67 +1228,67 @@
         <v>11.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.800000000000001</v>
+        <v>19</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.5</v>
+        <v>32</v>
       </c>
       <c r="BB3" t="n">
-        <v>12.5</v>
+        <v>34</v>
       </c>
       <c r="BC3" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="BD3" t="n">
-        <v>12.5</v>
+        <v>36</v>
       </c>
       <c r="BE3" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="BF3" t="n">
-        <v>12.5</v>
+        <v>34</v>
       </c>
       <c r="BG3" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BH3" t="n">
         <v>2.76</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="BJ3" t="n">
         <v>11.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BN3" t="n">
         <v>7</v>
@@ -1300,13 +1300,13 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BR3" t="n">
         <v>60</v>
       </c>
       <c r="BS3" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT3" t="n">
         <v>4.9</v>
@@ -1315,7 +1315,7 @@
         <v>4.4</v>
       </c>
       <c r="BV3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BW3" t="n">
         <v>8.800000000000001</v>
@@ -1324,17 +1324,17 @@
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>55</v>
       </c>
       <c r="CA3" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 21:18:54</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G4" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.47</v>
@@ -1407,19 +1407,19 @@
         <v>4.1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U4" t="n">
         <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y4" t="n">
         <v>13.5</v>
@@ -1446,7 +1446,7 @@
         <v>16.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH4" t="n">
         <v>22</v>
@@ -1476,13 +1476,13 @@
         <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR4" t="n">
         <v>21</v>
       </c>
       <c r="AS4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT4" t="n">
         <v>7.8</v>
@@ -1491,13 +1491,13 @@
         <v>6.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AX4" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AY4" t="n">
         <v>10</v>
@@ -1506,25 +1506,25 @@
         <v>16.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BC4" t="n">
         <v>21</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF4" t="n">
         <v>17.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BH4" t="n">
         <v>3.1</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 21:18:54</t>
         </is>
       </c>
     </row>
@@ -1622,13 +1622,13 @@
         <v>2.06</v>
       </c>
       <c r="G5" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H5" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I5" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J5" t="n">
         <v>3.7</v>
@@ -1664,13 +1664,13 @@
         <v>1.6</v>
       </c>
       <c r="U5" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W5" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X5" t="n">
         <v>24</v>
@@ -1679,7 +1679,7 @@
         <v>19</v>
       </c>
       <c r="Z5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA5" t="n">
         <v>75</v>
@@ -1697,7 +1697,7 @@
         <v>38</v>
       </c>
       <c r="AF5" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG5" t="n">
         <v>11</v>
@@ -1733,10 +1733,10 @@
         <v>16.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AS5" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AT5" t="n">
         <v>11</v>
@@ -1748,7 +1748,7 @@
         <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>32</v>
+        <v>8.4</v>
       </c>
       <c r="AX5" t="n">
         <v>13.5</v>
@@ -1760,7 +1760,7 @@
         <v>13</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BB5" t="n">
         <v>18.5</v>
@@ -1769,10 +1769,10 @@
         <v>17.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BF5" t="n">
         <v>10</v>
@@ -1802,7 +1802,7 @@
         <v>6.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP5" t="n">
         <v>18.5</v>
@@ -1820,7 +1820,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BV5" t="n">
         <v>32</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 21:18:54</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G6" t="n">
         <v>2.54</v>
@@ -1882,7 +1882,7 @@
         <v>3.45</v>
       </c>
       <c r="I6" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
         <v>3.15</v>
@@ -1897,31 +1897,31 @@
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="O6" t="n">
         <v>1.47</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="Q6" t="n">
         <v>2.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S6" t="n">
         <v>5.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
         <v>1.65</v>
@@ -1936,7 +1936,7 @@
         <v>28</v>
       </c>
       <c r="AA6" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AB6" t="n">
         <v>7.8</v>
@@ -1966,7 +1966,7 @@
         <v>44</v>
       </c>
       <c r="AK6" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AL6" t="n">
         <v>70</v>
@@ -1978,25 +1978,25 @@
         <v>40</v>
       </c>
       <c r="AO6" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AR6" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT6" t="n">
         <v>6</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AV6" t="n">
         <v>12</v>
@@ -2008,16 +2008,16 @@
         <v>11</v>
       </c>
       <c r="AY6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC6" t="n">
         <v>6</v>
@@ -2044,13 +2044,13 @@
         <v>11.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="BN6" t="n">
         <v>5.1</v>
@@ -2059,16 +2059,16 @@
         <v>4.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="BR6" t="n">
         <v>60</v>
       </c>
       <c r="BS6" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="BT6" t="n">
         <v>6.8</v>
@@ -2080,23 +2080,785 @@
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BZ6" t="n">
         <v>65</v>
       </c>
       <c r="CA6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-07-19 21:18:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Atletico MG</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-07-19 21:18:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Criciuma</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR8" t="n">
         <v>21</v>
       </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-07-19 19:08:57</t>
+      <c r="AS8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>28</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-07-19 21:18:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Avai</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>America MG</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-07-19 21:18:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -860,7 +860,7 @@
         <v>1.9</v>
       </c>
       <c r="G2" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H2" t="n">
         <v>4.4</v>
@@ -908,7 +908,7 @@
         <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X2" t="n">
         <v>16</v>
@@ -929,7 +929,7 @@
         <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE2" t="n">
         <v>70</v>
@@ -938,7 +938,7 @@
         <v>13.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
         <v>23</v>
@@ -971,10 +971,10 @@
         <v>13.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT2" t="n">
         <v>8</v>
@@ -986,7 +986,7 @@
         <v>15.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX2" t="n">
         <v>10.5</v>
@@ -998,34 +998,34 @@
         <v>17</v>
       </c>
       <c r="BA2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BC2" t="n">
         <v>18</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF2" t="n">
         <v>12</v>
       </c>
       <c r="BG2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH2" t="n">
         <v>3.35</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK2" t="n">
         <v>8</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="BN2" t="n">
         <v>4.6</v>
@@ -1043,7 +1043,7 @@
         <v>4.1</v>
       </c>
       <c r="BP2" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BQ2" t="n">
         <v>10</v>
@@ -1052,35 +1052,35 @@
         <v>29</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BT2" t="n">
         <v>8</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BX2" t="n">
         <v>60</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-19 21:18:54</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>3.95</v>
       </c>
       <c r="H3" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="I3" t="n">
         <v>2.32</v>
@@ -1126,10 +1126,10 @@
         <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="L3" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="M3" t="n">
         <v>1.12</v>
@@ -1138,28 +1138,28 @@
         <v>2.78</v>
       </c>
       <c r="O3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P3" t="n">
         <v>1.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="R3" t="n">
         <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T3" t="n">
         <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W3" t="n">
         <v>1.34</v>
@@ -1186,13 +1186,13 @@
         <v>12</v>
       </c>
       <c r="AE3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF3" t="n">
         <v>25</v>
       </c>
       <c r="AG3" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AH3" t="n">
         <v>23</v>
@@ -1213,13 +1213,13 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AO3" t="n">
         <v>29</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ3" t="n">
         <v>6.8</v>
@@ -1237,7 +1237,7 @@
         <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW3" t="n">
         <v>19.5</v>
@@ -1252,7 +1252,7 @@
         <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB3" t="n">
         <v>34</v>
@@ -1276,7 +1276,7 @@
         <v>2.76</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BJ3" t="n">
         <v>11.5</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BN3" t="n">
         <v>7</v>
@@ -1300,13 +1300,13 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BR3" t="n">
         <v>60</v>
       </c>
       <c r="BS3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT3" t="n">
         <v>4.9</v>
@@ -1318,23 +1318,23 @@
         <v>19</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ3" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="CA3" t="n">
         <v>12.5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-19 21:18:54</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>2.26</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H4" t="n">
         <v>3.5</v>
@@ -1419,7 +1419,7 @@
         <v>1.71</v>
       </c>
       <c r="X4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y4" t="n">
         <v>13.5</v>
@@ -1428,7 +1428,7 @@
         <v>29</v>
       </c>
       <c r="AA4" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AB4" t="n">
         <v>8.800000000000001</v>
@@ -1482,7 +1482,7 @@
         <v>21</v>
       </c>
       <c r="AS4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT4" t="n">
         <v>7.8</v>
@@ -1494,7 +1494,7 @@
         <v>13.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX4" t="n">
         <v>12.5</v>
@@ -1506,25 +1506,25 @@
         <v>16.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC4" t="n">
         <v>21</v>
       </c>
       <c r="BD4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BG4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH4" t="n">
         <v>3.1</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-19 21:18:54</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
         <v>18.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.94</v>
+        <v>10</v>
       </c>
       <c r="BR5" t="n">
         <v>30</v>
@@ -1820,7 +1820,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BV5" t="n">
         <v>32</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-19 21:18:54</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         <v>9.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z6" t="n">
         <v>28</v>
@@ -1990,7 +1990,7 @@
         <v>20</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT6" t="n">
         <v>6</v>
@@ -2002,7 +2002,7 @@
         <v>12</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX6" t="n">
         <v>11</v>
@@ -2014,25 +2014,25 @@
         <v>19</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BD6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF6" t="n">
         <v>6.6</v>
       </c>
-      <c r="BE6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BG6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH6" t="n">
         <v>2.8</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-19 21:18:54</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -2130,16 +2130,16 @@
         <v>2.16</v>
       </c>
       <c r="G7" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="H7" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="I7" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K7" t="n">
         <v>3.6</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-19 21:18:54</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -2381,73 +2381,73 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G8" t="n">
         <v>2.48</v>
       </c>
       <c r="H8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I8" t="n">
         <v>4.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K8" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L8" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="M8" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S8" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="T8" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U8" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="V8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W8" t="n">
         <v>1.67</v>
       </c>
       <c r="X8" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z8" t="n">
         <v>27</v>
       </c>
       <c r="AA8" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AB8" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC8" t="n">
         <v>7.6</v>
@@ -2465,7 +2465,7 @@
         <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
         <v>95</v>
@@ -2483,13 +2483,13 @@
         <v>200</v>
       </c>
       <c r="AN8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO8" t="n">
         <v>100</v>
       </c>
       <c r="AP8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AQ8" t="n">
         <v>9.199999999999999</v>
@@ -2498,10 +2498,10 @@
         <v>21</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU8" t="n">
         <v>6.2</v>
@@ -2510,7 +2510,7 @@
         <v>13.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX8" t="n">
         <v>11.5</v>
@@ -2519,10 +2519,10 @@
         <v>10</v>
       </c>
       <c r="AZ8" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB8" t="n">
         <v>21</v>
@@ -2531,80 +2531,80 @@
         <v>20</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF8" t="n">
+        <v>24</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK8" t="n">
         <v>7.4</v>
       </c>
-      <c r="BG8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.74</v>
+        <v>10.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP8" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.64</v>
+        <v>7.2</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.69</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT8" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV8" t="n">
         <v>50</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.68</v>
+        <v>8.6</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.7</v>
+        <v>9.4</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.69</v>
+        <v>9</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-19 21:18:54</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G9" t="n">
         <v>2.42</v>
       </c>
       <c r="H9" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I9" t="n">
         <v>4.6</v>
@@ -2650,7 +2650,7 @@
         <v>2.88</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
         <v>1.42</v>
@@ -2665,10 +2665,10 @@
         <v>1.41</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R9" t="n">
         <v>1.21</v>
@@ -2800,65 +2800,65 @@
         <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-19 21:18:54</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,7 +866,7 @@
         <v>4.4</v>
       </c>
       <c r="I2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
         <v>3.7</v>
@@ -875,7 +875,7 @@
         <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -890,7 +890,7 @@
         <v>1.94</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R2" t="n">
         <v>1.36</v>
@@ -911,13 +911,13 @@
         <v>2.04</v>
       </c>
       <c r="X2" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA2" t="n">
         <v>120</v>
@@ -959,7 +959,7 @@
         <v>130</v>
       </c>
       <c r="AN2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AO2" t="n">
         <v>80</v>
@@ -971,10 +971,10 @@
         <v>13.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT2" t="n">
         <v>8</v>
@@ -986,7 +986,7 @@
         <v>15.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX2" t="n">
         <v>10.5</v>
@@ -998,28 +998,28 @@
         <v>17</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>6</v>
+        <v>17.5</v>
       </c>
       <c r="BC2" t="n">
         <v>18</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF2" t="n">
         <v>12</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BI2" t="n">
         <v>3.1</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN2" t="n">
         <v>4.6</v>
@@ -1052,7 +1052,7 @@
         <v>29</v>
       </c>
       <c r="BS2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT2" t="n">
         <v>8</v>
@@ -1064,23 +1064,23 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX2" t="n">
         <v>60</v>
       </c>
       <c r="BY2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -1120,22 +1120,22 @@
         <v>2.24</v>
       </c>
       <c r="I3" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="J3" t="n">
         <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L3" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M3" t="n">
         <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="O3" t="n">
         <v>1.52</v>
@@ -1156,13 +1156,13 @@
         <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V3" t="n">
         <v>1.76</v>
       </c>
       <c r="W3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X3" t="n">
         <v>9.4</v>
@@ -1204,7 +1204,7 @@
         <v>100</v>
       </c>
       <c r="AK3" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL3" t="n">
         <v>100</v>
@@ -1273,68 +1273,68 @@
         <v>18.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN3" t="n">
         <v>7</v>
       </c>
       <c r="BO3" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BR3" t="n">
         <v>60</v>
       </c>
       <c r="BS3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BT3" t="n">
         <v>4.9</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="BV3" t="n">
         <v>19</v>
       </c>
       <c r="BW3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>44</v>
       </c>
       <c r="CA3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -1368,10 +1368,10 @@
         <v>2.26</v>
       </c>
       <c r="G4" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I4" t="n">
         <v>3.7</v>
@@ -1389,7 +1389,7 @@
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O4" t="n">
         <v>1.41</v>
@@ -1398,13 +1398,13 @@
         <v>1.76</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T4" t="n">
         <v>1.9</v>
@@ -1416,7 +1416,7 @@
         <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="X4" t="n">
         <v>11.5</v>
@@ -1476,7 +1476,7 @@
         <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR4" t="n">
         <v>21</v>
@@ -1488,13 +1488,13 @@
         <v>7.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX4" t="n">
         <v>12.5</v>
@@ -1521,7 +1521,7 @@
         <v>7.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG4" t="n">
         <v>7.2</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G5" t="n">
         <v>2.16</v>
       </c>
       <c r="H5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I5" t="n">
         <v>3.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,16 +1643,16 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P5" t="n">
         <v>2.34</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R5" t="n">
         <v>1.54</v>
@@ -1661,7 +1661,7 @@
         <v>2.62</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="U5" t="n">
         <v>2.48</v>
@@ -1676,13 +1676,13 @@
         <v>24</v>
       </c>
       <c r="Y5" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Z5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA5" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB5" t="n">
         <v>13</v>
@@ -1691,13 +1691,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF5" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG5" t="n">
         <v>11</v>
@@ -1706,7 +1706,7 @@
         <v>15.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ5" t="n">
         <v>26</v>
@@ -1718,7 +1718,7 @@
         <v>29</v>
       </c>
       <c r="AM5" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AN5" t="n">
         <v>11.5</v>
@@ -1730,13 +1730,13 @@
         <v>18</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR5" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT5" t="n">
         <v>11</v>
@@ -1745,10 +1745,10 @@
         <v>8</v>
       </c>
       <c r="AV5" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX5" t="n">
         <v>13.5</v>
@@ -1760,7 +1760,7 @@
         <v>13</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB5" t="n">
         <v>18.5</v>
@@ -1769,80 +1769,80 @@
         <v>17.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF5" t="n">
         <v>10</v>
       </c>
       <c r="BG5" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="BJ5" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="BN5" t="n">
         <v>6.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="BP5" t="n">
         <v>18.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>10</v>
+        <v>2.06</v>
       </c>
       <c r="BR5" t="n">
         <v>30</v>
       </c>
       <c r="BS5" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="BT5" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="BV5" t="n">
         <v>32</v>
       </c>
       <c r="BW5" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="BX5" t="n">
         <v>42</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="BZ5" t="n">
         <v>23</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G6" t="n">
         <v>2.54</v>
@@ -1882,7 +1882,7 @@
         <v>3.45</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J6" t="n">
         <v>3.15</v>
@@ -1894,34 +1894,34 @@
         <v>1.48</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="O6" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="P6" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="Q6" t="n">
         <v>2.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S6" t="n">
         <v>5.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
         <v>1.65</v>
@@ -1930,10 +1930,10 @@
         <v>9.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA6" t="n">
         <v>80</v>
@@ -1945,7 +1945,7 @@
         <v>7.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE6" t="n">
         <v>65</v>
@@ -1960,10 +1960,10 @@
         <v>26</v>
       </c>
       <c r="AI6" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AK6" t="n">
         <v>34</v>
@@ -1972,13 +1972,13 @@
         <v>70</v>
       </c>
       <c r="AM6" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN6" t="n">
         <v>40</v>
       </c>
       <c r="AO6" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AP6" t="n">
         <v>8</v>
@@ -1987,13 +1987,13 @@
         <v>8</v>
       </c>
       <c r="AR6" t="n">
-        <v>20</v>
+        <v>5.9</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AT6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU6" t="n">
         <v>6.4</v>
@@ -2002,7 +2002,7 @@
         <v>12</v>
       </c>
       <c r="AW6" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AX6" t="n">
         <v>11</v>
@@ -2014,25 +2014,25 @@
         <v>19</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BB6" t="n">
         <v>6.4</v>
       </c>
       <c r="BC6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF6" t="n">
         <v>6.4</v>
       </c>
-      <c r="BD6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BG6" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH6" t="n">
         <v>2.8</v>
@@ -2065,7 +2065,7 @@
         <v>8.4</v>
       </c>
       <c r="BR6" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
         <v>10.5</v>
@@ -2089,14 +2089,14 @@
         <v>11</v>
       </c>
       <c r="BZ6" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
         <v>10.5</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G7" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="H7" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I7" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="J7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K7" t="n">
         <v>3.55</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.6</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G8" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H8" t="n">
         <v>3.6</v>
@@ -2393,7 +2393,7 @@
         <v>4.2</v>
       </c>
       <c r="J8" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="K8" t="n">
         <v>3.25</v>
@@ -2405,10 +2405,10 @@
         <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="O8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P8" t="n">
         <v>1.53</v>
@@ -2429,13 +2429,13 @@
         <v>1.76</v>
       </c>
       <c r="V8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W8" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y8" t="n">
         <v>11</v>
@@ -2444,7 +2444,7 @@
         <v>27</v>
       </c>
       <c r="AA8" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AB8" t="n">
         <v>7.6</v>
@@ -2456,7 +2456,7 @@
         <v>17.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF8" t="n">
         <v>14</v>
@@ -2465,10 +2465,10 @@
         <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ8" t="n">
         <v>42</v>
@@ -2477,7 +2477,7 @@
         <v>38</v>
       </c>
       <c r="AL8" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM8" t="n">
         <v>200</v>
@@ -2486,79 +2486,79 @@
         <v>40</v>
       </c>
       <c r="AO8" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP8" t="n">
         <v>7.6</v>
       </c>
       <c r="AQ8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS8" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AR8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AT8" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AU8" t="n">
         <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX8" t="n">
         <v>11.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ8" t="n">
         <v>19.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB8" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BC8" t="n">
-        <v>20</v>
+        <v>7.8</v>
       </c>
       <c r="BD8" t="n">
         <v>8.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="BG8" t="n">
         <v>9</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BI8" t="n">
         <v>2.5</v>
       </c>
       <c r="BJ8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
         <v>12</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>10.5</v>
       </c>
       <c r="BN8" t="n">
         <v>5.1</v>
@@ -2570,16 +2570,16 @@
         <v>21</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BR8" t="n">
         <v>60</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT8" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU8" t="n">
         <v>5.8</v>
@@ -2588,23 +2588,23 @@
         <v>50</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX8" t="n">
         <v>80</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BZ8" t="n">
         <v>65</v>
       </c>
       <c r="CA8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="G9" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H9" t="n">
         <v>3.5</v>
       </c>
       <c r="I9" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="J9" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>3.45</v>
       </c>
       <c r="L9" t="n">
         <v>1.42</v>
@@ -2668,7 +2668,7 @@
         <v>1.52</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.02</v>
+        <v>2.16</v>
       </c>
       <c r="R9" t="n">
         <v>1.21</v>
@@ -2677,16 +2677,16 @@
         <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="U9" t="n">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="V9" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,515 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Univ Catolica (Ecu)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Barcelona (Ecu)</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>60</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>44</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>38</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-07-20 01:38:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Mexican Liga MX</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Cruz Azul</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X11" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>390</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>240</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>27</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>16</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>16</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G2" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H2" t="n">
         <v>4.4</v>
       </c>
       <c r="I2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
         <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -887,16 +887,16 @@
         <v>1.34</v>
       </c>
       <c r="P2" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
         <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T2" t="n">
         <v>1.86</v>
@@ -908,37 +908,37 @@
         <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X2" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AA2" t="n">
         <v>120</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC2" t="n">
         <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
         <v>70</v>
       </c>
       <c r="AF2" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH2" t="n">
         <v>23</v>
@@ -947,7 +947,7 @@
         <v>75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK2" t="n">
         <v>24</v>
@@ -959,7 +959,7 @@
         <v>130</v>
       </c>
       <c r="AN2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AO2" t="n">
         <v>80</v>
@@ -971,10 +971,10 @@
         <v>13.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT2" t="n">
         <v>8</v>
@@ -983,10 +983,10 @@
         <v>7.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AX2" t="n">
         <v>10.5</v>
@@ -998,43 +998,43 @@
         <v>17</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BB2" t="n">
-        <v>17.5</v>
+        <v>6</v>
       </c>
       <c r="BC2" t="n">
         <v>18</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF2" t="n">
         <v>12</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN2" t="n">
         <v>4.6</v>
@@ -1043,10 +1043,10 @@
         <v>4.1</v>
       </c>
       <c r="BP2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ2" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="BR2" t="n">
         <v>29</v>
@@ -1058,29 +1058,29 @@
         <v>8</v>
       </c>
       <c r="BU2" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BV2" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX2" t="n">
         <v>1000</v>
       </c>
-      <c r="BW2" t="n">
+      <c r="BY2" t="n">
         <v>11.5</v>
       </c>
-      <c r="BX2" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>12</v>
-      </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -1120,22 +1120,22 @@
         <v>2.24</v>
       </c>
       <c r="I3" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J3" t="n">
         <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
         <v>1.45</v>
       </c>
       <c r="M3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O3" t="n">
         <v>1.52</v>
@@ -1144,10 +1144,10 @@
         <v>1.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S3" t="n">
         <v>5.2</v>
@@ -1156,10 +1156,10 @@
         <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="W3" t="n">
         <v>1.33</v>
@@ -1189,7 +1189,7 @@
         <v>32</v>
       </c>
       <c r="AF3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG3" t="n">
         <v>17.5</v>
@@ -1201,19 +1201,19 @@
         <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
         <v>65</v>
       </c>
       <c r="AL3" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
         <v>29</v>
@@ -1225,10 +1225,10 @@
         <v>6.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AT3" t="n">
         <v>9.6</v>
@@ -1252,13 +1252,13 @@
         <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="BB3" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BC3" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="BD3" t="n">
         <v>36</v>
@@ -1273,7 +1273,7 @@
         <v>18.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BI3" t="n">
         <v>2.4</v>
@@ -1282,31 +1282,31 @@
         <v>11</v>
       </c>
       <c r="BK3" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BN3" t="n">
         <v>7</v>
       </c>
       <c r="BO3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BP3" t="n">
         <v>38</v>
       </c>
       <c r="BQ3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BR3" t="n">
         <v>60</v>
       </c>
       <c r="BS3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BT3" t="n">
         <v>4.9</v>
@@ -1318,23 +1318,23 @@
         <v>19</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX3" t="n">
         <v>40</v>
       </c>
       <c r="BY3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ3" t="n">
         <v>44</v>
       </c>
       <c r="CA3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="G4" t="n">
         <v>2.44</v>
       </c>
       <c r="H4" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J4" t="n">
         <v>3.25</v>
@@ -1389,25 +1389,25 @@
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
         <v>1.41</v>
       </c>
       <c r="P4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q4" t="n">
         <v>2.18</v>
       </c>
       <c r="R4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U4" t="n">
         <v>2</v>
@@ -1419,19 +1419,19 @@
         <v>1.69</v>
       </c>
       <c r="X4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA4" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC4" t="n">
         <v>7.6</v>
@@ -1443,7 +1443,7 @@
         <v>55</v>
       </c>
       <c r="AF4" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG4" t="n">
         <v>11.5</v>
@@ -1458,7 +1458,7 @@
         <v>38</v>
       </c>
       <c r="AK4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL4" t="n">
         <v>55</v>
@@ -1467,10 +1467,10 @@
         <v>140</v>
       </c>
       <c r="AN4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AO4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP4" t="n">
         <v>10</v>
@@ -1482,22 +1482,22 @@
         <v>21</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT4" t="n">
         <v>7.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV4" t="n">
         <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY4" t="n">
         <v>10</v>
@@ -1512,16 +1512,16 @@
         <v>6.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="BD4" t="n">
         <v>7.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BG4" t="n">
         <v>7.2</v>
@@ -1530,19 +1530,19 @@
         <v>3.1</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN4" t="n">
         <v>5.1</v>
@@ -1551,44 +1551,44 @@
         <v>4.5</v>
       </c>
       <c r="BP4" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BR4" t="n">
         <v>36</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BV4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW4" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BX4" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BY4" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BZ4" t="n">
         <v>34</v>
       </c>
       <c r="CA4" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="G5" t="n">
         <v>2.16</v>
       </c>
       <c r="H5" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I5" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J5" t="n">
         <v>3.65</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,16 +1643,16 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P5" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R5" t="n">
         <v>1.54</v>
@@ -1664,10 +1664,10 @@
         <v>1.58</v>
       </c>
       <c r="U5" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
         <v>1.86</v>
@@ -1676,7 +1676,7 @@
         <v>24</v>
       </c>
       <c r="Y5" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Z5" t="n">
         <v>32</v>
@@ -1688,22 +1688,22 @@
         <v>13</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD5" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE5" t="n">
         <v>40</v>
       </c>
       <c r="AF5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG5" t="n">
         <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI5" t="n">
         <v>44</v>
@@ -1724,125 +1724,125 @@
         <v>11.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AP5" t="n">
         <v>18</v>
       </c>
       <c r="AQ5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT5" t="n">
         <v>11</v>
       </c>
       <c r="AU5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV5" t="n">
         <v>14.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AX5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BB5" t="n">
         <v>18.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG5" t="n">
-        <v>17.5</v>
+        <v>8</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="BJ5" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.88</v>
+        <v>6.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="BN5" t="n">
         <v>6.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BP5" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BQ5" t="n">
-        <v>2.06</v>
+        <v>9.6</v>
       </c>
       <c r="BR5" t="n">
         <v>30</v>
       </c>
       <c r="BS5" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="BT5" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BV5" t="n">
         <v>32</v>
       </c>
       <c r="BW5" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="BX5" t="n">
         <v>42</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="BZ5" t="n">
         <v>23</v>
       </c>
       <c r="CA5" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G6" t="n">
         <v>2.54</v>
@@ -1888,7 +1888,7 @@
         <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="L6" t="n">
         <v>1.48</v>
@@ -1897,22 +1897,22 @@
         <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="O6" t="n">
         <v>1.5</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="Q6" t="n">
         <v>2.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
         <v>2.04</v>
@@ -1927,25 +1927,25 @@
         <v>1.65</v>
       </c>
       <c r="X6" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA6" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC6" t="n">
         <v>7.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE6" t="n">
         <v>65</v>
@@ -1960,52 +1960,52 @@
         <v>26</v>
       </c>
       <c r="AI6" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK6" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AL6" t="n">
         <v>70</v>
       </c>
       <c r="AM6" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO6" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AP6" t="n">
         <v>8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="AS6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU6" t="n">
         <v>6.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AX6" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AY6" t="n">
         <v>10.5</v>
@@ -2014,25 +2014,25 @@
         <v>19</v>
       </c>
       <c r="BA6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE6" t="n">
         <v>6.4</v>
       </c>
-      <c r="BC6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BF6" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BH6" t="n">
         <v>2.8</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G7" t="n">
         <v>2.22</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -2384,16 +2384,16 @@
         <v>2.28</v>
       </c>
       <c r="G8" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J8" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="K8" t="n">
         <v>3.25</v>
@@ -2408,31 +2408,31 @@
         <v>2.56</v>
       </c>
       <c r="O8" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P8" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="R8" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
         <v>5.3</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V8" t="n">
         <v>1.33</v>
       </c>
       <c r="W8" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="X8" t="n">
         <v>8.800000000000001</v>
@@ -2441,7 +2441,7 @@
         <v>11</v>
       </c>
       <c r="Z8" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AA8" t="n">
         <v>110</v>
@@ -2453,55 +2453,55 @@
         <v>7.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE8" t="n">
         <v>75</v>
       </c>
       <c r="AF8" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AJ8" t="n">
         <v>42</v>
       </c>
       <c r="AK8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL8" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AM8" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AN8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AO8" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AP8" t="n">
         <v>7.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR8" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AU8" t="n">
         <v>6.2</v>
@@ -2510,10 +2510,10 @@
         <v>12.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AX8" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AY8" t="n">
         <v>9</v>
@@ -2522,43 +2522,43 @@
         <v>19.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB8" t="n">
-        <v>25</v>
+        <v>7.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF8" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK8" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BN8" t="n">
         <v>5.1</v>
@@ -2570,41 +2570,41 @@
         <v>21</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BR8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BS8" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU8" t="n">
         <v>5.8</v>
       </c>
       <c r="BV8" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BX8" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="BY8" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BZ8" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -2635,230 +2635,230 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G9" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="I9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="K9" t="n">
         <v>3.45</v>
       </c>
       <c r="L9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="P9" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="R9" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U9" t="n">
-        <v>1.46</v>
+        <v>1.92</v>
       </c>
       <c r="V9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.04</v>
+        <v>15.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>1.85</v>
       </c>
       <c r="G10" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="H10" t="n">
         <v>4.7</v>
@@ -2901,70 +2901,70 @@
         <v>5.3</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K10" t="n">
         <v>3.75</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="O10" t="n">
         <v>1.36</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
         <v>2.08</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="T10" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="V10" t="n">
         <v>1.23</v>
       </c>
       <c r="W10" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X10" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z10" t="n">
         <v>38</v>
       </c>
       <c r="AA10" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE10" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF10" t="n">
         <v>11.5</v>
@@ -2973,146 +2973,146 @@
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AJ10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK10" t="n">
         <v>23</v>
       </c>
-      <c r="AK10" t="n">
-        <v>24</v>
-      </c>
       <c r="AL10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM10" t="n">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="AN10" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AO10" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP10" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AR10" t="n">
         <v>30</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW10" t="n">
         <v>55</v>
       </c>
       <c r="AX10" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY10" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
         <v>17.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BB10" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="BF10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BG10" t="n">
         <v>55</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.85</v>
+        <v>2.68</v>
       </c>
       <c r="BJ10" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.65</v>
+        <v>7.6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.85</v>
+        <v>12</v>
       </c>
       <c r="BN10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU10" t="n">
         <v>5.9</v>
       </c>
-      <c r="BO10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>44</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>11</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>1.59</v>
-      </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.81</v>
+        <v>10</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.81</v>
+        <v>10.5</v>
       </c>
       <c r="BZ10" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.77</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -3146,13 +3146,13 @@
         <v>1.34</v>
       </c>
       <c r="G11" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H11" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J11" t="n">
         <v>5.7</v>
@@ -3173,19 +3173,19 @@
         <v>1.23</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q11" t="n">
         <v>1.64</v>
       </c>
       <c r="R11" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S11" t="n">
         <v>2.66</v>
       </c>
       <c r="T11" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U11" t="n">
         <v>1.81</v>
@@ -3194,7 +3194,7 @@
         <v>1.09</v>
       </c>
       <c r="W11" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="X11" t="n">
         <v>21</v>
@@ -3203,22 +3203,22 @@
         <v>34</v>
       </c>
       <c r="Z11" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AA11" t="n">
-        <v>390</v>
+        <v>430</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC11" t="n">
         <v>14.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AE11" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AF11" t="n">
         <v>8.800000000000001</v>
@@ -3230,7 +3230,7 @@
         <v>32</v>
       </c>
       <c r="AI11" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AJ11" t="n">
         <v>11</v>
@@ -3239,22 +3239,22 @@
         <v>15</v>
       </c>
       <c r="AL11" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM11" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN11" t="n">
         <v>5.3</v>
       </c>
       <c r="AO11" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="AP11" t="n">
         <v>18.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.800000000000001</v>
+        <v>24</v>
       </c>
       <c r="AR11" t="n">
         <v>10.5</v>
@@ -3263,25 +3263,25 @@
         <v>11.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW11" t="n">
         <v>11</v>
       </c>
       <c r="AX11" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="AY11" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>27</v>
+        <v>8.6</v>
       </c>
       <c r="BA11" t="n">
         <v>11</v>
@@ -3290,83 +3290,83 @@
         <v>9.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="BD11" t="n">
-        <v>32</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE11" t="n">
         <v>11</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.24</v>
+        <v>3.35</v>
       </c>
       <c r="BJ11" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.96</v>
+        <v>7</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>2.24</v>
+        <v>14</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="BO11" t="n">
-        <v>2.84</v>
+        <v>3.4</v>
       </c>
       <c r="BP11" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BR11" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="BS11" t="n">
-        <v>2.08</v>
+        <v>9.4</v>
       </c>
       <c r="BT11" t="n">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="BU11" t="n">
-        <v>2</v>
+        <v>10.5</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>2.24</v>
+        <v>13.5</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.18</v>
+        <v>13</v>
       </c>
       <c r="BZ11" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.96</v>
+        <v>6.8</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G2" t="n">
         <v>1.97</v>
@@ -923,7 +923,7 @@
         <v>120</v>
       </c>
       <c r="AB2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC2" t="n">
         <v>8.6</v>
@@ -950,7 +950,7 @@
         <v>26</v>
       </c>
       <c r="AK2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL2" t="n">
         <v>44</v>
@@ -971,10 +971,10 @@
         <v>13.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AT2" t="n">
         <v>8</v>
@@ -986,7 +986,7 @@
         <v>16</v>
       </c>
       <c r="AW2" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AX2" t="n">
         <v>10.5</v>
@@ -998,25 +998,25 @@
         <v>17</v>
       </c>
       <c r="BA2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="BC2" t="n">
         <v>18</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF2" t="n">
         <v>12</v>
       </c>
       <c r="BG2" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BH2" t="n">
         <v>3.35</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN2" t="n">
         <v>4.6</v>
@@ -1043,10 +1043,10 @@
         <v>4.1</v>
       </c>
       <c r="BP2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BR2" t="n">
         <v>29</v>
@@ -1070,17 +1070,17 @@
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ2" t="n">
         <v>25</v>
       </c>
       <c r="CA2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>2.32</v>
       </c>
       <c r="J3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
         <v>3.3</v>
@@ -1132,7 +1132,7 @@
         <v>1.45</v>
       </c>
       <c r="M3" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N3" t="n">
         <v>2.8</v>
@@ -1147,16 +1147,16 @@
         <v>2.56</v>
       </c>
       <c r="R3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="T3" t="n">
         <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V3" t="n">
         <v>1.75</v>
@@ -1228,7 +1228,7 @@
         <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AT3" t="n">
         <v>9.6</v>
@@ -1255,7 +1255,7 @@
         <v>44</v>
       </c>
       <c r="BB3" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BC3" t="n">
         <v>42</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G4" t="n">
         <v>2.44</v>
@@ -1395,13 +1395,13 @@
         <v>1.41</v>
       </c>
       <c r="P4" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
         <v>2.18</v>
       </c>
       <c r="R4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S4" t="n">
         <v>4.1</v>
@@ -1413,7 +1413,7 @@
         <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W4" t="n">
         <v>1.69</v>
@@ -1518,7 +1518,7 @@
         <v>7.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF4" t="n">
         <v>19</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H5" t="n">
         <v>3.65</v>
@@ -1634,10 +1634,10 @@
         <v>3.65</v>
       </c>
       <c r="K5" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
@@ -1646,34 +1646,34 @@
         <v>4.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P5" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="Q5" t="n">
         <v>1.67</v>
       </c>
       <c r="R5" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S5" t="n">
         <v>2.62</v>
       </c>
       <c r="T5" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U5" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V5" t="n">
         <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y5" t="n">
         <v>20</v>
@@ -1730,13 +1730,13 @@
         <v>18</v>
       </c>
       <c r="AQ5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT5" t="n">
         <v>11</v>
@@ -1760,7 +1760,7 @@
         <v>12.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB5" t="n">
         <v>18.5</v>
@@ -1769,10 +1769,10 @@
         <v>17</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF5" t="n">
         <v>9.800000000000001</v>
@@ -1781,68 +1781,68 @@
         <v>8</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.16</v>
+        <v>3.4</v>
       </c>
       <c r="BJ5" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>2.1</v>
+        <v>12.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="BO5" t="n">
         <v>4.2</v>
       </c>
       <c r="BP5" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR5" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="BS5" t="n">
-        <v>2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BV5" t="n">
+        <v>25</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BX5" t="n">
         <v>32</v>
       </c>
-      <c r="BW5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>42</v>
-      </c>
       <c r="BY5" t="n">
-        <v>2.04</v>
+        <v>10</v>
       </c>
       <c r="BZ5" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.97</v>
+        <v>8</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G6" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H6" t="n">
         <v>3.45</v>
       </c>
       <c r="I6" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="J6" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="K6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L6" t="n">
         <v>1.48</v>
@@ -1897,7 +1897,7 @@
         <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O6" t="n">
         <v>1.5</v>
@@ -1918,13 +1918,13 @@
         <v>2.04</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V6" t="n">
         <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X6" t="n">
         <v>10.5</v>
@@ -2044,59 +2044,59 @@
         <v>11.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO6" t="n">
         <v>4.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT6" t="n">
         <v>6.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G7" t="n">
         <v>2.22</v>
       </c>
       <c r="H7" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I7" t="n">
         <v>3.85</v>
       </c>
       <c r="J7" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
         <v>3.55</v>
@@ -2157,7 +2157,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
         <v>1.97</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>2.28</v>
       </c>
       <c r="G8" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H8" t="n">
         <v>3.65</v>
@@ -2402,22 +2402,22 @@
         <v>1.55</v>
       </c>
       <c r="M8" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N8" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P8" t="n">
         <v>1.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S8" t="n">
         <v>5.3</v>
@@ -2432,7 +2432,7 @@
         <v>1.33</v>
       </c>
       <c r="W8" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X8" t="n">
         <v>8.800000000000001</v>
@@ -2459,13 +2459,13 @@
         <v>75</v>
       </c>
       <c r="AF8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG8" t="n">
         <v>13</v>
       </c>
       <c r="AH8" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AI8" t="n">
         <v>100</v>
@@ -2480,7 +2480,7 @@
         <v>75</v>
       </c>
       <c r="AM8" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN8" t="n">
         <v>42</v>
@@ -2498,7 +2498,7 @@
         <v>18.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AT8" t="n">
         <v>5.5</v>
@@ -2510,7 +2510,7 @@
         <v>12.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AX8" t="n">
         <v>10</v>
@@ -2522,25 +2522,25 @@
         <v>19.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH8" t="n">
         <v>2.8</v>
@@ -2549,7 +2549,7 @@
         <v>2.48</v>
       </c>
       <c r="BJ8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK8" t="n">
         <v>8.4</v>
@@ -2558,7 +2558,7 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN8" t="n">
         <v>5.1</v>
@@ -2576,7 +2576,7 @@
         <v>55</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT8" t="n">
         <v>7.2</v>
@@ -2588,23 +2588,23 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX8" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>2.22</v>
       </c>
       <c r="G9" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H9" t="n">
         <v>3.65</v>
@@ -2653,7 +2653,7 @@
         <v>3.45</v>
       </c>
       <c r="L9" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
@@ -2677,7 +2677,7 @@
         <v>4.4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U9" t="n">
         <v>1.92</v>
@@ -2686,7 +2686,7 @@
         <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="X9" t="n">
         <v>13</v>
@@ -2713,7 +2713,7 @@
         <v>75</v>
       </c>
       <c r="AF9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG9" t="n">
         <v>11.5</v>
@@ -2749,10 +2749,10 @@
         <v>10</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT9" t="n">
         <v>7.2</v>
@@ -2764,7 +2764,7 @@
         <v>14</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX9" t="n">
         <v>12</v>
@@ -2773,28 +2773,28 @@
         <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC9" t="n">
         <v>6.6</v>
       </c>
-      <c r="BC9" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BD9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF9" t="n">
         <v>18.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH9" t="n">
         <v>2.98</v>
@@ -2839,7 +2839,7 @@
         <v>6</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW9" t="n">
         <v>11.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="G10" t="n">
         <v>1.98</v>
       </c>
       <c r="H10" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="I10" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L10" t="n">
         <v>1.44</v>
@@ -2913,31 +2913,31 @@
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T10" t="n">
         <v>1.91</v>
       </c>
       <c r="U10" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V10" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
         <v>2.02</v>
@@ -2946,28 +2946,28 @@
         <v>12.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z10" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA10" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE10" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AF10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG10" t="n">
         <v>11</v>
@@ -2976,10 +2976,10 @@
         <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK10" t="n">
         <v>23</v>
@@ -2991,128 +2991,128 @@
         <v>130</v>
       </c>
       <c r="AN10" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP10" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR10" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AS10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU10" t="n">
         <v>7</v>
       </c>
-      <c r="AU10" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AV10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW10" t="n">
         <v>55</v>
       </c>
       <c r="AX10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY10" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BB10" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BC10" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD10" t="n">
         <v>36</v>
       </c>
       <c r="BE10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF10" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="BH10" t="n">
         <v>3.25</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="BJ10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR10" t="n">
         <v>32</v>
       </c>
       <c r="BS10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT10" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="BV10" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX10" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CA10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>1.34</v>
       </c>
       <c r="G11" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H11" t="n">
         <v>9.199999999999999</v>
@@ -3164,7 +3164,7 @@
         <v>1.27</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
         <v>4.8</v>
@@ -3179,13 +3179,13 @@
         <v>1.64</v>
       </c>
       <c r="R11" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S11" t="n">
         <v>2.66</v>
       </c>
       <c r="T11" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U11" t="n">
         <v>1.81</v>
@@ -3194,10 +3194,10 @@
         <v>1.09</v>
       </c>
       <c r="W11" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="X11" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Y11" t="n">
         <v>34</v>
@@ -3206,7 +3206,7 @@
         <v>110</v>
       </c>
       <c r="AA11" t="n">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="AB11" t="n">
         <v>9.4</v>
@@ -3239,7 +3239,7 @@
         <v>15</v>
       </c>
       <c r="AL11" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AM11" t="n">
         <v>200</v>
@@ -3248,70 +3248,70 @@
         <v>5.3</v>
       </c>
       <c r="AO11" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AP11" t="n">
         <v>18.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="AR11" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AT11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU11" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AV11" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX11" t="n">
         <v>7.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ11" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BA11" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB11" t="n">
         <v>9.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BD11" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BH11" t="n">
         <v>4.2</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK11" t="n">
         <v>7</v>
@@ -3320,10 +3320,10 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BN11" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BO11" t="n">
         <v>3.4</v>
@@ -3338,7 +3338,7 @@
         <v>24</v>
       </c>
       <c r="BS11" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT11" t="n">
         <v>14</v>
@@ -3350,23 +3350,23 @@
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BZ11" t="n">
         <v>12</v>
       </c>
       <c r="CA11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="G2" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="H2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I2" t="n">
         <v>4.4</v>
       </c>
-      <c r="I2" t="n">
-        <v>4.7</v>
-      </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N2" t="n">
         <v>3.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P2" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T2" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="U2" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V2" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W2" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="X2" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA2" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AE2" t="n">
-        <v>70</v>
+        <v>270</v>
       </c>
       <c r="AF2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG2" t="n">
         <v>10.5</v>
       </c>
       <c r="AH2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>23</v>
       </c>
-      <c r="AI2" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>26</v>
-      </c>
       <c r="AK2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL2" t="n">
         <v>44</v>
       </c>
       <c r="AM2" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="AS2" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="AT2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU2" t="n">
         <v>7.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.6</v>
+        <v>28</v>
       </c>
       <c r="AX2" t="n">
         <v>10.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="BB2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BC2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BD2" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="BE2" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="BF2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI2" t="n">
         <v>3.05</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BQ2" t="n">
         <v>9.6</v>
       </c>
       <c r="BR2" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT2" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BU2" t="n">
         <v>5.8</v>
       </c>
       <c r="BV2" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BZ2" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="CA2" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G3" t="n">
         <v>3.95</v>
@@ -1120,16 +1120,16 @@
         <v>2.24</v>
       </c>
       <c r="I3" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="M3" t="n">
         <v>1.12</v>
@@ -1141,10 +1141,10 @@
         <v>1.52</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="R3" t="n">
         <v>1.22</v>
@@ -1162,13 +1162,13 @@
         <v>1.75</v>
       </c>
       <c r="W3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Z3" t="n">
         <v>12.5</v>
@@ -1192,7 +1192,7 @@
         <v>26</v>
       </c>
       <c r="AG3" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH3" t="n">
         <v>23</v>
@@ -1204,7 +1204,7 @@
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>65</v>
+        <v>460</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1252,13 +1252,13 @@
         <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="BB3" t="n">
         <v>34</v>
       </c>
       <c r="BC3" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="BD3" t="n">
         <v>36</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -1368,124 +1368,124 @@
         <v>2.3</v>
       </c>
       <c r="G4" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I4" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O4" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="P4" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V4" t="n">
         <v>1.38</v>
       </c>
       <c r="W4" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="X4" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Y4" t="n">
         <v>12</v>
       </c>
       <c r="Z4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AA4" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AC4" t="n">
         <v>7.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AG4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>70</v>
+        <v>690</v>
       </c>
       <c r="AJ4" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK4" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM4" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AO4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AP4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU4" t="n">
         <v>6.8</v>
@@ -1494,46 +1494,46 @@
         <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.2</v>
+        <v>24</v>
       </c>
       <c r="AX4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>16.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.8</v>
+        <v>19.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.6</v>
+        <v>18</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.2</v>
+        <v>26</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.8</v>
+        <v>40</v>
       </c>
       <c r="BF4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.2</v>
+        <v>26</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="BJ4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK4" t="n">
         <v>6.2</v>
@@ -1542,53 +1542,53 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN4" t="n">
         <v>5.1</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BP4" t="n">
         <v>18.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BR4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT4" t="n">
         <v>6.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BV4" t="n">
         <v>30</v>
       </c>
       <c r="BW4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY4" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CA4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>2.08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="H5" t="n">
         <v>3.65</v>
@@ -1631,10 +1631,10 @@
         <v>3.9</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L5" t="n">
         <v>1.27</v>
@@ -1652,7 +1652,7 @@
         <v>2.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="R5" t="n">
         <v>1.55</v>
@@ -1661,16 +1661,16 @@
         <v>2.62</v>
       </c>
       <c r="T5" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U5" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="V5" t="n">
         <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="X5" t="n">
         <v>23</v>
@@ -1679,25 +1679,25 @@
         <v>20</v>
       </c>
       <c r="Z5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA5" t="n">
         <v>65</v>
       </c>
       <c r="AB5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AC5" t="n">
         <v>9</v>
       </c>
       <c r="AD5" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AF5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AG5" t="n">
         <v>11</v>
@@ -1709,7 +1709,7 @@
         <v>44</v>
       </c>
       <c r="AJ5" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AK5" t="n">
         <v>20</v>
@@ -1718,25 +1718,25 @@
         <v>29</v>
       </c>
       <c r="AM5" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AN5" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AO5" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AP5" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>17</v>
       </c>
       <c r="AR5" t="n">
-        <v>8.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT5" t="n">
         <v>11</v>
@@ -1748,49 +1748,49 @@
         <v>14.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.6</v>
+        <v>32</v>
       </c>
       <c r="AX5" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY5" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="BB5" t="n">
         <v>18.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BH5" t="n">
         <v>4.2</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BJ5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1820,7 +1820,7 @@
         <v>7</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BV5" t="n">
         <v>25</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G6" t="n">
         <v>2.56</v>
@@ -1882,43 +1882,43 @@
         <v>3.45</v>
       </c>
       <c r="I6" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="K6" t="n">
         <v>3.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="M6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="O6" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="P6" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U6" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="V6" t="n">
         <v>1.35</v>
@@ -1945,7 +1945,7 @@
         <v>7.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE6" t="n">
         <v>65</v>
@@ -1957,7 +1957,7 @@
         <v>14</v>
       </c>
       <c r="AH6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI6" t="n">
         <v>85</v>
@@ -1966,19 +1966,19 @@
         <v>40</v>
       </c>
       <c r="AK6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL6" t="n">
         <v>70</v>
       </c>
       <c r="AM6" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN6" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AO6" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
         <v>8</v>
@@ -1987,7 +1987,7 @@
         <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AS6" t="n">
         <v>6</v>
@@ -2002,7 +2002,7 @@
         <v>13.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AX6" t="n">
         <v>12.5</v>
@@ -2014,89 +2014,89 @@
         <v>19</v>
       </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BE6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BG6" t="n">
         <v>6.4</v>
       </c>
-      <c r="BF6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>6</v>
-      </c>
       <c r="BH6" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="BJ6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO6" t="n">
         <v>4.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -2136,13 +2136,13 @@
         <v>3.75</v>
       </c>
       <c r="I7" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -2396,46 +2396,46 @@
         <v>3.1</v>
       </c>
       <c r="K8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L8" t="n">
         <v>1.55</v>
       </c>
       <c r="M8" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P8" t="n">
         <v>1.54</v>
       </c>
-      <c r="P8" t="n">
-        <v>1.56</v>
-      </c>
       <c r="Q8" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R8" t="n">
         <v>1.19</v>
       </c>
       <c r="S8" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="T8" t="n">
         <v>2.08</v>
       </c>
       <c r="U8" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="V8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W8" t="n">
         <v>1.69</v>
       </c>
       <c r="X8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Y8" t="n">
         <v>11</v>
@@ -2447,10 +2447,10 @@
         <v>110</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD8" t="n">
         <v>18</v>
@@ -2459,10 +2459,10 @@
         <v>75</v>
       </c>
       <c r="AF8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
         <v>28</v>
@@ -2489,34 +2489,34 @@
         <v>100</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR8" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AS8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.6</v>
+        <v>44</v>
       </c>
       <c r="AX8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY8" t="n">
         <v>10</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9</v>
       </c>
       <c r="AZ8" t="n">
         <v>19.5</v>
@@ -2531,13 +2531,13 @@
         <v>7.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.6</v>
+        <v>42</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="BG8" t="n">
         <v>9</v>
@@ -2549,22 +2549,22 @@
         <v>2.48</v>
       </c>
       <c r="BJ8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK8" t="n">
-        <v>8.4</v>
+        <v>5.7</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN8" t="n">
         <v>5.1</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP8" t="n">
         <v>21</v>
@@ -2576,35 +2576,35 @@
         <v>55</v>
       </c>
       <c r="BS8" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT8" t="n">
         <v>7.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
         <v>1.44</v>
       </c>
       <c r="P9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q9" t="n">
         <v>2.3</v>
@@ -2710,7 +2710,7 @@
         <v>16.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AF9" t="n">
         <v>13.5</v>
@@ -2728,7 +2728,7 @@
         <v>42</v>
       </c>
       <c r="AK9" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AL9" t="n">
         <v>70</v>
@@ -2749,10 +2749,10 @@
         <v>10</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT9" t="n">
         <v>7.2</v>
@@ -2764,7 +2764,7 @@
         <v>14</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX9" t="n">
         <v>12</v>
@@ -2773,28 +2773,28 @@
         <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF9" t="n">
         <v>18.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH9" t="n">
         <v>2.98</v>
@@ -2806,7 +2806,7 @@
         <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2818,7 +2818,7 @@
         <v>4.9</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
@@ -2836,10 +2836,10 @@
         <v>7</v>
       </c>
       <c r="BU9" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BV9" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
         <v>11.5</v>
@@ -2851,14 +2851,14 @@
         <v>12.5</v>
       </c>
       <c r="BZ9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
         <v>12</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>1.92</v>
       </c>
       <c r="G10" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="H10" t="n">
         <v>4.4</v>
@@ -2907,7 +2907,7 @@
         <v>3.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="M10" t="n">
         <v>1.08</v>
@@ -2931,7 +2931,7 @@
         <v>3.85</v>
       </c>
       <c r="T10" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U10" t="n">
         <v>1.94</v>
@@ -2940,7 +2940,7 @@
         <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="X10" t="n">
         <v>12.5</v>
@@ -2991,7 +2991,7 @@
         <v>130</v>
       </c>
       <c r="AN10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO10" t="n">
         <v>95</v>
@@ -3003,10 +3003,10 @@
         <v>13</v>
       </c>
       <c r="AR10" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AS10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AT10" t="n">
         <v>7.2</v>
@@ -3018,7 +3018,7 @@
         <v>16</v>
       </c>
       <c r="AW10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
@@ -3054,7 +3054,7 @@
         <v>3.25</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
@@ -3090,7 +3090,7 @@
         <v>8</v>
       </c>
       <c r="BU10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
         <v>1.38</v>
       </c>
       <c r="H11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
         <v>12</v>
@@ -3164,7 +3164,7 @@
         <v>1.27</v>
       </c>
       <c r="M11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N11" t="n">
         <v>4.8</v>
@@ -3173,7 +3173,7 @@
         <v>1.23</v>
       </c>
       <c r="P11" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
         <v>1.64</v>
@@ -3188,7 +3188,7 @@
         <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V11" t="n">
         <v>1.09</v>
@@ -3200,13 +3200,13 @@
         <v>25</v>
       </c>
       <c r="Y11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z11" t="n">
         <v>110</v>
       </c>
       <c r="AA11" t="n">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="AB11" t="n">
         <v>9.4</v>
@@ -3218,7 +3218,7 @@
         <v>40</v>
       </c>
       <c r="AE11" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AF11" t="n">
         <v>8.800000000000001</v>
@@ -3239,7 +3239,7 @@
         <v>15</v>
       </c>
       <c r="AL11" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM11" t="n">
         <v>200</v>
@@ -3248,19 +3248,19 @@
         <v>5.3</v>
       </c>
       <c r="AO11" t="n">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="AP11" t="n">
         <v>18.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT11" t="n">
         <v>8.199999999999999</v>
@@ -3278,13 +3278,13 @@
         <v>7.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
         <v>8</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB11" t="n">
         <v>9.4</v>
@@ -3293,7 +3293,7 @@
         <v>11</v>
       </c>
       <c r="BD11" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE11" t="n">
         <v>10</v>
@@ -3311,7 +3311,7 @@
         <v>3.4</v>
       </c>
       <c r="BJ11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK11" t="n">
         <v>7</v>
@@ -3320,53 +3320,53 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="BP11" t="n">
         <v>7.6</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BR11" t="n">
         <v>24</v>
       </c>
       <c r="BS11" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BT11" t="n">
         <v>14</v>
       </c>
       <c r="BU11" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ11" t="n">
         <v>12</v>
       </c>
       <c r="CA11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -869,7 +869,7 @@
         <v>4.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
         <v>3.85</v>
@@ -887,7 +887,7 @@
         <v>1.35</v>
       </c>
       <c r="P2" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q2" t="n">
         <v>2.02</v>
@@ -902,7 +902,7 @@
         <v>1.9</v>
       </c>
       <c r="U2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V2" t="n">
         <v>1.29</v>
@@ -914,7 +914,7 @@
         <v>15.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Z2" t="n">
         <v>36</v>
@@ -929,10 +929,10 @@
         <v>8.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AF2" t="n">
         <v>11.5</v>
@@ -947,19 +947,19 @@
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK2" t="n">
         <v>23</v>
       </c>
       <c r="AL2" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
@@ -1004,7 +1004,7 @@
         <v>20</v>
       </c>
       <c r="BC2" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BD2" t="n">
         <v>24</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H3" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I3" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J3" t="n">
         <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L3" t="n">
         <v>1.55</v>
@@ -1144,7 +1144,7 @@
         <v>1.61</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
         <v>1.22</v>
@@ -1153,13 +1153,13 @@
         <v>5.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
         <v>1.81</v>
       </c>
       <c r="V3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W3" t="n">
         <v>1.34</v>
@@ -1204,7 +1204,7 @@
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>460</v>
+        <v>420</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G4" t="n">
         <v>2.42</v>
       </c>
       <c r="H4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I4" t="n">
         <v>3.6</v>
@@ -1380,22 +1380,22 @@
         <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O4" t="n">
         <v>1.39</v>
       </c>
       <c r="P4" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q4" t="n">
         <v>2.16</v>
@@ -1407,7 +1407,7 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="U4" t="n">
         <v>2.04</v>
@@ -1422,7 +1422,7 @@
         <v>13.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z4" t="n">
         <v>25</v>
@@ -1431,7 +1431,7 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC4" t="n">
         <v>7.6</v>
@@ -1443,7 +1443,7 @@
         <v>50</v>
       </c>
       <c r="AF4" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AG4" t="n">
         <v>12</v>
@@ -1467,13 +1467,13 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO4" t="n">
         <v>50</v>
       </c>
       <c r="AP4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ4" t="n">
         <v>10.5</v>
@@ -1485,7 +1485,7 @@
         <v>30</v>
       </c>
       <c r="AT4" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU4" t="n">
         <v>6.8</v>
@@ -1530,7 +1530,7 @@
         <v>3.15</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="BJ4" t="n">
         <v>10</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
         <v>3.65</v>
       </c>
       <c r="I5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
         <v>3.55</v>
@@ -1646,13 +1646,13 @@
         <v>4.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P5" t="n">
         <v>2.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R5" t="n">
         <v>1.55</v>
@@ -1667,10 +1667,10 @@
         <v>2.62</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X5" t="n">
         <v>23</v>
@@ -1820,7 +1820,7 @@
         <v>7</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV5" t="n">
         <v>25</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -1876,13 +1876,13 @@
         <v>2.36</v>
       </c>
       <c r="G6" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="H6" t="n">
         <v>3.45</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J6" t="n">
         <v>3.15</v>
@@ -1900,16 +1900,16 @@
         <v>2.76</v>
       </c>
       <c r="O6" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R6" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1918,25 +1918,25 @@
         <v>2.02</v>
       </c>
       <c r="U6" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V6" t="n">
         <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X6" t="n">
         <v>10.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
         <v>28</v>
       </c>
       <c r="AA6" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB6" t="n">
         <v>8.800000000000001</v>
@@ -1969,7 +1969,7 @@
         <v>38</v>
       </c>
       <c r="AL6" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM6" t="n">
         <v>190</v>
@@ -1987,10 +1987,10 @@
         <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="AS6" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="AT6" t="n">
         <v>6.8</v>
@@ -2002,7 +2002,7 @@
         <v>13.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="AX6" t="n">
         <v>12.5</v>
@@ -2014,25 +2014,25 @@
         <v>19</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH6" t="n">
         <v>2.82</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G7" t="n">
         <v>2.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.22</v>
       </c>
       <c r="H7" t="n">
         <v>3.75</v>
@@ -2139,10 +2139,10 @@
         <v>3.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2157,11 +2157,11 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1.97</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -2381,46 +2381,46 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G8" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="H8" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I8" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K8" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M8" t="n">
         <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O8" t="n">
         <v>1.52</v>
       </c>
       <c r="P8" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="R8" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S8" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T8" t="n">
         <v>2.08</v>
@@ -2429,10 +2429,10 @@
         <v>1.8</v>
       </c>
       <c r="V8" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X8" t="n">
         <v>9.4</v>
@@ -2453,7 +2453,7 @@
         <v>7.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE8" t="n">
         <v>75</v>
@@ -2489,7 +2489,7 @@
         <v>100</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ8" t="n">
         <v>9</v>
@@ -2498,10 +2498,10 @@
         <v>21</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU8" t="n">
         <v>6</v>
@@ -2522,25 +2522,25 @@
         <v>19.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD8" t="n">
         <v>42</v>
       </c>
       <c r="BE8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG8" t="n">
         <v>9.6</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>24</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>9</v>
       </c>
       <c r="BH8" t="n">
         <v>2.8</v>
@@ -2564,7 +2564,7 @@
         <v>5.1</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP8" t="n">
         <v>21</v>
@@ -2582,16 +2582,16 @@
         <v>7.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW8" t="n">
         <v>8.6</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY8" t="n">
         <v>9.4</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
         <v>3.15</v>
       </c>
       <c r="K9" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L9" t="n">
         <v>1.5</v>
@@ -2686,13 +2686,13 @@
         <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X9" t="n">
         <v>13</v>
       </c>
       <c r="Y9" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Z9" t="n">
         <v>36</v>
@@ -2716,7 +2716,7 @@
         <v>13.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH9" t="n">
         <v>21</v>
@@ -2728,16 +2728,16 @@
         <v>42</v>
       </c>
       <c r="AK9" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AL9" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AM9" t="n">
         <v>170</v>
       </c>
       <c r="AN9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO9" t="n">
         <v>95</v>
@@ -2746,13 +2746,13 @@
         <v>9.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS9" t="n">
         <v>7.2</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>9</v>
       </c>
       <c r="AT9" t="n">
         <v>7.2</v>
@@ -2764,7 +2764,7 @@
         <v>14</v>
       </c>
       <c r="AW9" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX9" t="n">
         <v>12</v>
@@ -2773,34 +2773,34 @@
         <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6.8</v>
+        <v>17.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.6</v>
+        <v>24</v>
       </c>
       <c r="BC9" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE9" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>9.4</v>
       </c>
       <c r="BF9" t="n">
         <v>18.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="BH9" t="n">
         <v>2.98</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BJ9" t="n">
         <v>10.5</v>
@@ -2812,19 +2812,19 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
@@ -2833,16 +2833,16 @@
         <v>11.5</v>
       </c>
       <c r="BT9" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
@@ -2854,11 +2854,11 @@
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -2898,16 +2898,16 @@
         <v>4.4</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J10" t="n">
         <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L10" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
         <v>1.08</v>
@@ -2931,10 +2931,10 @@
         <v>3.85</v>
       </c>
       <c r="T10" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U10" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V10" t="n">
         <v>1.25</v>
@@ -3051,22 +3051,22 @@
         <v>38</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN10" t="n">
         <v>4.6</v>
@@ -3078,41 +3078,41 @@
         <v>14.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR10" t="n">
         <v>32</v>
       </c>
       <c r="BS10" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT10" t="n">
         <v>8</v>
       </c>
       <c r="BU10" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ10" t="n">
         <v>29</v>
       </c>
       <c r="CA10" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="G11" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J11" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K11" t="n">
         <v>6.4</v>
@@ -3164,34 +3164,34 @@
         <v>1.27</v>
       </c>
       <c r="M11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O11" t="n">
         <v>1.23</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R11" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S11" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T11" t="n">
         <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="V11" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W11" t="n">
         <v>3.6</v>
@@ -3200,16 +3200,16 @@
         <v>25</v>
       </c>
       <c r="Y11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z11" t="n">
         <v>110</v>
       </c>
       <c r="AA11" t="n">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC11" t="n">
         <v>14.5</v>
@@ -3245,7 +3245,7 @@
         <v>200</v>
       </c>
       <c r="AN11" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AO11" t="n">
         <v>240</v>
@@ -3254,34 +3254,34 @@
         <v>18.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW11" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>10</v>
       </c>
       <c r="AX11" t="n">
         <v>7.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BA11" t="n">
         <v>10</v>
@@ -3290,25 +3290,25 @@
         <v>9.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BD11" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH11" t="n">
         <v>4.2</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="BJ11" t="n">
         <v>12.5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB11"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="G2" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="I2" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="J2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K2" t="n">
         <v>3.7</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.85</v>
       </c>
       <c r="L2" t="n">
         <v>1.43</v>
@@ -881,76 +881,76 @@
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O2" t="n">
         <v>1.35</v>
       </c>
       <c r="P2" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="U2" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V2" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="X2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD2" t="n">
         <v>15.5</v>
       </c>
-      <c r="Y2" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z2" t="n">
+      <c r="AE2" t="n">
+        <v>190</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>740</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK2" t="n">
         <v>36</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>280</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>23</v>
       </c>
       <c r="AL2" t="n">
         <v>100</v>
@@ -962,46 +962,46 @@
         <v>17</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV2" t="n">
         <v>13</v>
       </c>
-      <c r="AR2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>15</v>
-      </c>
       <c r="AW2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX2" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB2" t="n">
         <v>17.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>20</v>
       </c>
       <c r="BC2" t="n">
         <v>16.5</v>
@@ -1010,13 +1010,13 @@
         <v>24</v>
       </c>
       <c r="BE2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BF2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BG2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BH2" t="n">
         <v>3.3</v>
@@ -1025,7 +1025,7 @@
         <v>3.05</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK2" t="n">
         <v>6.4</v>
@@ -1034,16 +1034,16 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO2" t="n">
         <v>4.2</v>
       </c>
       <c r="BP2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ2" t="n">
         <v>9.6</v>
@@ -1052,16 +1052,16 @@
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW2" t="n">
         <v>12</v>
@@ -1070,17 +1070,17 @@
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ2" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="CA2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
         <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
         <v>1.55</v>
@@ -1138,13 +1138,13 @@
         <v>2.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P3" t="n">
         <v>1.61</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="R3" t="n">
         <v>1.22</v>
@@ -1153,10 +1153,10 @@
         <v>5.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V3" t="n">
         <v>1.76</v>
@@ -1177,10 +1177,10 @@
         <v>32</v>
       </c>
       <c r="AB3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD3" t="n">
         <v>12</v>
@@ -1204,7 +1204,7 @@
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1237,7 +1237,7 @@
         <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW3" t="n">
         <v>19.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -1368,10 +1368,10 @@
         <v>2.32</v>
       </c>
       <c r="G4" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I4" t="n">
         <v>3.6</v>
@@ -1395,7 +1395,7 @@
         <v>1.39</v>
       </c>
       <c r="P4" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q4" t="n">
         <v>2.16</v>
@@ -1407,13 +1407,13 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U4" t="n">
         <v>2.04</v>
       </c>
       <c r="V4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W4" t="n">
         <v>1.71</v>
@@ -1431,7 +1431,7 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AC4" t="n">
         <v>7.6</v>
@@ -1446,16 +1446,16 @@
         <v>16.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH4" t="n">
         <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>690</v>
+        <v>710</v>
       </c>
       <c r="AJ4" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AK4" t="n">
         <v>30</v>
@@ -1473,7 +1473,7 @@
         <v>50</v>
       </c>
       <c r="AP4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>10.5</v>
@@ -1509,7 +1509,7 @@
         <v>30</v>
       </c>
       <c r="BB4" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC4" t="n">
         <v>18</v>
@@ -1530,7 +1530,7 @@
         <v>3.15</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="BJ4" t="n">
         <v>10</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H5" t="n">
         <v>3.65</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
         <v>3.95</v>
@@ -1646,16 +1646,16 @@
         <v>4.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P5" t="n">
         <v>2.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S5" t="n">
         <v>2.62</v>
@@ -1667,7 +1667,7 @@
         <v>2.62</v>
       </c>
       <c r="V5" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W5" t="n">
         <v>1.84</v>
@@ -1676,7 +1676,7 @@
         <v>23</v>
       </c>
       <c r="Y5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z5" t="n">
         <v>30</v>
@@ -1685,7 +1685,7 @@
         <v>65</v>
       </c>
       <c r="AB5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC5" t="n">
         <v>9</v>
@@ -1703,7 +1703,7 @@
         <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AI5" t="n">
         <v>44</v>
@@ -1736,7 +1736,7 @@
         <v>21</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT5" t="n">
         <v>11</v>
@@ -1772,13 +1772,13 @@
         <v>22</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF5" t="n">
         <v>10</v>
       </c>
       <c r="BG5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH5" t="n">
         <v>4.2</v>
@@ -1790,13 +1790,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BN5" t="n">
         <v>5.3</v>
@@ -1808,48 +1808,48 @@
         <v>14.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BR5" t="n">
         <v>24</v>
       </c>
       <c r="BS5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV5" t="n">
         <v>25</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BX5" t="n">
         <v>32</v>
       </c>
       <c r="BY5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ5" t="n">
         <v>17.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Union de Touarga</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Delfin</t>
+          <t>Jeunesse Massira</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.36</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>2.52</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>2.76</v>
+        <v>1.24</v>
       </c>
       <c r="O6" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>1.59</v>
+        <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="R6" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="T6" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.82</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Atletico MG</t>
+          <t>Olympique Dcheira</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>US Amal Tiznit</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.18</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.94</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Delfin</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="G8" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="I8" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J8" t="n">
         <v>3.15</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="M8" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="O8" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="P8" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="R8" t="n">
         <v>1.21</v>
       </c>
       <c r="S8" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="U8" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="V8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="X8" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA8" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE8" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF8" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AH8" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL8" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM8" t="n">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="AN8" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AO8" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ8" t="n">
         <v>9</v>
       </c>
       <c r="AR8" t="n">
-        <v>21</v>
+        <v>4.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="AT8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU8" t="n">
         <v>6.4</v>
       </c>
-      <c r="AU8" t="n">
-        <v>6</v>
-      </c>
       <c r="AV8" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>44</v>
+        <v>4.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.4</v>
+        <v>4.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="BC8" t="n">
-        <v>8.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>42</v>
+        <v>4.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.6</v>
+        <v>4.6</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="BJ8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BN8" t="n">
         <v>5.1</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BP8" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BU8" t="n">
         <v>5.8</v>
       </c>
       <c r="BV8" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BX8" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,246 +2626,246 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Atletico MG</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G9" t="n">
         <v>2.22</v>
       </c>
-      <c r="G9" t="n">
-        <v>2.34</v>
-      </c>
       <c r="H9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K9" t="n">
         <v>3.65</v>
       </c>
-      <c r="I9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.4</v>
-      </c>
       <c r="L9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BN9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ9" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BT9" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,498 +2875,1006 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Barcelona (Ecu)</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.92</v>
+        <v>2.32</v>
       </c>
       <c r="G10" t="n">
-        <v>2.02</v>
+        <v>2.46</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="I10" t="n">
-        <v>4.9</v>
+        <v>3.85</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="K10" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="M10" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="N10" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="O10" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="P10" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>2.56</v>
       </c>
       <c r="R10" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="S10" t="n">
-        <v>3.85</v>
+        <v>5.3</v>
       </c>
       <c r="T10" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="U10" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="X10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG10" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y10" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="AH10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP10" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AC10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF10" t="n">
+      <c r="AQ10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV10" t="n">
         <v>12</v>
       </c>
-      <c r="AG10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH10" t="n">
+      <c r="AW10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>24</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP10" t="n">
         <v>21</v>
       </c>
-      <c r="AI10" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT10" t="n">
+      <c r="BQ10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>55</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT10" t="n">
         <v>7.2</v>
       </c>
-      <c r="AU10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>60</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>38</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>8</v>
-      </c>
       <c r="BU10" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW10" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY10" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BZ10" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Avai</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>America MG</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="X11" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:28:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Univ Catolica (Ecu)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Barcelona (Ecu)</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="X12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>60</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>38</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>29</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:28:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Mexican Liga MX</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>22:00:00</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Cruz Azul</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Puebla</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="F13" t="n">
         <v>1.35</v>
       </c>
-      <c r="G11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="H11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="I11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="G13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K13" t="n">
         <v>6.4</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L13" t="n">
         <v>1.27</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M13" t="n">
         <v>1.04</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N13" t="n">
+        <v>5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X13" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>430</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>95</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF13" t="n">
         <v>4.9</v>
       </c>
-      <c r="O11" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="X11" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>430</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="BG13" t="n">
+        <v>46</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>24</v>
+      </c>
+      <c r="BS13" t="n">
         <v>9.6</v>
       </c>
-      <c r="AC11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>180</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>240</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>24</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BT11" t="n">
+      <c r="BT13" t="n">
         <v>14</v>
       </c>
-      <c r="BU11" t="n">
+      <c r="BU13" t="n">
         <v>7.4</v>
       </c>
-      <c r="BV11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW11" t="n">
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
         <v>13.5</v>
       </c>
-      <c r="BX11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY11" t="n">
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
         <v>13.5</v>
       </c>
-      <c r="BZ11" t="n">
+      <c r="BZ13" t="n">
         <v>12</v>
       </c>
-      <c r="CA11" t="n">
+      <c r="CA13" t="n">
         <v>6.8</v>
       </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>2026-07-20 10:18:32</t>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G2" t="n">
         <v>2.16</v>
       </c>
       <c r="H2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I2" t="n">
         <v>4.1</v>
@@ -872,7 +872,7 @@
         <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L2" t="n">
         <v>1.43</v>
@@ -887,7 +887,7 @@
         <v>1.35</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q2" t="n">
         <v>2.04</v>
@@ -899,67 +899,67 @@
         <v>3.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U2" t="n">
         <v>2.1</v>
       </c>
       <c r="V2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y2" t="n">
         <v>14</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>13.5</v>
       </c>
       <c r="Z2" t="n">
         <v>28</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
-        <v>190</v>
+        <v>50</v>
       </c>
       <c r="AF2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>740</v>
+        <v>60</v>
       </c>
       <c r="AJ2" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AK2" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="AL2" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO2" t="n">
         <v>55</v>
@@ -968,52 +968,52 @@
         <v>12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS2" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU2" t="n">
         <v>7.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW2" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AX2" t="n">
         <v>12</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA2" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BB2" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="BC2" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BE2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BF2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BG2" t="n">
         <v>29</v>
@@ -1046,7 +1046,7 @@
         <v>15</v>
       </c>
       <c r="BQ2" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
@@ -1058,13 +1058,13 @@
         <v>7.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BV2" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
@@ -1073,14 +1073,14 @@
         <v>13.5</v>
       </c>
       <c r="BZ2" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-20 12:28:57</t>
+          <t>2026-07-20 14:38:58</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>3.75</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="H3" t="n">
         <v>2.26</v>
@@ -1123,28 +1123,28 @@
         <v>2.32</v>
       </c>
       <c r="J3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
         <v>3.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M3" t="n">
         <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="R3" t="n">
         <v>1.22</v>
@@ -1153,34 +1153,34 @@
         <v>5.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V3" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="W3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AA3" t="n">
         <v>32</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD3" t="n">
         <v>12</v>
@@ -1198,13 +1198,13 @@
         <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ3" t="n">
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1222,31 +1222,31 @@
         <v>8.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR3" t="n">
         <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU3" t="n">
         <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW3" t="n">
         <v>19.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AZ3" t="n">
         <v>20</v>
@@ -1273,22 +1273,22 @@
         <v>18.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BN3" t="n">
         <v>7</v>
@@ -1312,13 +1312,13 @@
         <v>4.9</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BV3" t="n">
         <v>19</v>
       </c>
       <c r="BW3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX3" t="n">
         <v>40</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-20 12:28:57</t>
+          <t>2026-07-20 14:38:58</t>
         </is>
       </c>
     </row>
@@ -1374,10 +1374,10 @@
         <v>3.45</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
         <v>3.5</v>
@@ -1395,7 +1395,7 @@
         <v>1.39</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q4" t="n">
         <v>2.16</v>
@@ -1404,64 +1404,64 @@
         <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T4" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U4" t="n">
         <v>2.04</v>
       </c>
       <c r="V4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W4" t="n">
         <v>1.71</v>
       </c>
       <c r="X4" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AC4" t="n">
         <v>7.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF4" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG4" t="n">
         <v>11.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>710</v>
+        <v>600</v>
       </c>
       <c r="AJ4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AL4" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
@@ -1470,7 +1470,7 @@
         <v>23</v>
       </c>
       <c r="AO4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP4" t="n">
         <v>10.5</v>
@@ -1506,13 +1506,13 @@
         <v>16.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB4" t="n">
         <v>20</v>
       </c>
       <c r="BC4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD4" t="n">
         <v>26</v>
@@ -1527,13 +1527,13 @@
         <v>26</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="BJ4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK4" t="n">
         <v>6.2</v>
@@ -1551,10 +1551,10 @@
         <v>4.1</v>
       </c>
       <c r="BP4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR4" t="n">
         <v>34</v>
@@ -1569,16 +1569,16 @@
         <v>5.2</v>
       </c>
       <c r="BV4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BW4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX4" t="n">
         <v>44</v>
       </c>
       <c r="BY4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ4" t="n">
         <v>32</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-20 12:28:57</t>
+          <t>2026-07-20 14:38:58</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G5" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="H5" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="I5" t="n">
         <v>3.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
         <v>3.95</v>
@@ -1646,31 +1646,31 @@
         <v>4.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P5" t="n">
         <v>2.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="R5" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S5" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="T5" t="n">
         <v>1.58</v>
       </c>
       <c r="U5" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="V5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="X5" t="n">
         <v>23</v>
@@ -1685,13 +1685,13 @@
         <v>65</v>
       </c>
       <c r="AB5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AE5" t="n">
         <v>46</v>
@@ -1700,13 +1700,13 @@
         <v>19</v>
       </c>
       <c r="AG5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ5" t="n">
         <v>30</v>
@@ -1718,7 +1718,7 @@
         <v>29</v>
       </c>
       <c r="AM5" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AN5" t="n">
         <v>13</v>
@@ -1730,10 +1730,10 @@
         <v>17.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR5" t="n">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="AS5" t="n">
         <v>7</v>
@@ -1745,7 +1745,7 @@
         <v>7.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AW5" t="n">
         <v>32</v>
@@ -1754,7 +1754,7 @@
         <v>14.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AZ5" t="n">
         <v>11</v>
@@ -1763,7 +1763,7 @@
         <v>32</v>
       </c>
       <c r="BB5" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BC5" t="n">
         <v>17.5</v>
@@ -1784,13 +1784,13 @@
         <v>4.2</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="BJ5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1802,13 +1802,13 @@
         <v>5.3</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BP5" t="n">
         <v>14.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="BR5" t="n">
         <v>24</v>
@@ -1820,7 +1820,7 @@
         <v>7.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BV5" t="n">
         <v>25</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-20 12:28:57</t>
+          <t>2026-07-20 14:38:58</t>
         </is>
       </c>
     </row>
@@ -1876,16 +1876,16 @@
         <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H6" t="n">
         <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K6" t="n">
         <v>950</v>
@@ -1897,34 +1897,34 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-20 12:28:57</t>
+          <t>2026-07-20 14:38:58</t>
         </is>
       </c>
     </row>
@@ -2130,16 +2130,16 @@
         <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H7" t="n">
         <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
         <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
         <v>1.01</v>
@@ -2166,19 +2166,19 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-20 12:28:57</t>
+          <t>2026-07-20 14:38:58</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
         <v>3.15</v>
       </c>
       <c r="K8" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L8" t="n">
         <v>1.54</v>
@@ -2408,7 +2408,7 @@
         <v>2.78</v>
       </c>
       <c r="O8" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P8" t="n">
         <v>1.61</v>
@@ -2546,13 +2546,13 @@
         <v>2.82</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ8" t="n">
         <v>11</v>
       </c>
       <c r="BK8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-20 12:28:57</t>
+          <t>2026-07-20 14:38:58</t>
         </is>
       </c>
     </row>
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G9" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H9" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I9" t="n">
         <v>3.8</v>
@@ -2650,7 +2650,7 @@
         <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-20 12:28:57</t>
+          <t>2026-07-20 14:38:58</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="G10" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="H10" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="I10" t="n">
         <v>3.85</v>
@@ -2913,7 +2913,7 @@
         <v>1.12</v>
       </c>
       <c r="N10" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="O10" t="n">
         <v>1.51</v>
@@ -2922,16 +2922,16 @@
         <v>1.58</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R10" t="n">
         <v>1.21</v>
       </c>
       <c r="S10" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U10" t="n">
         <v>1.8</v>
@@ -2940,19 +2940,19 @@
         <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="X10" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="Y10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z10" t="n">
         <v>30</v>
       </c>
       <c r="AA10" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB10" t="n">
         <v>7.8</v>
@@ -2961,13 +2961,13 @@
         <v>7.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE10" t="n">
         <v>75</v>
       </c>
       <c r="AF10" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG10" t="n">
         <v>12.5</v>
@@ -2976,13 +2976,13 @@
         <v>28</v>
       </c>
       <c r="AI10" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AJ10" t="n">
         <v>42</v>
       </c>
       <c r="AK10" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AL10" t="n">
         <v>75</v>
@@ -2997,19 +2997,19 @@
         <v>90</v>
       </c>
       <c r="AP10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ10" t="n">
         <v>9</v>
       </c>
       <c r="AR10" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU10" t="n">
         <v>6</v>
@@ -3018,37 +3018,37 @@
         <v>12</v>
       </c>
       <c r="AW10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
         <v>19.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB10" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE10" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>10</v>
       </c>
       <c r="BF10" t="n">
         <v>24</v>
       </c>
       <c r="BG10" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH10" t="n">
         <v>2.8</v>
@@ -3060,22 +3060,22 @@
         <v>12</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ10" t="n">
         <v>14</v>
@@ -3084,35 +3084,35 @@
         <v>55</v>
       </c>
       <c r="BS10" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BT10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV10" t="n">
         <v>42</v>
       </c>
       <c r="BW10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BX10" t="n">
-        <v>65</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>9</v>
-      </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-20 12:28:57</t>
+          <t>2026-07-20 14:38:58</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
         <v>3.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M11" t="n">
         <v>1.1</v>
@@ -3248,7 +3248,7 @@
         <v>32</v>
       </c>
       <c r="AO11" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AP11" t="n">
         <v>9.4</v>
@@ -3305,68 +3305,68 @@
         <v>7</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="BJ11" t="n">
         <v>10.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BN11" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS11" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT11" t="n">
         <v>6.8</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>38</v>
+      </c>
+      <c r="CA11" t="n">
         <v>12.5</v>
       </c>
-      <c r="BZ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>11.5</v>
-      </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-20 12:28:57</t>
+          <t>2026-07-20 14:38:58</t>
         </is>
       </c>
     </row>
@@ -3409,13 +3409,13 @@
         <v>5</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K12" t="n">
         <v>3.65</v>
       </c>
       <c r="L12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M12" t="n">
         <v>1.08</v>
@@ -3487,7 +3487,7 @@
         <v>75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK12" t="n">
         <v>23</v>
@@ -3598,7 +3598,7 @@
         <v>8</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-20 12:28:57</t>
+          <t>2026-07-20 14:38:58</t>
         </is>
       </c>
     </row>
@@ -3657,16 +3657,16 @@
         <v>1.38</v>
       </c>
       <c r="H13" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I13" t="n">
         <v>10.5</v>
       </c>
       <c r="J13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="K13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L13" t="n">
         <v>1.27</v>
@@ -3675,7 +3675,7 @@
         <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O13" t="n">
         <v>1.23</v>
@@ -3693,7 +3693,7 @@
         <v>2.7</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U13" t="n">
         <v>1.85</v>
@@ -3705,7 +3705,7 @@
         <v>3.6</v>
       </c>
       <c r="X13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y13" t="n">
         <v>32</v>
@@ -3717,7 +3717,7 @@
         <v>430</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC13" t="n">
         <v>14</v>
@@ -3726,7 +3726,7 @@
         <v>38</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AF13" t="n">
         <v>8.6</v>
@@ -3747,7 +3747,7 @@
         <v>14.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
@@ -3759,10 +3759,10 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ13" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AR13" t="n">
         <v>34</v>
@@ -3777,7 +3777,7 @@
         <v>12.5</v>
       </c>
       <c r="AV13" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AW13" t="n">
         <v>42</v>
@@ -3789,7 +3789,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BA13" t="n">
         <v>40</v>
@@ -3828,7 +3828,7 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BN13" t="n">
         <v>3.8</v>
@@ -3846,7 +3846,7 @@
         <v>24</v>
       </c>
       <c r="BS13" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BT13" t="n">
         <v>14</v>
@@ -3864,7 +3864,7 @@
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BZ13" t="n">
         <v>12</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-20 12:28:57</t>
+          <t>2026-07-20 14:38:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G2" t="n">
         <v>2.16</v>
@@ -872,7 +872,7 @@
         <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.43</v>
@@ -881,7 +881,7 @@
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O2" t="n">
         <v>1.35</v>
@@ -893,7 +893,7 @@
         <v>2.04</v>
       </c>
       <c r="R2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S2" t="n">
         <v>3.7</v>
@@ -908,25 +908,25 @@
         <v>1.32</v>
       </c>
       <c r="W2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X2" t="n">
         <v>13.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA2" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD2" t="n">
         <v>16</v>
@@ -953,7 +953,7 @@
         <v>24</v>
       </c>
       <c r="AL2" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -974,7 +974,7 @@
         <v>24</v>
       </c>
       <c r="AS2" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AT2" t="n">
         <v>8.6</v>
@@ -989,10 +989,10 @@
         <v>42</v>
       </c>
       <c r="AX2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
         <v>17</v>
@@ -1010,7 +1010,7 @@
         <v>34</v>
       </c>
       <c r="BE2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BF2" t="n">
         <v>14.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-20 14:38:58</t>
+          <t>2026-07-20 16:48:27</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G3" t="n">
         <v>3.95</v>
       </c>
       <c r="H3" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I3" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="J3" t="n">
         <v>3.2</v>
@@ -1144,13 +1144,13 @@
         <v>1.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="R3" t="n">
         <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T3" t="n">
         <v>2.16</v>
@@ -1159,7 +1159,7 @@
         <v>1.82</v>
       </c>
       <c r="V3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W3" t="n">
         <v>1.33</v>
@@ -1198,7 +1198,7 @@
         <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ3" t="n">
         <v>1000</v>
@@ -1207,7 +1207,7 @@
         <v>65</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
@@ -1222,10 +1222,10 @@
         <v>8.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS3" t="n">
         <v>19.5</v>
@@ -1234,7 +1234,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AU3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV3" t="n">
         <v>10.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-20 14:38:58</t>
+          <t>2026-07-20 16:48:27</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G4" t="n">
         <v>2.4</v>
@@ -1374,16 +1374,16 @@
         <v>3.45</v>
       </c>
       <c r="I4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
         <v>3.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1392,7 +1392,7 @@
         <v>3.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P4" t="n">
         <v>1.81</v>
@@ -1401,16 +1401,16 @@
         <v>2.16</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S4" t="n">
         <v>3.95</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="U4" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V4" t="n">
         <v>1.38</v>
@@ -1422,16 +1422,16 @@
         <v>12</v>
       </c>
       <c r="Y4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC4" t="n">
         <v>7.6</v>
@@ -1452,13 +1452,13 @@
         <v>18.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>600</v>
+        <v>670</v>
       </c>
       <c r="AJ4" t="n">
         <v>55</v>
       </c>
       <c r="AK4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL4" t="n">
         <v>44</v>
@@ -1494,7 +1494,7 @@
         <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX4" t="n">
         <v>12.5</v>
@@ -1506,7 +1506,7 @@
         <v>16.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB4" t="n">
         <v>20</v>
@@ -1539,7 +1539,7 @@
         <v>6.2</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM4" t="n">
         <v>15.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-20 14:38:58</t>
+          <t>2026-07-20 16:48:27</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="G5" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="I5" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
         <v>3.95</v>
@@ -1652,25 +1652,25 @@
         <v>2.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S5" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T5" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U5" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="V5" t="n">
         <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="X5" t="n">
         <v>23</v>
@@ -1688,13 +1688,13 @@
         <v>15</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AF5" t="n">
         <v>19</v>
@@ -1703,10 +1703,10 @@
         <v>11.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AI5" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ5" t="n">
         <v>30</v>
@@ -1733,10 +1733,10 @@
         <v>16</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT5" t="n">
         <v>11</v>
@@ -1748,7 +1748,7 @@
         <v>12</v>
       </c>
       <c r="AW5" t="n">
-        <v>32</v>
+        <v>6.6</v>
       </c>
       <c r="AX5" t="n">
         <v>14.5</v>
@@ -1763,7 +1763,7 @@
         <v>32</v>
       </c>
       <c r="BB5" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="BC5" t="n">
         <v>17.5</v>
@@ -1775,13 +1775,13 @@
         <v>7</v>
       </c>
       <c r="BF5" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BG5" t="n">
         <v>6.4</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI5" t="n">
         <v>3.75</v>
@@ -1790,13 +1790,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BN5" t="n">
         <v>5.3</v>
@@ -1805,16 +1805,16 @@
         <v>4.7</v>
       </c>
       <c r="BP5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BR5" t="n">
         <v>24</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT5" t="n">
         <v>7.2</v>
@@ -1826,23 +1826,23 @@
         <v>25</v>
       </c>
       <c r="BW5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BX5" t="n">
         <v>32</v>
       </c>
       <c r="BY5" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BZ5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-20 14:38:58</t>
+          <t>2026-07-20 16:48:27</t>
         </is>
       </c>
     </row>
@@ -1897,22 +1897,22 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -1981,52 +1981,52 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -2038,65 +2038,65 @@
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-20 14:38:58</t>
+          <t>2026-07-20 16:48:27</t>
         </is>
       </c>
     </row>
@@ -2235,52 +2235,52 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
         <v>1.01</v>
@@ -2292,65 +2292,65 @@
         <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-20 14:38:58</t>
+          <t>2026-07-20 16:48:27</t>
         </is>
       </c>
     </row>
@@ -2405,13 +2405,13 @@
         <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="O8" t="n">
         <v>1.49</v>
       </c>
       <c r="P8" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="Q8" t="n">
         <v>2.46</v>
@@ -2432,7 +2432,7 @@
         <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X8" t="n">
         <v>10.5</v>
@@ -2447,13 +2447,13 @@
         <v>80</v>
       </c>
       <c r="AB8" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AC8" t="n">
         <v>7.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE8" t="n">
         <v>65</v>
@@ -2495,7 +2495,7 @@
         <v>9</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AS8" t="n">
         <v>4.6</v>
@@ -2510,7 +2510,7 @@
         <v>13.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AX8" t="n">
         <v>12.5</v>
@@ -2522,7 +2522,7 @@
         <v>19</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BB8" t="n">
         <v>4.3</v>
@@ -2531,13 +2531,13 @@
         <v>4.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BE8" t="n">
         <v>4.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BG8" t="n">
         <v>4.6</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-20 14:38:58</t>
+          <t>2026-07-20 16:48:27</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>3.8</v>
       </c>
       <c r="J9" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
         <v>3.6</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-20 14:38:58</t>
+          <t>2026-07-20 16:48:27</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="G10" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H10" t="n">
         <v>3.45</v>
       </c>
       <c r="I10" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="J10" t="n">
         <v>3.15</v>
@@ -2913,31 +2913,31 @@
         <v>1.12</v>
       </c>
       <c r="N10" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="O10" t="n">
         <v>1.51</v>
       </c>
       <c r="P10" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="R10" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T10" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="U10" t="n">
         <v>1.8</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
         <v>1.65</v>
@@ -2946,31 +2946,31 @@
         <v>11</v>
       </c>
       <c r="Y10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z10" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
         <v>100</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC10" t="n">
         <v>7.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE10" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AF10" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH10" t="n">
         <v>28</v>
@@ -2982,7 +2982,7 @@
         <v>42</v>
       </c>
       <c r="AK10" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AL10" t="n">
         <v>75</v>
@@ -2994,34 +2994,34 @@
         <v>42</v>
       </c>
       <c r="AO10" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP10" t="n">
         <v>8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU10" t="n">
         <v>6</v>
       </c>
       <c r="AV10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.6</v>
+        <v>38</v>
       </c>
       <c r="AX10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY10" t="n">
         <v>10.5</v>
@@ -3030,7 +3030,7 @@
         <v>19.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="BB10" t="n">
         <v>26</v>
@@ -3039,80 +3039,80 @@
         <v>24</v>
       </c>
       <c r="BD10" t="n">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BF10" t="n">
         <v>24</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH10" t="n">
         <v>2.8</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="BJ10" t="n">
         <v>12</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP10" t="n">
         <v>22</v>
       </c>
       <c r="BQ10" t="n">
-        <v>14</v>
+        <v>7.4</v>
       </c>
       <c r="BR10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT10" t="n">
         <v>7</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV10" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
         <v>9</v>
       </c>
-      <c r="BZ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-20 14:38:58</t>
+          <t>2026-07-20 16:48:27</t>
         </is>
       </c>
     </row>
@@ -3149,16 +3149,16 @@
         <v>2.34</v>
       </c>
       <c r="H11" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I11" t="n">
         <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L11" t="n">
         <v>1.51</v>
@@ -3188,7 +3188,7 @@
         <v>1.96</v>
       </c>
       <c r="U11" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V11" t="n">
         <v>1.33</v>
@@ -3284,7 +3284,7 @@
         <v>17.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BB11" t="n">
         <v>24</v>
@@ -3293,7 +3293,7 @@
         <v>22</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE11" t="n">
         <v>7.4</v>
@@ -3335,7 +3335,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BR11" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
         <v>12.5</v>
@@ -3359,14 +3359,14 @@
         <v>13.5</v>
       </c>
       <c r="BZ11" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
         <v>12.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-20 14:38:58</t>
+          <t>2026-07-20 16:48:27</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="G12" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I12" t="n">
         <v>5</v>
@@ -3427,7 +3427,7 @@
         <v>1.37</v>
       </c>
       <c r="P12" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q12" t="n">
         <v>2.1</v>
@@ -3448,7 +3448,7 @@
         <v>1.25</v>
       </c>
       <c r="W12" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X12" t="n">
         <v>12.5</v>
@@ -3457,7 +3457,7 @@
         <v>15</v>
       </c>
       <c r="Z12" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA12" t="n">
         <v>120</v>
@@ -3496,13 +3496,13 @@
         <v>44</v>
       </c>
       <c r="AM12" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN12" t="n">
         <v>17</v>
       </c>
       <c r="AO12" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AP12" t="n">
         <v>10.5</v>
@@ -3526,7 +3526,7 @@
         <v>16</v>
       </c>
       <c r="AW12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX12" t="n">
         <v>10</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-20 14:38:58</t>
+          <t>2026-07-20 16:48:27</t>
         </is>
       </c>
     </row>
@@ -3654,19 +3654,19 @@
         <v>1.35</v>
       </c>
       <c r="G13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="H13" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J13" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="K13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L13" t="n">
         <v>1.27</v>
@@ -3675,7 +3675,7 @@
         <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
         <v>1.23</v>
@@ -3690,25 +3690,25 @@
         <v>1.55</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="T13" t="n">
         <v>2.1</v>
       </c>
       <c r="U13" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V13" t="n">
         <v>1.11</v>
       </c>
       <c r="W13" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="X13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Z13" t="n">
         <v>100</v>
@@ -3720,7 +3720,7 @@
         <v>9.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD13" t="n">
         <v>38</v>
@@ -3732,13 +3732,13 @@
         <v>8.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ13" t="n">
         <v>11</v>
@@ -3747,28 +3747,28 @@
         <v>14.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN13" t="n">
         <v>5.2</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AP13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR13" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS13" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="AT13" t="n">
         <v>8.6</v>
@@ -3777,10 +3777,10 @@
         <v>12.5</v>
       </c>
       <c r="AV13" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AW13" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX13" t="n">
         <v>7.8</v>
@@ -3789,22 +3789,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="BA13" t="n">
         <v>40</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC13" t="n">
         <v>13</v>
       </c>
       <c r="BD13" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BE13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BF13" t="n">
         <v>4.9</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-20 14:38:58</t>
+          <t>2026-07-20 16:48:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -352,7 +352,7 @@
     <t>America MG</t>
   </si>
   <si>
-    <t>2026-07-20 18:05:15</t>
+    <t>2026-07-20 18:26:24</t>
   </si>
 </sst>
 </file>
@@ -946,13 +946,13 @@
         <v>102</v>
       </c>
       <c r="F2">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G2">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H2">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I2">
         <v>4.1</v>
@@ -964,7 +964,7 @@
         <v>3.65</v>
       </c>
       <c r="L2">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M2">
         <v>1.08</v>
@@ -979,7 +979,7 @@
         <v>1.91</v>
       </c>
       <c r="Q2">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R2">
         <v>1.34</v>
@@ -994,22 +994,22 @@
         <v>2.1</v>
       </c>
       <c r="V2">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W2">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z2">
         <v>28</v>
       </c>
       <c r="AA2">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB2">
         <v>9.199999999999999</v>
@@ -1102,7 +1102,7 @@
         <v>40</v>
       </c>
       <c r="BF2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG2">
         <v>29</v>
@@ -1188,7 +1188,7 @@
         <v>103</v>
       </c>
       <c r="F3">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="G3">
         <v>4.1</v>
@@ -1197,16 +1197,16 @@
         <v>2.22</v>
       </c>
       <c r="I3">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="J3">
         <v>3.3</v>
       </c>
       <c r="K3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L3">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="M3">
         <v>1.11</v>
@@ -1221,7 +1221,7 @@
         <v>1.61</v>
       </c>
       <c r="Q3">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="R3">
         <v>1.22</v>
@@ -1242,7 +1242,7 @@
         <v>1.33</v>
       </c>
       <c r="X3">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y3">
         <v>7.2</v>
@@ -1251,13 +1251,13 @@
         <v>12.5</v>
       </c>
       <c r="AA3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AB3">
         <v>10.5</v>
       </c>
       <c r="AC3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD3">
         <v>12</v>
@@ -1272,10 +1272,10 @@
         <v>18</v>
       </c>
       <c r="AH3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ3">
         <v>90</v>
@@ -1287,7 +1287,7 @@
         <v>85</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN3">
         <v>90</v>
@@ -1299,16 +1299,16 @@
         <v>8.6</v>
       </c>
       <c r="AQ3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR3">
         <v>11</v>
       </c>
       <c r="AS3">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AT3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU3">
         <v>7</v>
@@ -1317,37 +1317,37 @@
         <v>10.5</v>
       </c>
       <c r="AW3">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AX3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY3">
         <v>15.5</v>
       </c>
       <c r="AZ3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA3">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="BB3">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="BC3">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="BD3">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="BE3">
         <v>46</v>
       </c>
       <c r="BF3">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="BG3">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="BH3">
         <v>2.76</v>
@@ -1430,13 +1430,13 @@
         <v>104</v>
       </c>
       <c r="F4">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G4">
         <v>2.38</v>
       </c>
       <c r="H4">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I4">
         <v>3.7</v>
@@ -1451,7 +1451,7 @@
         <v>1.45</v>
       </c>
       <c r="M4">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N4">
         <v>3.4</v>
@@ -1499,7 +1499,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD4">
         <v>15</v>
@@ -1517,7 +1517,7 @@
         <v>18.5</v>
       </c>
       <c r="AI4">
-        <v>610</v>
+        <v>580</v>
       </c>
       <c r="AJ4">
         <v>55</v>
@@ -1547,7 +1547,7 @@
         <v>20</v>
       </c>
       <c r="AS4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AT4">
         <v>8.4</v>
@@ -1595,61 +1595,61 @@
         <v>3.2</v>
       </c>
       <c r="BI4">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="BJ4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK4">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL4">
         <v>140</v>
       </c>
       <c r="BM4">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN4">
         <v>5.1</v>
       </c>
       <c r="BO4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP4">
         <v>18</v>
       </c>
       <c r="BQ4">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR4">
         <v>34</v>
       </c>
       <c r="BS4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BT4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU4">
         <v>5.2</v>
       </c>
       <c r="BV4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BW4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX4">
         <v>44</v>
       </c>
       <c r="BY4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BZ4">
         <v>32</v>
       </c>
       <c r="CA4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CB4" t="s">
         <v>112</v>
@@ -1675,19 +1675,19 @@
         <v>2.1</v>
       </c>
       <c r="G5">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H5">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I5">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J5">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K5">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L5">
         <v>1.27</v>
@@ -1696,34 +1696,34 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O5">
         <v>1.21</v>
       </c>
       <c r="P5">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="Q5">
         <v>1.63</v>
       </c>
       <c r="R5">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S5">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T5">
         <v>1.57</v>
       </c>
       <c r="U5">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="V5">
         <v>1.35</v>
       </c>
       <c r="W5">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="X5">
         <v>23</v>
@@ -1735,7 +1735,7 @@
         <v>30</v>
       </c>
       <c r="AA5">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB5">
         <v>15</v>
@@ -1801,7 +1801,7 @@
         <v>12</v>
       </c>
       <c r="AW5">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="AX5">
         <v>14.5</v>
@@ -1831,13 +1831,13 @@
         <v>9.6</v>
       </c>
       <c r="BG5">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="BH5">
         <v>4.1</v>
       </c>
       <c r="BI5">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BJ5">
         <v>8.800000000000001</v>
@@ -1849,7 +1849,7 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN5">
         <v>5.3</v>
@@ -1858,10 +1858,10 @@
         <v>4.7</v>
       </c>
       <c r="BP5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR5">
         <v>24</v>
@@ -1876,10 +1876,10 @@
         <v>5.2</v>
       </c>
       <c r="BV5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BW5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX5">
         <v>32</v>
@@ -2156,7 +2156,7 @@
         <v>107</v>
       </c>
       <c r="F7">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="G7">
         <v>990</v>
@@ -2416,7 +2416,7 @@
         <v>3.3</v>
       </c>
       <c r="L8">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="M8">
         <v>1.12</v>
@@ -2440,7 +2440,7 @@
         <v>5</v>
       </c>
       <c r="T8">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U8">
         <v>1.85</v>
@@ -2455,7 +2455,7 @@
         <v>10.5</v>
       </c>
       <c r="Y8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z8">
         <v>28</v>
@@ -2479,7 +2479,7 @@
         <v>16.5</v>
       </c>
       <c r="AG8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH8">
         <v>25</v>
@@ -2512,10 +2512,10 @@
         <v>9</v>
       </c>
       <c r="AR8">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS8">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT8">
         <v>6.8</v>
@@ -2527,7 +2527,7 @@
         <v>13.5</v>
       </c>
       <c r="AW8">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX8">
         <v>12.5</v>
@@ -2539,28 +2539,28 @@
         <v>19</v>
       </c>
       <c r="BA8">
+        <v>7.6</v>
+      </c>
+      <c r="BB8">
         <v>7</v>
       </c>
-      <c r="BB8">
-        <v>6.6</v>
-      </c>
       <c r="BC8">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BD8">
+        <v>7.4</v>
+      </c>
+      <c r="BE8">
+        <v>8</v>
+      </c>
+      <c r="BF8">
         <v>6.8</v>
       </c>
-      <c r="BE8">
-        <v>7.4</v>
-      </c>
-      <c r="BF8">
-        <v>6.4</v>
-      </c>
       <c r="BG8">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BH8">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BI8">
         <v>2.56</v>
@@ -2569,16 +2569,16 @@
         <v>11</v>
       </c>
       <c r="BK8">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN8">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO8">
         <v>4.5</v>
@@ -2587,13 +2587,13 @@
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BT8">
         <v>6.6</v>
@@ -2605,19 +2605,19 @@
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
+        <v>13</v>
+      </c>
+      <c r="BZ8">
+        <v>1000</v>
+      </c>
+      <c r="CA8">
         <v>12</v>
-      </c>
-      <c r="BZ8">
-        <v>1000</v>
-      </c>
-      <c r="CA8">
-        <v>11.5</v>
       </c>
       <c r="CB8" t="s">
         <v>112</v>
@@ -2652,19 +2652,19 @@
         <v>3.8</v>
       </c>
       <c r="J9">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K9">
         <v>3.6</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M9">
         <v>1.07</v>
       </c>
       <c r="N9">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O9">
         <v>1.32</v>
@@ -2682,34 +2682,34 @@
         <v>3.5</v>
       </c>
       <c r="T9">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U9">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V9">
         <v>1.35</v>
       </c>
       <c r="W9">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X9">
         <v>14</v>
       </c>
       <c r="Y9">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="Z9">
         <v>27</v>
       </c>
       <c r="AA9">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB9">
         <v>10.5</v>
       </c>
       <c r="AC9">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD9">
         <v>16</v>
@@ -2718,7 +2718,7 @@
         <v>50</v>
       </c>
       <c r="AF9">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AG9">
         <v>11.5</v>
@@ -2730,7 +2730,7 @@
         <v>60</v>
       </c>
       <c r="AJ9">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AK9">
         <v>24</v>
@@ -2742,13 +2742,13 @@
         <v>95</v>
       </c>
       <c r="AN9">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AO9">
         <v>48</v>
       </c>
       <c r="AP9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ9">
         <v>13</v>
@@ -2772,7 +2772,7 @@
         <v>38</v>
       </c>
       <c r="AX9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY9">
         <v>10</v>
@@ -2924,7 +2924,7 @@
         <v>5.1</v>
       </c>
       <c r="T10">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="U10">
         <v>1.8</v>
@@ -2942,7 +2942,7 @@
         <v>10.5</v>
       </c>
       <c r="Z10">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AA10">
         <v>100</v>
@@ -2999,7 +2999,7 @@
         <v>18.5</v>
       </c>
       <c r="AS10">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT10">
         <v>6.6</v>
@@ -3023,7 +3023,7 @@
         <v>19.5</v>
       </c>
       <c r="BA10">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB10">
         <v>26</v>
@@ -3035,13 +3035,13 @@
         <v>10</v>
       </c>
       <c r="BE10">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF10">
         <v>24</v>
       </c>
       <c r="BG10">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH10">
         <v>2.8</v>
@@ -3256,7 +3256,7 @@
         <v>6.8</v>
       </c>
       <c r="AX11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY11">
         <v>10</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -352,7 +352,7 @@
     <t>America MG</t>
   </si>
   <si>
-    <t>2026-07-20 18:26:24</t>
+    <t>2026-07-20 20:33:00</t>
   </si>
 </sst>
 </file>
@@ -946,22 +946,22 @@
         <v>102</v>
       </c>
       <c r="F2">
+        <v>2.06</v>
+      </c>
+      <c r="G2">
         <v>2.1</v>
       </c>
-      <c r="G2">
-        <v>2.14</v>
-      </c>
       <c r="H2">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I2">
         <v>4.1</v>
       </c>
       <c r="J2">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K2">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L2">
         <v>1.44</v>
@@ -988,58 +988,58 @@
         <v>3.7</v>
       </c>
       <c r="T2">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U2">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V2">
         <v>1.32</v>
       </c>
       <c r="W2">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="X2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y2">
         <v>14.5</v>
       </c>
       <c r="Z2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA2">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="AB2">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2">
         <v>16.5</v>
       </c>
       <c r="AE2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI2">
         <v>60</v>
       </c>
       <c r="AJ2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL2">
         <v>40</v>
@@ -1060,13 +1060,13 @@
         <v>12.5</v>
       </c>
       <c r="AR2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AS2">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AT2">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AU2">
         <v>7.4</v>
@@ -1081,7 +1081,7 @@
         <v>11.5</v>
       </c>
       <c r="AY2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ2">
         <v>17</v>
@@ -1090,7 +1090,7 @@
         <v>50</v>
       </c>
       <c r="BB2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC2">
         <v>21</v>
@@ -1102,10 +1102,10 @@
         <v>40</v>
       </c>
       <c r="BF2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BG2">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="BH2">
         <v>3.3</v>
@@ -1188,28 +1188,28 @@
         <v>103</v>
       </c>
       <c r="F3">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="G3">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>2.22</v>
       </c>
       <c r="I3">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J3">
         <v>3.3</v>
       </c>
       <c r="K3">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L3">
         <v>1.58</v>
       </c>
       <c r="M3">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N3">
         <v>2.78</v>
@@ -1221,37 +1221,37 @@
         <v>1.61</v>
       </c>
       <c r="Q3">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R3">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S3">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T3">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U3">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V3">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W3">
         <v>1.33</v>
       </c>
       <c r="X3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Y3">
         <v>7.2</v>
       </c>
       <c r="Z3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB3">
         <v>10.5</v>
@@ -1260,7 +1260,7 @@
         <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE3">
         <v>30</v>
@@ -1275,7 +1275,7 @@
         <v>24</v>
       </c>
       <c r="AI3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ3">
         <v>90</v>
@@ -1305,7 +1305,7 @@
         <v>11</v>
       </c>
       <c r="AS3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AT3">
         <v>10</v>
@@ -1329,7 +1329,7 @@
         <v>21</v>
       </c>
       <c r="BA3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB3">
         <v>75</v>
@@ -1341,7 +1341,7 @@
         <v>65</v>
       </c>
       <c r="BE3">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="BF3">
         <v>70</v>
@@ -1353,61 +1353,61 @@
         <v>2.76</v>
       </c>
       <c r="BI3">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="BJ3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK3">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BN3">
         <v>7.2</v>
       </c>
       <c r="BO3">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP3">
         <v>40</v>
       </c>
       <c r="BQ3">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BR3">
         <v>60</v>
       </c>
       <c r="BS3">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BT3">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BU3">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BV3">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BW3">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BX3">
         <v>40</v>
       </c>
       <c r="BY3">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BZ3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="CA3">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="CB3" t="s">
         <v>112</v>
@@ -1433,10 +1433,10 @@
         <v>2.28</v>
       </c>
       <c r="G4">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I4">
         <v>3.7</v>
@@ -1448,34 +1448,34 @@
         <v>3.55</v>
       </c>
       <c r="L4">
-        <v>1.45</v>
+        <v>1.17</v>
       </c>
       <c r="M4">
         <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O4">
         <v>1.38</v>
       </c>
       <c r="P4">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="Q4">
         <v>2.12</v>
       </c>
       <c r="R4">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S4">
         <v>3.9</v>
       </c>
       <c r="T4">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="U4">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V4">
         <v>1.37</v>
@@ -1499,7 +1499,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD4">
         <v>15</v>
@@ -1517,10 +1517,10 @@
         <v>18.5</v>
       </c>
       <c r="AI4">
-        <v>580</v>
+        <v>75</v>
       </c>
       <c r="AJ4">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AK4">
         <v>27</v>
@@ -1529,10 +1529,10 @@
         <v>42</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AN4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO4">
         <v>50</v>
@@ -1547,7 +1547,7 @@
         <v>20</v>
       </c>
       <c r="AS4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT4">
         <v>8.4</v>
@@ -1559,7 +1559,7 @@
         <v>13.5</v>
       </c>
       <c r="AW4">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AX4">
         <v>12.5</v>
@@ -1571,85 +1571,85 @@
         <v>16.5</v>
       </c>
       <c r="BA4">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="BB4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BC4">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BD4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BE4">
         <v>40</v>
       </c>
       <c r="BF4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BG4">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BH4">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BM4">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
         <v>112</v>
@@ -1672,22 +1672,22 @@
         <v>105</v>
       </c>
       <c r="F5">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G5">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="H5">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I5">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J5">
         <v>3.6</v>
       </c>
       <c r="K5">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L5">
         <v>1.27</v>
@@ -1708,10 +1708,10 @@
         <v>1.63</v>
       </c>
       <c r="R5">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S5">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="T5">
         <v>1.57</v>
@@ -1720,34 +1720,34 @@
         <v>2.58</v>
       </c>
       <c r="V5">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W5">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="X5">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y5">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z5">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AA5">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AB5">
         <v>15</v>
       </c>
       <c r="AC5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD5">
         <v>18.5</v>
       </c>
       <c r="AE5">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AF5">
         <v>19</v>
@@ -1759,22 +1759,22 @@
         <v>14.5</v>
       </c>
       <c r="AI5">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AJ5">
         <v>30</v>
       </c>
       <c r="AK5">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM5">
         <v>60</v>
       </c>
       <c r="AN5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO5">
         <v>34</v>
@@ -1786,10 +1786,10 @@
         <v>16</v>
       </c>
       <c r="AR5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS5">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT5">
         <v>12.5</v>
@@ -1819,16 +1819,16 @@
         <v>18.5</v>
       </c>
       <c r="BC5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD5">
-        <v>22</v>
+        <v>6.8</v>
       </c>
       <c r="BE5">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF5">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG5">
         <v>20</v>
@@ -1914,19 +1914,19 @@
         <v>106</v>
       </c>
       <c r="F6">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="G6">
         <v>990</v>
       </c>
       <c r="H6">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="I6">
         <v>990</v>
       </c>
       <c r="J6">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -1938,7 +1938,7 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="O6">
         <v>1.01</v>
@@ -2156,22 +2156,22 @@
         <v>107</v>
       </c>
       <c r="F7">
-        <v>1.06</v>
+        <v>1.61</v>
       </c>
       <c r="G7">
         <v>990</v>
       </c>
       <c r="H7">
-        <v>1.05</v>
+        <v>1.59</v>
       </c>
       <c r="I7">
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K7">
-        <v>950</v>
+        <v>3.15</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2312,7 +2312,7 @@
         <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG7">
         <v>1.01</v>
@@ -2401,13 +2401,13 @@
         <v>2.36</v>
       </c>
       <c r="G8">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H8">
         <v>3.45</v>
       </c>
       <c r="I8">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J8">
         <v>3.15</v>
@@ -2422,10 +2422,10 @@
         <v>1.12</v>
       </c>
       <c r="N8">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="O8">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P8">
         <v>1.59</v>
@@ -2455,25 +2455,25 @@
         <v>10.5</v>
       </c>
       <c r="Y8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z8">
         <v>28</v>
       </c>
       <c r="AA8">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AB8">
         <v>8.4</v>
       </c>
       <c r="AC8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD8">
         <v>17</v>
       </c>
       <c r="AE8">
-        <v>65</v>
+        <v>370</v>
       </c>
       <c r="AF8">
         <v>16.5</v>
@@ -2485,7 +2485,7 @@
         <v>25</v>
       </c>
       <c r="AI8">
-        <v>75</v>
+        <v>380</v>
       </c>
       <c r="AJ8">
         <v>40</v>
@@ -2494,13 +2494,13 @@
         <v>38</v>
       </c>
       <c r="AL8">
-        <v>65</v>
+        <v>380</v>
       </c>
       <c r="AM8">
-        <v>190</v>
+        <v>580</v>
       </c>
       <c r="AN8">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AO8">
         <v>1000</v>
@@ -2512,10 +2512,10 @@
         <v>9</v>
       </c>
       <c r="AR8">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="AS8">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT8">
         <v>6.8</v>
@@ -2527,7 +2527,7 @@
         <v>13.5</v>
       </c>
       <c r="AW8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX8">
         <v>12.5</v>
@@ -2542,7 +2542,7 @@
         <v>7.6</v>
       </c>
       <c r="BB8">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="BC8">
         <v>7</v>
@@ -2551,13 +2551,13 @@
         <v>7.4</v>
       </c>
       <c r="BE8">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF8">
         <v>6.8</v>
       </c>
       <c r="BG8">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH8">
         <v>2.8</v>
@@ -2664,25 +2664,25 @@
         <v>1.07</v>
       </c>
       <c r="N9">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O9">
         <v>1.32</v>
       </c>
       <c r="P9">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q9">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="R9">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S9">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T9">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="U9">
         <v>2.18</v>
@@ -2721,7 +2721,7 @@
         <v>13.5</v>
       </c>
       <c r="AG9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH9">
         <v>18</v>
@@ -2739,10 +2739,10 @@
         <v>38</v>
       </c>
       <c r="AM9">
-        <v>95</v>
+        <v>190</v>
       </c>
       <c r="AN9">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AO9">
         <v>48</v>
@@ -2757,28 +2757,28 @@
         <v>23</v>
       </c>
       <c r="AS9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT9">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU9">
         <v>7</v>
       </c>
       <c r="AV9">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW9">
         <v>38</v>
       </c>
       <c r="AX9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY9">
         <v>10</v>
       </c>
       <c r="AZ9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA9">
         <v>46</v>
@@ -2787,19 +2787,19 @@
         <v>24</v>
       </c>
       <c r="BC9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD9">
         <v>32</v>
       </c>
       <c r="BE9">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="BF9">
         <v>16</v>
       </c>
       <c r="BG9">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BH9">
         <v>3.9</v>
@@ -2882,16 +2882,16 @@
         <v>110</v>
       </c>
       <c r="F10">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="G10">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="H10">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="I10">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="J10">
         <v>3.15</v>
@@ -2903,16 +2903,16 @@
         <v>1.56</v>
       </c>
       <c r="M10">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N10">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="O10">
         <v>1.51</v>
       </c>
       <c r="P10">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q10">
         <v>2.58</v>
@@ -2921,55 +2921,55 @@
         <v>1.19</v>
       </c>
       <c r="S10">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="T10">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="U10">
         <v>1.8</v>
       </c>
       <c r="V10">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W10">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="X10">
+        <v>9.6</v>
+      </c>
+      <c r="Y10">
         <v>11</v>
-      </c>
-      <c r="Y10">
-        <v>10.5</v>
       </c>
       <c r="Z10">
         <v>32</v>
       </c>
       <c r="AA10">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="AB10">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC10">
         <v>7.4</v>
       </c>
       <c r="AD10">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AE10">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="AF10">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH10">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI10">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AJ10">
         <v>42</v>
@@ -2978,19 +2978,19 @@
         <v>42</v>
       </c>
       <c r="AL10">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="AM10">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AN10">
         <v>42</v>
       </c>
       <c r="AO10">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AP10">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ10">
         <v>7.2</v>
@@ -2999,22 +2999,22 @@
         <v>18.5</v>
       </c>
       <c r="AS10">
-        <v>8.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="AT10">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU10">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW10">
         <v>38</v>
       </c>
       <c r="AX10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY10">
         <v>10.5</v>
@@ -3023,37 +3023,37 @@
         <v>19.5</v>
       </c>
       <c r="BA10">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB10">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BC10">
         <v>24</v>
       </c>
       <c r="BD10">
+        <v>28</v>
+      </c>
+      <c r="BE10">
         <v>10</v>
-      </c>
-      <c r="BE10">
-        <v>8.800000000000001</v>
       </c>
       <c r="BF10">
         <v>24</v>
       </c>
       <c r="BG10">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH10">
         <v>2.8</v>
       </c>
       <c r="BI10">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BJ10">
         <v>12</v>
       </c>
       <c r="BK10">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL10">
         <v>1000</v>
@@ -3077,19 +3077,19 @@
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT10">
         <v>7.2</v>
       </c>
       <c r="BU10">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX10">
         <v>1000</v>
@@ -3101,7 +3101,7 @@
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB10" t="s">
         <v>112</v>
@@ -3124,22 +3124,22 @@
         <v>111</v>
       </c>
       <c r="F11">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G11">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="H11">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I11">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="J11">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K11">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L11">
         <v>1.51</v>
@@ -3148,49 +3148,49 @@
         <v>1.1</v>
       </c>
       <c r="N11">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="O11">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="P11">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="Q11">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="R11">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S11">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="T11">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U11">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="V11">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W11">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="X11">
         <v>13</v>
       </c>
       <c r="Y11">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="Z11">
         <v>36</v>
       </c>
       <c r="AA11">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="AB11">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC11">
         <v>9</v>
@@ -3199,7 +3199,7 @@
         <v>22</v>
       </c>
       <c r="AE11">
-        <v>55</v>
+        <v>370</v>
       </c>
       <c r="AF11">
         <v>13.5</v>
@@ -3220,40 +3220,40 @@
         <v>36</v>
       </c>
       <c r="AL11">
-        <v>48</v>
+        <v>290</v>
       </c>
       <c r="AM11">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN11">
         <v>32</v>
       </c>
       <c r="AO11">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AP11">
         <v>9.4</v>
       </c>
       <c r="AQ11">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR11">
         <v>20</v>
       </c>
       <c r="AS11">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT11">
         <v>7.2</v>
       </c>
       <c r="AU11">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV11">
         <v>14</v>
       </c>
       <c r="AW11">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX11">
         <v>11.5</v>
@@ -3262,10 +3262,10 @@
         <v>10</v>
       </c>
       <c r="AZ11">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA11">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB11">
         <v>24</v>
@@ -3274,16 +3274,16 @@
         <v>22</v>
       </c>
       <c r="BD11">
-        <v>6.6</v>
+        <v>23</v>
       </c>
       <c r="BE11">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF11">
         <v>18.5</v>
       </c>
       <c r="BG11">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH11">
         <v>2.96</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -352,7 +352,7 @@
     <t>America MG</t>
   </si>
   <si>
-    <t>2026-07-20 20:33:00</t>
+    <t>2026-07-20 22:39:05</t>
   </si>
 </sst>
 </file>
@@ -955,13 +955,13 @@
         <v>4</v>
       </c>
       <c r="I2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J2">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K2">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L2">
         <v>1.44</v>
@@ -973,10 +973,10 @@
         <v>3.6</v>
       </c>
       <c r="O2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P2">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q2">
         <v>2.04</v>
@@ -985,37 +985,37 @@
         <v>1.34</v>
       </c>
       <c r="S2">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T2">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U2">
         <v>2.08</v>
       </c>
       <c r="V2">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W2">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="X2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y2">
         <v>14.5</v>
       </c>
       <c r="Z2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA2">
         <v>160</v>
       </c>
       <c r="AB2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD2">
         <v>16.5</v>
@@ -1033,7 +1033,7 @@
         <v>19</v>
       </c>
       <c r="AI2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AJ2">
         <v>25</v>
@@ -1048,40 +1048,40 @@
         <v>110</v>
       </c>
       <c r="AN2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO2">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AP2">
         <v>12</v>
       </c>
       <c r="AQ2">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS2">
         <v>55</v>
       </c>
       <c r="AT2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU2">
         <v>7.4</v>
       </c>
       <c r="AV2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AX2">
         <v>11.5</v>
       </c>
       <c r="AY2">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2">
         <v>17</v>
@@ -1096,52 +1096,52 @@
         <v>21</v>
       </c>
       <c r="BD2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE2">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="BF2">
         <v>14.5</v>
       </c>
       <c r="BG2">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BH2">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BI2">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ2">
         <v>9.800000000000001</v>
       </c>
       <c r="BK2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BN2">
         <v>4.8</v>
       </c>
       <c r="BO2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BQ2">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS2">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BT2">
         <v>7.2</v>
@@ -1150,22 +1150,22 @@
         <v>5.8</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW2">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY2">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA2">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="CB2" t="s">
         <v>112</v>
@@ -1188,19 +1188,19 @@
         <v>103</v>
       </c>
       <c r="F3">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H3">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="I3">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="J3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K3">
         <v>3.45</v>
@@ -1209,7 +1209,7 @@
         <v>1.58</v>
       </c>
       <c r="M3">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N3">
         <v>2.78</v>
@@ -1221,22 +1221,22 @@
         <v>1.61</v>
       </c>
       <c r="Q3">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="R3">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S3">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="T3">
         <v>2.18</v>
       </c>
       <c r="U3">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V3">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W3">
         <v>1.33</v>
@@ -1254,7 +1254,7 @@
         <v>29</v>
       </c>
       <c r="AB3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC3">
         <v>7.6</v>
@@ -1269,7 +1269,7 @@
         <v>26</v>
       </c>
       <c r="AG3">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH3">
         <v>24</v>
@@ -1296,16 +1296,16 @@
         <v>28</v>
       </c>
       <c r="AP3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ3">
         <v>6.8</v>
       </c>
       <c r="AR3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT3">
         <v>10</v>
@@ -1323,13 +1323,13 @@
         <v>23</v>
       </c>
       <c r="AY3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AZ3">
         <v>21</v>
       </c>
       <c r="BA3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BB3">
         <v>75</v>
@@ -1338,22 +1338,22 @@
         <v>55</v>
       </c>
       <c r="BD3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BE3">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="BF3">
         <v>70</v>
       </c>
       <c r="BG3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BH3">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="BI3">
-        <v>2.42</v>
+        <v>2.64</v>
       </c>
       <c r="BJ3">
         <v>11</v>
@@ -1365,49 +1365,49 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BN3">
         <v>7.2</v>
       </c>
       <c r="BO3">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BP3">
         <v>40</v>
       </c>
       <c r="BQ3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BR3">
         <v>60</v>
       </c>
       <c r="BS3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BT3">
         <v>4.8</v>
       </c>
       <c r="BU3">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BV3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BW3">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BX3">
         <v>40</v>
       </c>
       <c r="BY3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BZ3">
         <v>42</v>
       </c>
       <c r="CA3">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="CB3" t="s">
         <v>112</v>
@@ -1430,16 +1430,16 @@
         <v>104</v>
       </c>
       <c r="F4">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G4">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H4">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I4">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J4">
         <v>3.35</v>
@@ -1448,19 +1448,19 @@
         <v>3.55</v>
       </c>
       <c r="L4">
-        <v>1.17</v>
+        <v>1.45</v>
       </c>
       <c r="M4">
         <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O4">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P4">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q4">
         <v>2.12</v>
@@ -1472,25 +1472,25 @@
         <v>3.9</v>
       </c>
       <c r="T4">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U4">
         <v>2.08</v>
       </c>
       <c r="V4">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W4">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="X4">
         <v>12.5</v>
       </c>
       <c r="Y4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA4">
         <v>70</v>
@@ -1511,7 +1511,7 @@
         <v>14.5</v>
       </c>
       <c r="AG4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH4">
         <v>18.5</v>
@@ -1520,7 +1520,7 @@
         <v>75</v>
       </c>
       <c r="AJ4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK4">
         <v>27</v>
@@ -1541,10 +1541,10 @@
         <v>11</v>
       </c>
       <c r="AQ4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS4">
         <v>32</v>
@@ -1571,7 +1571,7 @@
         <v>16.5</v>
       </c>
       <c r="BA4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB4">
         <v>24</v>
@@ -1580,10 +1580,10 @@
         <v>21</v>
       </c>
       <c r="BD4">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BE4">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BF4">
         <v>19.5</v>
@@ -1592,64 +1592,64 @@
         <v>30</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>14</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="CB4" t="s">
         <v>112</v>
@@ -1684,10 +1684,10 @@
         <v>3.9</v>
       </c>
       <c r="J5">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K5">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L5">
         <v>1.27</v>
@@ -1702,16 +1702,16 @@
         <v>1.21</v>
       </c>
       <c r="P5">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q5">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R5">
         <v>1.59</v>
       </c>
       <c r="S5">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="T5">
         <v>1.57</v>
@@ -1729,7 +1729,7 @@
         <v>21</v>
       </c>
       <c r="Y5">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z5">
         <v>65</v>
@@ -1765,10 +1765,10 @@
         <v>30</v>
       </c>
       <c r="AK5">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL5">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AM5">
         <v>60</v>
@@ -1789,7 +1789,7 @@
         <v>7</v>
       </c>
       <c r="AS5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT5">
         <v>12.5</v>
@@ -1914,19 +1914,19 @@
         <v>106</v>
       </c>
       <c r="F6">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="G6">
         <v>990</v>
       </c>
       <c r="H6">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="I6">
         <v>990</v>
       </c>
       <c r="J6">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2156,19 +2156,19 @@
         <v>107</v>
       </c>
       <c r="F7">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="G7">
         <v>990</v>
       </c>
       <c r="H7">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="I7">
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="K7">
         <v>3.15</v>
@@ -2398,7 +2398,7 @@
         <v>108</v>
       </c>
       <c r="F8">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G8">
         <v>2.5</v>
@@ -2407,19 +2407,19 @@
         <v>3.45</v>
       </c>
       <c r="I8">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J8">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K8">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L8">
         <v>1.58</v>
       </c>
       <c r="M8">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N8">
         <v>2.74</v>
@@ -2431,7 +2431,7 @@
         <v>1.59</v>
       </c>
       <c r="Q8">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R8">
         <v>1.21</v>
@@ -2467,7 +2467,7 @@
         <v>8.4</v>
       </c>
       <c r="AC8">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD8">
         <v>17</v>
@@ -2515,7 +2515,7 @@
         <v>10.5</v>
       </c>
       <c r="AS8">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT8">
         <v>6.8</v>
@@ -2527,7 +2527,7 @@
         <v>13.5</v>
       </c>
       <c r="AW8">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX8">
         <v>12.5</v>
@@ -2539,25 +2539,25 @@
         <v>19</v>
       </c>
       <c r="BA8">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB8">
         <v>14.5</v>
       </c>
       <c r="BC8">
+        <v>7.2</v>
+      </c>
+      <c r="BD8">
+        <v>7.8</v>
+      </c>
+      <c r="BE8">
+        <v>8.4</v>
+      </c>
+      <c r="BF8">
         <v>7</v>
       </c>
-      <c r="BD8">
-        <v>7.4</v>
-      </c>
-      <c r="BE8">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF8">
-        <v>6.8</v>
-      </c>
       <c r="BG8">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH8">
         <v>2.8</v>
@@ -2652,13 +2652,13 @@
         <v>3.8</v>
       </c>
       <c r="J9">
+        <v>3.5</v>
+      </c>
+      <c r="K9">
         <v>3.55</v>
       </c>
-      <c r="K9">
-        <v>3.6</v>
-      </c>
       <c r="L9">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M9">
         <v>1.07</v>
@@ -2691,13 +2691,13 @@
         <v>1.35</v>
       </c>
       <c r="W9">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="X9">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y9">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Z9">
         <v>27</v>
@@ -2706,7 +2706,7 @@
         <v>70</v>
       </c>
       <c r="AB9">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC9">
         <v>7.8</v>
@@ -2751,13 +2751,13 @@
         <v>12.5</v>
       </c>
       <c r="AQ9">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR9">
         <v>23</v>
       </c>
       <c r="AS9">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT9">
         <v>9.199999999999999</v>
@@ -2796,7 +2796,7 @@
         <v>75</v>
       </c>
       <c r="BF9">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BG9">
         <v>38</v>
@@ -2885,7 +2885,7 @@
         <v>2.34</v>
       </c>
       <c r="G10">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H10">
         <v>3.75</v>
@@ -2903,28 +2903,28 @@
         <v>1.56</v>
       </c>
       <c r="M10">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N10">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="O10">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P10">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q10">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R10">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S10">
         <v>5.4</v>
       </c>
       <c r="T10">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U10">
         <v>1.8</v>
@@ -2936,16 +2936,16 @@
         <v>1.72</v>
       </c>
       <c r="X10">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>11</v>
       </c>
       <c r="Z10">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AA10">
-        <v>900</v>
+        <v>85</v>
       </c>
       <c r="AB10">
         <v>7.6</v>
@@ -2954,13 +2954,13 @@
         <v>7.4</v>
       </c>
       <c r="AD10">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE10">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AF10">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG10">
         <v>12.5</v>
@@ -2969,79 +2969,79 @@
         <v>25</v>
       </c>
       <c r="AI10">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AJ10">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AK10">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AL10">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AM10">
         <v>500</v>
       </c>
       <c r="AN10">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AO10">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AP10">
         <v>8.199999999999999</v>
       </c>
       <c r="AQ10">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="AR10">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AS10">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="AT10">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU10">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV10">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW10">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AX10">
+        <v>11.5</v>
+      </c>
+      <c r="AY10">
         <v>11</v>
       </c>
-      <c r="AY10">
-        <v>10.5</v>
-      </c>
       <c r="AZ10">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BA10">
-        <v>9.4</v>
+        <v>60</v>
       </c>
       <c r="BB10">
         <v>23</v>
       </c>
       <c r="BC10">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="BD10">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="BE10">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BF10">
         <v>24</v>
       </c>
       <c r="BG10">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="BH10">
         <v>2.8</v>
@@ -3148,7 +3148,7 @@
         <v>1.1</v>
       </c>
       <c r="N11">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="O11">
         <v>1.47</v>
@@ -3157,19 +3157,19 @@
         <v>1.66</v>
       </c>
       <c r="Q11">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="R11">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S11">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T11">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U11">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="V11">
         <v>1.35</v>
@@ -3190,7 +3190,7 @@
         <v>900</v>
       </c>
       <c r="AB11">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC11">
         <v>9</v>
@@ -3202,7 +3202,7 @@
         <v>370</v>
       </c>
       <c r="AF11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG11">
         <v>13</v>
@@ -3220,7 +3220,7 @@
         <v>36</v>
       </c>
       <c r="AL11">
-        <v>290</v>
+        <v>110</v>
       </c>
       <c r="AM11">
         <v>580</v>
@@ -3235,7 +3235,7 @@
         <v>9.4</v>
       </c>
       <c r="AQ11">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR11">
         <v>20</v>
@@ -3247,10 +3247,10 @@
         <v>7.2</v>
       </c>
       <c r="AU11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV11">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AW11">
         <v>7.4</v>
@@ -3283,7 +3283,7 @@
         <v>18.5</v>
       </c>
       <c r="BG11">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BH11">
         <v>2.96</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -352,7 +352,7 @@
     <t>America MG</t>
   </si>
   <si>
-    <t>2026-07-20 22:39:05</t>
+    <t>2026-07-21 00:46:03</t>
   </si>
 </sst>
 </file>
@@ -946,16 +946,16 @@
         <v>102</v>
       </c>
       <c r="F2">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G2">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H2">
         <v>4</v>
       </c>
       <c r="I2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J2">
         <v>3.6</v>
@@ -970,13 +970,13 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O2">
         <v>1.35</v>
       </c>
       <c r="P2">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q2">
         <v>2.04</v>
@@ -988,37 +988,37 @@
         <v>3.75</v>
       </c>
       <c r="T2">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U2">
         <v>2.08</v>
       </c>
       <c r="V2">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="X2">
         <v>13</v>
       </c>
       <c r="Y2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA2">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="AB2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC2">
         <v>8</v>
       </c>
       <c r="AD2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE2">
         <v>55</v>
@@ -1030,10 +1030,10 @@
         <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ2">
         <v>25</v>
@@ -1045,13 +1045,13 @@
         <v>40</v>
       </c>
       <c r="AM2">
-        <v>110</v>
+        <v>310</v>
       </c>
       <c r="AN2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO2">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="AP2">
         <v>12</v>
@@ -1063,7 +1063,7 @@
         <v>27</v>
       </c>
       <c r="AS2">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AT2">
         <v>8.199999999999999</v>
@@ -1078,16 +1078,16 @@
         <v>46</v>
       </c>
       <c r="AX2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2">
         <v>17</v>
       </c>
       <c r="BA2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB2">
         <v>22</v>
@@ -1099,40 +1099,40 @@
         <v>36</v>
       </c>
       <c r="BE2">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="BF2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG2">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="BH2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI2">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BJ2">
         <v>9.800000000000001</v>
       </c>
       <c r="BK2">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
+        <v>18</v>
+      </c>
+      <c r="BN2">
+        <v>4.7</v>
+      </c>
+      <c r="BO2">
+        <v>4.4</v>
+      </c>
+      <c r="BP2">
         <v>15</v>
-      </c>
-      <c r="BN2">
-        <v>4.8</v>
-      </c>
-      <c r="BO2">
-        <v>4.3</v>
-      </c>
-      <c r="BP2">
-        <v>15.5</v>
       </c>
       <c r="BQ2">
         <v>9.6</v>
@@ -1141,31 +1141,31 @@
         <v>30</v>
       </c>
       <c r="BS2">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BT2">
         <v>7.2</v>
       </c>
       <c r="BU2">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BV2">
         <v>34</v>
       </c>
       <c r="BW2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BX2">
         <v>46</v>
       </c>
       <c r="BY2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BZ2">
         <v>27</v>
       </c>
       <c r="CA2">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="CB2" t="s">
         <v>112</v>
@@ -1188,19 +1188,19 @@
         <v>103</v>
       </c>
       <c r="F3">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="G3">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>2.18</v>
       </c>
       <c r="I3">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J3">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K3">
         <v>3.45</v>
@@ -1209,25 +1209,25 @@
         <v>1.58</v>
       </c>
       <c r="M3">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N3">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O3">
         <v>1.52</v>
       </c>
       <c r="P3">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q3">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R3">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S3">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T3">
         <v>2.18</v>
@@ -1236,7 +1236,7 @@
         <v>1.81</v>
       </c>
       <c r="V3">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="W3">
         <v>1.33</v>
@@ -1266,7 +1266,7 @@
         <v>30</v>
       </c>
       <c r="AF3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG3">
         <v>17.5</v>
@@ -1275,10 +1275,10 @@
         <v>24</v>
       </c>
       <c r="AI3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ3">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AK3">
         <v>65</v>
@@ -1296,7 +1296,7 @@
         <v>28</v>
       </c>
       <c r="AP3">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ3">
         <v>6.8</v>
@@ -1305,7 +1305,7 @@
         <v>10.5</v>
       </c>
       <c r="AS3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT3">
         <v>10</v>
@@ -1329,7 +1329,7 @@
         <v>21</v>
       </c>
       <c r="BA3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB3">
         <v>75</v>
@@ -1341,73 +1341,73 @@
         <v>70</v>
       </c>
       <c r="BE3">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BF3">
         <v>70</v>
       </c>
       <c r="BG3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH3">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="BI3">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="BJ3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK3">
+        <v>9.6</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>21</v>
+      </c>
+      <c r="BN3">
         <v>7</v>
       </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>17</v>
-      </c>
-      <c r="BN3">
-        <v>7.2</v>
-      </c>
       <c r="BO3">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BP3">
         <v>40</v>
       </c>
       <c r="BQ3">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BR3">
         <v>60</v>
       </c>
       <c r="BS3">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BT3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BU3">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV3">
         <v>18</v>
       </c>
       <c r="BW3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BX3">
         <v>40</v>
       </c>
       <c r="BY3">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BZ3">
         <v>42</v>
       </c>
       <c r="CA3">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="CB3" t="s">
         <v>112</v>
@@ -1430,16 +1430,16 @@
         <v>104</v>
       </c>
       <c r="F4">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="G4">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H4">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I4">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J4">
         <v>3.35</v>
@@ -1448,34 +1448,34 @@
         <v>3.55</v>
       </c>
       <c r="L4">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M4">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N4">
         <v>3.4</v>
       </c>
       <c r="O4">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P4">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q4">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R4">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S4">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T4">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U4">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V4">
         <v>1.36</v>
@@ -1484,10 +1484,10 @@
         <v>1.75</v>
       </c>
       <c r="X4">
+        <v>12</v>
+      </c>
+      <c r="Y4">
         <v>12.5</v>
-      </c>
-      <c r="Y4">
-        <v>13</v>
       </c>
       <c r="Z4">
         <v>25</v>
@@ -1496,25 +1496,25 @@
         <v>70</v>
       </c>
       <c r="AB4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC4">
         <v>7.6</v>
       </c>
       <c r="AD4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE4">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG4">
         <v>11</v>
       </c>
       <c r="AH4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI4">
         <v>75</v>
@@ -1535,22 +1535,22 @@
         <v>22</v>
       </c>
       <c r="AO4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4">
         <v>11.5</v>
       </c>
       <c r="AR4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS4">
         <v>32</v>
       </c>
       <c r="AT4">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU4">
         <v>7</v>
@@ -1562,10 +1562,10 @@
         <v>32</v>
       </c>
       <c r="AX4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ4">
         <v>16.5</v>
@@ -1574,82 +1574,82 @@
         <v>42</v>
       </c>
       <c r="BB4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BC4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD4">
         <v>36</v>
       </c>
       <c r="BE4">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="BF4">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH4">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI4">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="BJ4">
         <v>10</v>
       </c>
       <c r="BK4">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL4">
         <v>140</v>
       </c>
       <c r="BM4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BN4">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO4">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BP4">
         <v>17.5</v>
       </c>
       <c r="BQ4">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR4">
         <v>34</v>
       </c>
       <c r="BS4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT4">
         <v>6.8</v>
       </c>
       <c r="BU4">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BV4">
         <v>30</v>
       </c>
       <c r="BW4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BX4">
         <v>44</v>
       </c>
       <c r="BY4">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ4">
         <v>32</v>
       </c>
       <c r="CA4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB4" t="s">
         <v>112</v>
@@ -1672,7 +1672,7 @@
         <v>105</v>
       </c>
       <c r="F5">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G5">
         <v>2.18</v>
@@ -1684,7 +1684,7 @@
         <v>3.9</v>
       </c>
       <c r="J5">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K5">
         <v>3.9</v>
@@ -1696,22 +1696,22 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O5">
         <v>1.21</v>
       </c>
       <c r="P5">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q5">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R5">
         <v>1.59</v>
       </c>
       <c r="S5">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T5">
         <v>1.57</v>
@@ -1768,7 +1768,7 @@
         <v>19</v>
       </c>
       <c r="AL5">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="AM5">
         <v>60</v>
@@ -1786,10 +1786,10 @@
         <v>16</v>
       </c>
       <c r="AR5">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AS5">
-        <v>8.199999999999999</v>
+        <v>25</v>
       </c>
       <c r="AT5">
         <v>12.5</v>
@@ -1798,7 +1798,7 @@
         <v>7.8</v>
       </c>
       <c r="AV5">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AW5">
         <v>27</v>
@@ -1810,7 +1810,7 @@
         <v>10</v>
       </c>
       <c r="AZ5">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BA5">
         <v>32</v>
@@ -1831,13 +1831,13 @@
         <v>9.4</v>
       </c>
       <c r="BG5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI5">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BJ5">
         <v>8.800000000000001</v>
@@ -1864,10 +1864,10 @@
         <v>7.4</v>
       </c>
       <c r="BR5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS5">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BT5">
         <v>7.2</v>
@@ -1876,13 +1876,13 @@
         <v>5.2</v>
       </c>
       <c r="BV5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BW5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX5">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
         <v>10.5</v>
@@ -1914,19 +1914,19 @@
         <v>106</v>
       </c>
       <c r="F6">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="G6">
         <v>990</v>
       </c>
       <c r="H6">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="I6">
         <v>990</v>
       </c>
       <c r="J6">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -1965,7 +1965,7 @@
         <v>1.02</v>
       </c>
       <c r="W6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2156,19 +2156,19 @@
         <v>107</v>
       </c>
       <c r="F7">
-        <v>1.32</v>
+        <v>1.69</v>
       </c>
       <c r="G7">
         <v>990</v>
       </c>
       <c r="H7">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I7">
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="K7">
         <v>3.15</v>
@@ -2401,13 +2401,13 @@
         <v>2.34</v>
       </c>
       <c r="G8">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H8">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="I8">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="J8">
         <v>3.05</v>
@@ -2422,7 +2422,7 @@
         <v>1.11</v>
       </c>
       <c r="N8">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="O8">
         <v>1.51</v>
@@ -2440,16 +2440,16 @@
         <v>5</v>
       </c>
       <c r="T8">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U8">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V8">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W8">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="X8">
         <v>10.5</v>
@@ -2485,13 +2485,13 @@
         <v>25</v>
       </c>
       <c r="AI8">
-        <v>380</v>
+        <v>500</v>
       </c>
       <c r="AJ8">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AK8">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AL8">
         <v>380</v>
@@ -2512,10 +2512,10 @@
         <v>9</v>
       </c>
       <c r="AR8">
-        <v>10.5</v>
+        <v>21</v>
       </c>
       <c r="AS8">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT8">
         <v>6.8</v>
@@ -2527,7 +2527,7 @@
         <v>13.5</v>
       </c>
       <c r="AW8">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX8">
         <v>12.5</v>
@@ -2548,34 +2548,34 @@
         <v>7.2</v>
       </c>
       <c r="BD8">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF8">
+        <v>7.2</v>
+      </c>
+      <c r="BG8">
         <v>8.4</v>
-      </c>
-      <c r="BF8">
-        <v>7</v>
-      </c>
-      <c r="BG8">
-        <v>8</v>
       </c>
       <c r="BH8">
         <v>2.8</v>
       </c>
       <c r="BI8">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ8">
         <v>11</v>
       </c>
       <c r="BK8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN8">
         <v>5.1</v>
@@ -2593,7 +2593,7 @@
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT8">
         <v>6.6</v>
@@ -2611,13 +2611,13 @@
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CB8" t="s">
         <v>112</v>
@@ -2649,13 +2649,13 @@
         <v>3.7</v>
       </c>
       <c r="I9">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J9">
         <v>3.5</v>
       </c>
       <c r="K9">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L9">
         <v>1.35</v>
@@ -2670,7 +2670,7 @@
         <v>1.32</v>
       </c>
       <c r="P9">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -2679,19 +2679,19 @@
         <v>1.36</v>
       </c>
       <c r="S9">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T9">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U9">
         <v>2.18</v>
       </c>
       <c r="V9">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W9">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X9">
         <v>14.5</v>
@@ -2706,13 +2706,13 @@
         <v>70</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC9">
         <v>7.8</v>
       </c>
       <c r="AD9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE9">
         <v>50</v>
@@ -2760,7 +2760,7 @@
         <v>60</v>
       </c>
       <c r="AT9">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU9">
         <v>7</v>
@@ -2796,13 +2796,13 @@
         <v>75</v>
       </c>
       <c r="BF9">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BG9">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BH9">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BI9">
         <v>2.78</v>
@@ -2811,13 +2811,13 @@
         <v>13</v>
       </c>
       <c r="BK9">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BN9">
         <v>6.6</v>
@@ -2829,13 +2829,13 @@
         <v>22</v>
       </c>
       <c r="BQ9">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BR9">
         <v>40</v>
       </c>
       <c r="BS9">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BT9">
         <v>9.199999999999999</v>
@@ -2847,19 +2847,19 @@
         <v>40</v>
       </c>
       <c r="BW9">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BZ9">
         <v>36</v>
       </c>
       <c r="CA9">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="CB9" t="s">
         <v>112</v>
@@ -2882,13 +2882,13 @@
         <v>110</v>
       </c>
       <c r="F10">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G10">
         <v>2.4</v>
       </c>
       <c r="H10">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I10">
         <v>3.85</v>
@@ -2906,7 +2906,7 @@
         <v>1.12</v>
       </c>
       <c r="N10">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="O10">
         <v>1.52</v>
@@ -2915,7 +2915,7 @@
         <v>1.55</v>
       </c>
       <c r="Q10">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="R10">
         <v>1.2</v>
@@ -2924,7 +2924,7 @@
         <v>5.4</v>
       </c>
       <c r="T10">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U10">
         <v>1.8</v>
@@ -2933,7 +2933,7 @@
         <v>1.35</v>
       </c>
       <c r="W10">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -2969,7 +2969,7 @@
         <v>25</v>
       </c>
       <c r="AI10">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="AJ10">
         <v>34</v>
@@ -2987,10 +2987,10 @@
         <v>34</v>
       </c>
       <c r="AO10">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AP10">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ10">
         <v>9.4</v>
@@ -3041,10 +3041,10 @@
         <v>24</v>
       </c>
       <c r="BG10">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH10">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BI10">
         <v>2.46</v>
@@ -3053,13 +3053,13 @@
         <v>12</v>
       </c>
       <c r="BK10">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN10">
         <v>5.1</v>
@@ -3071,13 +3071,13 @@
         <v>21</v>
       </c>
       <c r="BQ10">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT10">
         <v>7.2</v>
@@ -3089,19 +3089,19 @@
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
         <v>9.4</v>
-      </c>
-      <c r="BZ10">
-        <v>1000</v>
-      </c>
-      <c r="CA10">
-        <v>9.199999999999999</v>
       </c>
       <c r="CB10" t="s">
         <v>112</v>
@@ -3127,13 +3127,13 @@
         <v>2.26</v>
       </c>
       <c r="G11">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H11">
+        <v>3.65</v>
+      </c>
+      <c r="I11">
         <v>3.8</v>
-      </c>
-      <c r="I11">
-        <v>3.85</v>
       </c>
       <c r="J11">
         <v>3.35</v>
@@ -3148,10 +3148,10 @@
         <v>1.1</v>
       </c>
       <c r="N11">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="O11">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P11">
         <v>1.66</v>
@@ -3160,10 +3160,10 @@
         <v>2.42</v>
       </c>
       <c r="R11">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S11">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T11">
         <v>2.04</v>
@@ -3175,7 +3175,7 @@
         <v>1.35</v>
       </c>
       <c r="W11">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="X11">
         <v>13</v>
@@ -3184,7 +3184,7 @@
         <v>11</v>
       </c>
       <c r="Z11">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="AA11">
         <v>900</v>
@@ -3235,13 +3235,13 @@
         <v>9.4</v>
       </c>
       <c r="AQ11">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR11">
         <v>20</v>
       </c>
       <c r="AS11">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT11">
         <v>7.2</v>
@@ -3250,10 +3250,10 @@
         <v>7</v>
       </c>
       <c r="AV11">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AW11">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX11">
         <v>11.5</v>
@@ -3265,10 +3265,10 @@
         <v>18</v>
       </c>
       <c r="BA11">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB11">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="BC11">
         <v>22</v>
@@ -3277,13 +3277,13 @@
         <v>23</v>
       </c>
       <c r="BE11">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF11">
         <v>18.5</v>
       </c>
       <c r="BG11">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH11">
         <v>2.96</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -352,7 +352,7 @@
     <t>America MG</t>
   </si>
   <si>
-    <t>2026-07-21 00:46:03</t>
+    <t>2026-07-21 02:53:07</t>
   </si>
 </sst>
 </file>
@@ -946,70 +946,70 @@
         <v>102</v>
       </c>
       <c r="F2">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G2">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H2">
         <v>4</v>
       </c>
       <c r="I2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K2">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L2">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M2">
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O2">
         <v>1.35</v>
       </c>
       <c r="P2">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q2">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R2">
         <v>1.34</v>
       </c>
       <c r="S2">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T2">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U2">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V2">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W2">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="X2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y2">
         <v>15</v>
       </c>
       <c r="Z2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA2">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB2">
         <v>8.800000000000001</v>
@@ -1033,10 +1033,10 @@
         <v>18.5</v>
       </c>
       <c r="AI2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK2">
         <v>23</v>
@@ -1060,10 +1060,10 @@
         <v>13.5</v>
       </c>
       <c r="AR2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS2">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AT2">
         <v>8.199999999999999</v>
@@ -1078,22 +1078,22 @@
         <v>46</v>
       </c>
       <c r="AX2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2">
         <v>17</v>
       </c>
       <c r="BA2">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BB2">
         <v>22</v>
       </c>
       <c r="BC2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD2">
         <v>36</v>
@@ -1102,16 +1102,16 @@
         <v>50</v>
       </c>
       <c r="BF2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BG2">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BH2">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI2">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ2">
         <v>9.800000000000001</v>
@@ -1123,13 +1123,13 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BN2">
         <v>4.7</v>
       </c>
       <c r="BO2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP2">
         <v>15</v>
@@ -1141,31 +1141,31 @@
         <v>30</v>
       </c>
       <c r="BS2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT2">
         <v>7.2</v>
       </c>
       <c r="BU2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV2">
         <v>34</v>
       </c>
       <c r="BW2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BX2">
         <v>46</v>
       </c>
       <c r="BY2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BZ2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CA2">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="CB2" t="s">
         <v>112</v>
@@ -1188,31 +1188,31 @@
         <v>103</v>
       </c>
       <c r="F3">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="H3">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="I3">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K3">
         <v>3.45</v>
       </c>
       <c r="L3">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M3">
         <v>1.12</v>
       </c>
       <c r="N3">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O3">
         <v>1.52</v>
@@ -1221,13 +1221,13 @@
         <v>1.6</v>
       </c>
       <c r="Q3">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="R3">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S3">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T3">
         <v>2.18</v>
@@ -1236,10 +1236,10 @@
         <v>1.81</v>
       </c>
       <c r="V3">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="W3">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="X3">
         <v>9.4</v>
@@ -1281,16 +1281,16 @@
         <v>95</v>
       </c>
       <c r="AK3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AL3">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AM3">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN3">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AO3">
         <v>28</v>
@@ -1341,25 +1341,25 @@
         <v>70</v>
       </c>
       <c r="BE3">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BF3">
         <v>70</v>
       </c>
       <c r="BG3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH3">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="BI3">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="BJ3">
         <v>11.5</v>
       </c>
       <c r="BK3">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1377,10 +1377,10 @@
         <v>40</v>
       </c>
       <c r="BQ3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BR3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BS3">
         <v>17</v>
@@ -1398,13 +1398,13 @@
         <v>10</v>
       </c>
       <c r="BX3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY3">
         <v>15</v>
       </c>
       <c r="BZ3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="CA3">
         <v>15</v>
@@ -1430,55 +1430,55 @@
         <v>104</v>
       </c>
       <c r="F4">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="G4">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H4">
         <v>3.6</v>
       </c>
       <c r="I4">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J4">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K4">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L4">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M4">
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O4">
         <v>1.39</v>
       </c>
       <c r="P4">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q4">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R4">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T4">
         <v>1.9</v>
       </c>
       <c r="U4">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V4">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W4">
         <v>1.75</v>
@@ -1490,7 +1490,7 @@
         <v>12.5</v>
       </c>
       <c r="Z4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA4">
         <v>70</v>
@@ -1526,13 +1526,13 @@
         <v>27</v>
       </c>
       <c r="AL4">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM4">
-        <v>440</v>
+        <v>120</v>
       </c>
       <c r="AN4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO4">
         <v>55</v>
@@ -1541,7 +1541,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR4">
         <v>22</v>
@@ -1550,7 +1550,7 @@
         <v>32</v>
       </c>
       <c r="AT4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU4">
         <v>7</v>
@@ -1565,13 +1565,13 @@
         <v>12</v>
       </c>
       <c r="AY4">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4">
         <v>16.5</v>
       </c>
       <c r="BA4">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB4">
         <v>26</v>
@@ -1586,70 +1586,70 @@
         <v>65</v>
       </c>
       <c r="BF4">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BG4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI4">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BJ4">
         <v>10</v>
       </c>
       <c r="BK4">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="BL4">
         <v>140</v>
       </c>
       <c r="BM4">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BN4">
         <v>5</v>
       </c>
       <c r="BO4">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP4">
         <v>17.5</v>
       </c>
       <c r="BQ4">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BR4">
         <v>34</v>
       </c>
       <c r="BS4">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BT4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU4">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BV4">
         <v>30</v>
       </c>
       <c r="BW4">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BX4">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BY4">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BZ4">
         <v>32</v>
       </c>
       <c r="CA4">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="CB4" t="s">
         <v>112</v>
@@ -1675,79 +1675,79 @@
         <v>2.1</v>
       </c>
       <c r="G5">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H5">
+        <v>3.75</v>
+      </c>
+      <c r="I5">
+        <v>3.95</v>
+      </c>
+      <c r="J5">
         <v>3.65</v>
       </c>
-      <c r="I5">
-        <v>3.9</v>
-      </c>
-      <c r="J5">
-        <v>3.7</v>
-      </c>
       <c r="K5">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L5">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="M5">
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="O5">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P5">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="Q5">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R5">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S5">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="T5">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="U5">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="V5">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W5">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X5">
         <v>21</v>
       </c>
       <c r="Y5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z5">
+        <v>32</v>
+      </c>
+      <c r="AA5">
         <v>65</v>
-      </c>
-      <c r="AA5">
-        <v>150</v>
       </c>
       <c r="AB5">
         <v>15</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5">
         <v>18.5</v>
       </c>
       <c r="AE5">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="AF5">
         <v>19</v>
@@ -1759,7 +1759,7 @@
         <v>14.5</v>
       </c>
       <c r="AI5">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="AJ5">
         <v>30</v>
@@ -1768,7 +1768,7 @@
         <v>19</v>
       </c>
       <c r="AL5">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AM5">
         <v>60</v>
@@ -1783,16 +1783,16 @@
         <v>17.5</v>
       </c>
       <c r="AQ5">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AR5">
-        <v>11.5</v>
+        <v>25</v>
       </c>
       <c r="AS5">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="AT5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU5">
         <v>7.8</v>
@@ -1801,10 +1801,10 @@
         <v>14.5</v>
       </c>
       <c r="AW5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AX5">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY5">
         <v>10</v>
@@ -1816,22 +1816,22 @@
         <v>32</v>
       </c>
       <c r="BB5">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BC5">
         <v>17</v>
       </c>
       <c r="BD5">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="BE5">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="BF5">
         <v>9.4</v>
       </c>
       <c r="BG5">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BH5">
         <v>4.2</v>
@@ -1840,16 +1840,16 @@
         <v>3.8</v>
       </c>
       <c r="BJ5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK5">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BN5">
         <v>5.3</v>
@@ -1861,37 +1861,37 @@
         <v>14</v>
       </c>
       <c r="BQ5">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BR5">
         <v>23</v>
       </c>
       <c r="BS5">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT5">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU5">
         <v>5.2</v>
       </c>
       <c r="BV5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW5">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY5">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CA5">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="CB5" t="s">
         <v>112</v>
@@ -1914,166 +1914,166 @@
         <v>106</v>
       </c>
       <c r="F6">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="G6">
-        <v>990</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>1.11</v>
+        <v>5.2</v>
       </c>
       <c r="I6">
-        <v>990</v>
+        <v>6.2</v>
       </c>
       <c r="J6">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>950</v>
+        <v>3.45</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N6">
-        <v>1.31</v>
+        <v>2.24</v>
       </c>
       <c r="O6">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="P6">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="Q6">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="R6">
         <v>1.18</v>
       </c>
       <c r="S6">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="T6">
-        <v>1.11</v>
+        <v>2.36</v>
       </c>
       <c r="U6">
-        <v>1.11</v>
+        <v>1.62</v>
       </c>
       <c r="V6">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO6">
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2156,19 +2156,19 @@
         <v>107</v>
       </c>
       <c r="F7">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="G7">
         <v>990</v>
       </c>
       <c r="H7">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="I7">
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="K7">
         <v>3.15</v>
@@ -2398,46 +2398,46 @@
         <v>108</v>
       </c>
       <c r="F8">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G8">
         <v>2.46</v>
       </c>
       <c r="H8">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I8">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="J8">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K8">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L8">
         <v>1.58</v>
       </c>
       <c r="M8">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N8">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="O8">
         <v>1.51</v>
       </c>
       <c r="P8">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q8">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="R8">
         <v>1.21</v>
       </c>
       <c r="S8">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T8">
         <v>2.06</v>
@@ -2467,7 +2467,7 @@
         <v>8.4</v>
       </c>
       <c r="AC8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD8">
         <v>17</v>
@@ -2488,10 +2488,10 @@
         <v>500</v>
       </c>
       <c r="AJ8">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="AK8">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AL8">
         <v>380</v>
@@ -2515,7 +2515,7 @@
         <v>21</v>
       </c>
       <c r="AS8">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT8">
         <v>6.8</v>
@@ -2527,10 +2527,10 @@
         <v>13.5</v>
       </c>
       <c r="AW8">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AX8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY8">
         <v>10.5</v>
@@ -2545,19 +2545,19 @@
         <v>14.5</v>
       </c>
       <c r="BC8">
-        <v>7.2</v>
+        <v>14.5</v>
       </c>
       <c r="BD8">
+        <v>7.8</v>
+      </c>
+      <c r="BE8">
+        <v>8.4</v>
+      </c>
+      <c r="BF8">
+        <v>7</v>
+      </c>
+      <c r="BG8">
         <v>8</v>
-      </c>
-      <c r="BE8">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF8">
-        <v>7.2</v>
-      </c>
-      <c r="BG8">
-        <v>8.4</v>
       </c>
       <c r="BH8">
         <v>2.8</v>
@@ -2569,16 +2569,16 @@
         <v>11</v>
       </c>
       <c r="BK8">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>16.5</v>
+        <v>2.42</v>
       </c>
       <c r="BN8">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO8">
         <v>4.5</v>
@@ -2587,13 +2587,13 @@
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BT8">
         <v>6.6</v>
@@ -2605,19 +2605,19 @@
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
+        <v>2.34</v>
+      </c>
+      <c r="BZ8">
+        <v>1000</v>
+      </c>
+      <c r="CA8">
         <v>13.5</v>
-      </c>
-      <c r="BZ8">
-        <v>1000</v>
-      </c>
-      <c r="CA8">
-        <v>12.5</v>
       </c>
       <c r="CB8" t="s">
         <v>112</v>
@@ -2640,43 +2640,43 @@
         <v>109</v>
       </c>
       <c r="F9">
+        <v>2.18</v>
+      </c>
+      <c r="G9">
         <v>2.2</v>
       </c>
-      <c r="G9">
-        <v>2.24</v>
-      </c>
       <c r="H9">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I9">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J9">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K9">
         <v>3.6</v>
       </c>
       <c r="L9">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="M9">
         <v>1.07</v>
       </c>
       <c r="N9">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O9">
         <v>1.32</v>
       </c>
       <c r="P9">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q9">
         <v>2</v>
       </c>
       <c r="R9">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S9">
         <v>3.6</v>
@@ -2688,25 +2688,25 @@
         <v>2.18</v>
       </c>
       <c r="V9">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W9">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X9">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y9">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z9">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA9">
         <v>70</v>
       </c>
       <c r="AB9">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC9">
         <v>7.8</v>
@@ -2715,7 +2715,7 @@
         <v>15</v>
       </c>
       <c r="AE9">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AF9">
         <v>13.5</v>
@@ -2724,22 +2724,22 @@
         <v>11</v>
       </c>
       <c r="AH9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ9">
         <v>28</v>
       </c>
       <c r="AK9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL9">
         <v>38</v>
       </c>
       <c r="AM9">
-        <v>190</v>
+        <v>95</v>
       </c>
       <c r="AN9">
         <v>21</v>
@@ -2757,34 +2757,34 @@
         <v>23</v>
       </c>
       <c r="AS9">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AT9">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU9">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV9">
         <v>14</v>
       </c>
       <c r="AW9">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX9">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ9">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA9">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC9">
         <v>21</v>
@@ -2802,64 +2802,64 @@
         <v>26</v>
       </c>
       <c r="BH9">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="BI9">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="BJ9">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="BK9">
-        <v>2.98</v>
+        <v>6.2</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>3.85</v>
+        <v>14.5</v>
       </c>
       <c r="BN9">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="BO9">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="BP9">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="BQ9">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="BR9">
+        <v>29</v>
+      </c>
+      <c r="BS9">
+        <v>10.5</v>
+      </c>
+      <c r="BT9">
+        <v>7</v>
+      </c>
+      <c r="BU9">
+        <v>6</v>
+      </c>
+      <c r="BV9">
+        <v>29</v>
+      </c>
+      <c r="BW9">
+        <v>10.5</v>
+      </c>
+      <c r="BX9">
         <v>40</v>
       </c>
-      <c r="BS9">
-        <v>3.5</v>
-      </c>
-      <c r="BT9">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BU9">
-        <v>4.6</v>
-      </c>
-      <c r="BV9">
-        <v>40</v>
-      </c>
-      <c r="BW9">
-        <v>3.5</v>
-      </c>
-      <c r="BX9">
-        <v>1000</v>
-      </c>
       <c r="BY9">
-        <v>3.6</v>
+        <v>11.5</v>
       </c>
       <c r="BZ9">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="CA9">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="CB9" t="s">
         <v>112</v>
@@ -2891,7 +2891,7 @@
         <v>3.7</v>
       </c>
       <c r="I10">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J10">
         <v>3.15</v>
@@ -2900,31 +2900,31 @@
         <v>3.2</v>
       </c>
       <c r="L10">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="M10">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N10">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O10">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="P10">
         <v>1.55</v>
       </c>
       <c r="Q10">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="R10">
         <v>1.2</v>
       </c>
       <c r="S10">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="T10">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U10">
         <v>1.8</v>
@@ -2969,7 +2969,7 @@
         <v>25</v>
       </c>
       <c r="AI10">
-        <v>190</v>
+        <v>90</v>
       </c>
       <c r="AJ10">
         <v>34</v>
@@ -2984,10 +2984,10 @@
         <v>500</v>
       </c>
       <c r="AN10">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="AO10">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP10">
         <v>8</v>
@@ -3038,10 +3038,10 @@
         <v>13.5</v>
       </c>
       <c r="BF10">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BG10">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="BH10">
         <v>2.78</v>
@@ -3086,7 +3086,7 @@
         <v>4.8</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW10">
         <v>9</v>
@@ -3098,7 +3098,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA10">
         <v>9.4</v>
@@ -3124,13 +3124,13 @@
         <v>111</v>
       </c>
       <c r="F11">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G11">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H11">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I11">
         <v>3.8</v>
@@ -3142,16 +3142,16 @@
         <v>3.4</v>
       </c>
       <c r="L11">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M11">
         <v>1.1</v>
       </c>
       <c r="N11">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="O11">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P11">
         <v>1.66</v>
@@ -3166,16 +3166,16 @@
         <v>4.8</v>
       </c>
       <c r="T11">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U11">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V11">
         <v>1.35</v>
       </c>
       <c r="W11">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X11">
         <v>13</v>
@@ -3190,25 +3190,25 @@
         <v>900</v>
       </c>
       <c r="AB11">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC11">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD11">
         <v>22</v>
       </c>
       <c r="AE11">
-        <v>370</v>
+        <v>120</v>
       </c>
       <c r="AF11">
         <v>13</v>
       </c>
       <c r="AG11">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH11">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AI11">
         <v>85</v>
@@ -3235,7 +3235,7 @@
         <v>9.4</v>
       </c>
       <c r="AQ11">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR11">
         <v>20</v>
@@ -3274,19 +3274,19 @@
         <v>22</v>
       </c>
       <c r="BD11">
-        <v>23</v>
+        <v>7.4</v>
       </c>
       <c r="BE11">
         <v>8.199999999999999</v>
       </c>
       <c r="BF11">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BG11">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BH11">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BI11">
         <v>2.56</v>
@@ -3295,31 +3295,31 @@
         <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>17.5</v>
+        <v>5</v>
       </c>
       <c r="BN11">
         <v>4.9</v>
       </c>
       <c r="BO11">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT11">
         <v>6.8</v>
@@ -3331,19 +3331,19 @@
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="CB11" t="s">
         <v>112</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -352,7 +352,7 @@
     <t>America MG</t>
   </si>
   <si>
-    <t>2026-07-21 02:53:07</t>
+    <t>2026-07-21 05:00:08</t>
   </si>
 </sst>
 </file>
@@ -946,79 +946,79 @@
         <v>102</v>
       </c>
       <c r="F2">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="G2">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H2">
+        <v>4.1</v>
+      </c>
+      <c r="I2">
+        <v>4.3</v>
+      </c>
+      <c r="J2">
+        <v>3.65</v>
+      </c>
+      <c r="K2">
+        <v>3.75</v>
+      </c>
+      <c r="L2">
+        <v>1.44</v>
+      </c>
+      <c r="M2">
+        <v>1.07</v>
+      </c>
+      <c r="N2">
         <v>4</v>
       </c>
-      <c r="I2">
-        <v>4.2</v>
-      </c>
-      <c r="J2">
-        <v>3.55</v>
-      </c>
-      <c r="K2">
-        <v>3.65</v>
-      </c>
-      <c r="L2">
-        <v>1.46</v>
-      </c>
-      <c r="M2">
-        <v>1.08</v>
-      </c>
-      <c r="N2">
-        <v>3.7</v>
-      </c>
       <c r="O2">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="P2">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="Q2">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="R2">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S2">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="T2">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="U2">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V2">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="X2">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE2">
         <v>55</v>
@@ -1030,7 +1030,7 @@
         <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI2">
         <v>60</v>
@@ -1039,91 +1039,91 @@
         <v>24</v>
       </c>
       <c r="AK2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM2">
-        <v>310</v>
+        <v>100</v>
       </c>
       <c r="AN2">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ2">
         <v>13.5</v>
       </c>
       <c r="AR2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AS2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AT2">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV2">
         <v>15</v>
       </c>
       <c r="AW2">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AX2">
         <v>11.5</v>
       </c>
       <c r="AY2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA2">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BB2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE2">
         <v>50</v>
       </c>
       <c r="BF2">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BG2">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BH2">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="BI2">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BJ2">
         <v>9.800000000000001</v>
       </c>
       <c r="BK2">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BN2">
         <v>4.7</v>
@@ -1132,40 +1132,40 @@
         <v>4.3</v>
       </c>
       <c r="BP2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ2">
         <v>9.6</v>
       </c>
       <c r="BR2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BS2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BT2">
         <v>7.2</v>
       </c>
       <c r="BU2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV2">
         <v>34</v>
       </c>
       <c r="BW2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BX2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BZ2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="CA2">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="CB2" t="s">
         <v>112</v>
@@ -1188,73 +1188,73 @@
         <v>103</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G3">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="H3">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="I3">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J3">
+        <v>3.25</v>
+      </c>
+      <c r="K3">
         <v>3.35</v>
       </c>
-      <c r="K3">
-        <v>3.45</v>
-      </c>
       <c r="L3">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="M3">
         <v>1.12</v>
       </c>
       <c r="N3">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="O3">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="P3">
         <v>1.6</v>
       </c>
       <c r="Q3">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="R3">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S3">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T3">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="U3">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="V3">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W3">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X3">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Y3">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="Z3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC3">
         <v>7.6</v>
@@ -1266,49 +1266,49 @@
         <v>30</v>
       </c>
       <c r="AF3">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AG3">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI3">
         <v>60</v>
       </c>
       <c r="AJ3">
+        <v>110</v>
+      </c>
+      <c r="AK3">
+        <v>75</v>
+      </c>
+      <c r="AL3">
         <v>95</v>
-      </c>
-      <c r="AK3">
-        <v>70</v>
-      </c>
-      <c r="AL3">
-        <v>90</v>
       </c>
       <c r="AM3">
         <v>190</v>
       </c>
       <c r="AN3">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AO3">
         <v>28</v>
       </c>
       <c r="AP3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ3">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AR3">
         <v>10.5</v>
       </c>
       <c r="AS3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AT3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU3">
         <v>7</v>
@@ -1320,19 +1320,19 @@
         <v>26</v>
       </c>
       <c r="AX3">
+        <v>26</v>
+      </c>
+      <c r="AY3">
+        <v>17</v>
+      </c>
+      <c r="AZ3">
         <v>23</v>
-      </c>
-      <c r="AY3">
-        <v>16</v>
-      </c>
-      <c r="AZ3">
-        <v>21</v>
       </c>
       <c r="BA3">
         <v>50</v>
       </c>
       <c r="BB3">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BC3">
         <v>55</v>
@@ -1341,73 +1341,73 @@
         <v>70</v>
       </c>
       <c r="BE3">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="BF3">
         <v>70</v>
       </c>
       <c r="BG3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BH3">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="BI3">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BJ3">
         <v>11.5</v>
       </c>
       <c r="BK3">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="BM3">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BN3">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BO3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BP3">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BQ3">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BR3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BS3">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BT3">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BU3">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BV3">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BW3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BX3">
         <v>42</v>
       </c>
       <c r="BY3">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BZ3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="CA3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="CB3" t="s">
         <v>112</v>
@@ -1430,19 +1430,19 @@
         <v>104</v>
       </c>
       <c r="F4">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G4">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H4">
         <v>3.6</v>
       </c>
       <c r="I4">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K4">
         <v>3.5</v>
@@ -1454,16 +1454,16 @@
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O4">
         <v>1.39</v>
       </c>
       <c r="P4">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q4">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R4">
         <v>1.31</v>
@@ -1472,25 +1472,25 @@
         <v>4.1</v>
       </c>
       <c r="T4">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U4">
         <v>2.04</v>
       </c>
       <c r="V4">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W4">
         <v>1.75</v>
       </c>
       <c r="X4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y4">
         <v>12.5</v>
       </c>
       <c r="Z4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA4">
         <v>70</v>
@@ -1502,10 +1502,10 @@
         <v>7.6</v>
       </c>
       <c r="AD4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE4">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF4">
         <v>14</v>
@@ -1517,7 +1517,7 @@
         <v>19</v>
       </c>
       <c r="AI4">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AJ4">
         <v>32</v>
@@ -1526,7 +1526,7 @@
         <v>27</v>
       </c>
       <c r="AL4">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM4">
         <v>120</v>
@@ -1541,16 +1541,16 @@
         <v>10.5</v>
       </c>
       <c r="AQ4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR4">
         <v>22</v>
       </c>
       <c r="AS4">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AT4">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU4">
         <v>7</v>
@@ -1559,19 +1559,19 @@
         <v>13.5</v>
       </c>
       <c r="AW4">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AX4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY4">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA4">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BB4">
         <v>26</v>
@@ -1580,10 +1580,10 @@
         <v>23</v>
       </c>
       <c r="BD4">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BE4">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="BF4">
         <v>20</v>
@@ -1592,64 +1592,64 @@
         <v>34</v>
       </c>
       <c r="BH4">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BI4">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ4">
         <v>10</v>
       </c>
       <c r="BK4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BL4">
         <v>140</v>
       </c>
       <c r="BM4">
-        <v>18.5</v>
+        <v>110</v>
       </c>
       <c r="BN4">
         <v>5</v>
       </c>
       <c r="BO4">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP4">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ4">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR4">
         <v>34</v>
       </c>
       <c r="BS4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BT4">
         <v>6.6</v>
       </c>
       <c r="BU4">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="BV4">
         <v>30</v>
       </c>
       <c r="BW4">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX4">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY4">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BZ4">
         <v>32</v>
       </c>
       <c r="CA4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="CB4" t="s">
         <v>112</v>
@@ -1675,25 +1675,25 @@
         <v>2.1</v>
       </c>
       <c r="G5">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H5">
+        <v>3.7</v>
+      </c>
+      <c r="I5">
+        <v>3.9</v>
+      </c>
+      <c r="J5">
         <v>3.75</v>
       </c>
-      <c r="I5">
-        <v>3.95</v>
-      </c>
-      <c r="J5">
-        <v>3.65</v>
-      </c>
       <c r="K5">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L5">
         <v>1.32</v>
       </c>
       <c r="M5">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N5">
         <v>5.5</v>
@@ -1705,52 +1705,52 @@
         <v>2.48</v>
       </c>
       <c r="Q5">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R5">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S5">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T5">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="U5">
         <v>2.62</v>
       </c>
       <c r="V5">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W5">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y5">
         <v>21</v>
       </c>
       <c r="Z5">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AA5">
         <v>65</v>
       </c>
       <c r="AB5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC5">
         <v>8.800000000000001</v>
       </c>
       <c r="AD5">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AE5">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AF5">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AG5">
         <v>11.5</v>
@@ -1759,13 +1759,13 @@
         <v>14.5</v>
       </c>
       <c r="AI5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK5">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL5">
         <v>32</v>
@@ -1774,28 +1774,28 @@
         <v>60</v>
       </c>
       <c r="AN5">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO5">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AP5">
+        <v>18.5</v>
+      </c>
+      <c r="AQ5">
         <v>17.5</v>
-      </c>
-      <c r="AQ5">
-        <v>18</v>
       </c>
       <c r="AR5">
         <v>25</v>
       </c>
       <c r="AS5">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AT5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV5">
         <v>14.5</v>
@@ -1804,19 +1804,19 @@
         <v>30</v>
       </c>
       <c r="AX5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA5">
         <v>32</v>
       </c>
       <c r="BB5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC5">
         <v>17</v>
@@ -1831,7 +1831,7 @@
         <v>9.4</v>
       </c>
       <c r="BG5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH5">
         <v>4.2</v>
@@ -1840,16 +1840,16 @@
         <v>3.8</v>
       </c>
       <c r="BJ5">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BK5">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BN5">
         <v>5.3</v>
@@ -1861,13 +1861,13 @@
         <v>14</v>
       </c>
       <c r="BQ5">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BR5">
         <v>23</v>
       </c>
       <c r="BS5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT5">
         <v>7</v>
@@ -1879,19 +1879,19 @@
         <v>24</v>
       </c>
       <c r="BW5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX5">
         <v>32</v>
       </c>
       <c r="BY5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ5">
         <v>16.5</v>
       </c>
       <c r="CA5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="CB5" t="s">
         <v>112</v>
@@ -1920,19 +1920,19 @@
         <v>2</v>
       </c>
       <c r="H6">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I6">
         <v>6.2</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K6">
         <v>3.45</v>
       </c>
       <c r="L6">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="M6">
         <v>1.14</v>
@@ -1953,7 +1953,7 @@
         <v>1.18</v>
       </c>
       <c r="S6">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="T6">
         <v>2.36</v>
@@ -1968,10 +1968,10 @@
         <v>2</v>
       </c>
       <c r="X6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y6">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z6">
         <v>120</v>
@@ -1998,7 +1998,7 @@
         <v>12</v>
       </c>
       <c r="AH6">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AI6">
         <v>180</v>
@@ -2016,124 +2016,124 @@
         <v>330</v>
       </c>
       <c r="AN6">
-        <v>30</v>
+        <v>600</v>
       </c>
       <c r="AO6">
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AQ6">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AR6">
+        <v>7</v>
+      </c>
+      <c r="AS6">
+        <v>8</v>
+      </c>
+      <c r="AT6">
+        <v>3.7</v>
+      </c>
+      <c r="AU6">
+        <v>4</v>
+      </c>
+      <c r="AV6">
+        <v>6.4</v>
+      </c>
+      <c r="AW6">
+        <v>7.8</v>
+      </c>
+      <c r="AX6">
+        <v>4.5</v>
+      </c>
+      <c r="AY6">
+        <v>4.9</v>
+      </c>
+      <c r="AZ6">
+        <v>6.6</v>
+      </c>
+      <c r="BA6">
+        <v>7.8</v>
+      </c>
+      <c r="BB6">
         <v>6.2</v>
       </c>
-      <c r="AS6">
-        <v>6.8</v>
-      </c>
-      <c r="AT6">
-        <v>3.45</v>
-      </c>
-      <c r="AU6">
-        <v>3.75</v>
-      </c>
-      <c r="AV6">
-        <v>5.6</v>
-      </c>
-      <c r="AW6">
+      <c r="BC6">
         <v>6.6</v>
       </c>
-      <c r="AX6">
-        <v>4.1</v>
-      </c>
-      <c r="AY6">
-        <v>4.4</v>
-      </c>
-      <c r="AZ6">
-        <v>5.9</v>
-      </c>
-      <c r="BA6">
-        <v>6.8</v>
-      </c>
-      <c r="BB6">
-        <v>5.6</v>
-      </c>
-      <c r="BC6">
-        <v>5.8</v>
-      </c>
       <c r="BD6">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BE6">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BF6">
+        <v>6.2</v>
+      </c>
+      <c r="BG6">
+        <v>8</v>
+      </c>
+      <c r="BH6">
+        <v>2.62</v>
+      </c>
+      <c r="BI6">
+        <v>2.24</v>
+      </c>
+      <c r="BJ6">
+        <v>13</v>
+      </c>
+      <c r="BK6">
+        <v>1.91</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>2.22</v>
+      </c>
+      <c r="BN6">
+        <v>4.3</v>
+      </c>
+      <c r="BO6">
+        <v>3.35</v>
+      </c>
+      <c r="BP6">
+        <v>16</v>
+      </c>
+      <c r="BQ6">
+        <v>1.97</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>2.14</v>
+      </c>
+      <c r="BT6">
+        <v>9</v>
+      </c>
+      <c r="BU6">
         <v>5.7</v>
       </c>
-      <c r="BG6">
-        <v>6.8</v>
-      </c>
-      <c r="BH6">
-        <v>1000</v>
-      </c>
-      <c r="BI6">
-        <v>1.04</v>
-      </c>
-      <c r="BJ6">
-        <v>1000</v>
-      </c>
-      <c r="BK6">
-        <v>1.04</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>1.04</v>
-      </c>
-      <c r="BN6">
-        <v>1000</v>
-      </c>
-      <c r="BO6">
-        <v>1.04</v>
-      </c>
-      <c r="BP6">
-        <v>1000</v>
-      </c>
-      <c r="BQ6">
-        <v>1.04</v>
-      </c>
-      <c r="BR6">
-        <v>1000</v>
-      </c>
-      <c r="BS6">
-        <v>1.04</v>
-      </c>
-      <c r="BT6">
-        <v>1000</v>
-      </c>
-      <c r="BU6">
-        <v>1.04</v>
-      </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="CB6" t="s">
         <v>112</v>
@@ -2156,106 +2156,106 @@
         <v>107</v>
       </c>
       <c r="F7">
-        <v>1.74</v>
+        <v>2.12</v>
       </c>
       <c r="G7">
-        <v>990</v>
+        <v>2.38</v>
       </c>
       <c r="H7">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="I7">
-        <v>990</v>
+        <v>4.9</v>
       </c>
       <c r="J7">
-        <v>1.25</v>
+        <v>2.84</v>
       </c>
       <c r="K7">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N7">
-        <v>1.25</v>
+        <v>2.4</v>
       </c>
       <c r="O7">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="P7">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="Q7">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="R7">
         <v>1.18</v>
       </c>
       <c r="S7">
-        <v>1.05</v>
+        <v>4.7</v>
       </c>
       <c r="T7">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="U7">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="V7">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="W7">
-        <v>1.02</v>
+        <v>1.72</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AN7">
         <v>1000</v>
@@ -2264,58 +2264,58 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BF7">
-        <v>1.55</v>
+        <v>7.4</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2398,13 +2398,13 @@
         <v>108</v>
       </c>
       <c r="F8">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G8">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="H8">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I8">
         <v>3.95</v>
@@ -2413,49 +2413,49 @@
         <v>3.1</v>
       </c>
       <c r="K8">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L8">
         <v>1.58</v>
       </c>
       <c r="M8">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N8">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="O8">
         <v>1.51</v>
       </c>
       <c r="P8">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q8">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="R8">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S8">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="T8">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U8">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V8">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W8">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="X8">
         <v>10.5</v>
       </c>
       <c r="Y8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z8">
         <v>28</v>
@@ -2491,7 +2491,7 @@
         <v>40</v>
       </c>
       <c r="AK8">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AL8">
         <v>380</v>
@@ -2509,7 +2509,7 @@
         <v>8</v>
       </c>
       <c r="AQ8">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR8">
         <v>21</v>
@@ -2533,7 +2533,7 @@
         <v>12</v>
       </c>
       <c r="AY8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ8">
         <v>19</v>
@@ -2542,13 +2542,13 @@
         <v>8</v>
       </c>
       <c r="BB8">
-        <v>14.5</v>
+        <v>7</v>
       </c>
       <c r="BC8">
-        <v>14.5</v>
+        <v>7</v>
       </c>
       <c r="BD8">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE8">
         <v>8.4</v>
@@ -2557,25 +2557,25 @@
         <v>7</v>
       </c>
       <c r="BG8">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH8">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="BI8">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="BJ8">
         <v>11</v>
       </c>
       <c r="BK8">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>2.42</v>
+        <v>15.5</v>
       </c>
       <c r="BN8">
         <v>5</v>
@@ -2587,16 +2587,16 @@
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BT8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU8">
         <v>5.8</v>
@@ -2605,19 +2605,19 @@
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>2.34</v>
+        <v>13</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="CB8" t="s">
         <v>112</v>
@@ -2646,10 +2646,10 @@
         <v>2.2</v>
       </c>
       <c r="H9">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I9">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J9">
         <v>3.55</v>
@@ -2670,7 +2670,7 @@
         <v>1.32</v>
       </c>
       <c r="P9">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -2703,7 +2703,7 @@
         <v>26</v>
       </c>
       <c r="AA9">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB9">
         <v>10</v>
@@ -2715,7 +2715,7 @@
         <v>15</v>
       </c>
       <c r="AE9">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF9">
         <v>13.5</v>
@@ -2730,7 +2730,7 @@
         <v>55</v>
       </c>
       <c r="AJ9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK9">
         <v>23</v>
@@ -2745,19 +2745,19 @@
         <v>21</v>
       </c>
       <c r="AO9">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AP9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ9">
         <v>14</v>
       </c>
       <c r="AR9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS9">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AT9">
         <v>9.199999999999999</v>
@@ -2775,28 +2775,28 @@
         <v>12.5</v>
       </c>
       <c r="AY9">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ9">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA9">
         <v>48</v>
       </c>
       <c r="BB9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD9">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE9">
         <v>75</v>
       </c>
       <c r="BF9">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BG9">
         <v>26</v>
@@ -2817,7 +2817,7 @@
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN9">
         <v>5</v>
@@ -2826,7 +2826,7 @@
         <v>4.5</v>
       </c>
       <c r="BP9">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ9">
         <v>8</v>
@@ -2853,7 +2853,7 @@
         <v>40</v>
       </c>
       <c r="BY9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ9">
         <v>26</v>
@@ -2882,19 +2882,19 @@
         <v>110</v>
       </c>
       <c r="F10">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G10">
         <v>2.4</v>
       </c>
       <c r="H10">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I10">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J10">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K10">
         <v>3.2</v>
@@ -2924,13 +2924,13 @@
         <v>5.6</v>
       </c>
       <c r="T10">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U10">
         <v>1.8</v>
       </c>
       <c r="V10">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W10">
         <v>1.71</v>
@@ -2957,7 +2957,7 @@
         <v>17</v>
       </c>
       <c r="AE10">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF10">
         <v>13</v>
@@ -2984,10 +2984,10 @@
         <v>500</v>
       </c>
       <c r="AN10">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="AO10">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AP10">
         <v>8</v>
@@ -3023,7 +3023,7 @@
         <v>22</v>
       </c>
       <c r="BA10">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="BB10">
         <v>23</v>
@@ -3035,13 +3035,13 @@
         <v>50</v>
       </c>
       <c r="BE10">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BF10">
         <v>30</v>
       </c>
       <c r="BG10">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="BH10">
         <v>2.78</v>
@@ -3053,13 +3053,13 @@
         <v>12</v>
       </c>
       <c r="BK10">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN10">
         <v>5.1</v>
@@ -3071,37 +3071,37 @@
         <v>21</v>
       </c>
       <c r="BQ10">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT10">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU10">
         <v>4.8</v>
       </c>
       <c r="BV10">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
+        <v>10</v>
+      </c>
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
         <v>9.800000000000001</v>
-      </c>
-      <c r="BZ10">
-        <v>50</v>
-      </c>
-      <c r="CA10">
-        <v>9.4</v>
       </c>
       <c r="CB10" t="s">
         <v>112</v>
@@ -3157,7 +3157,7 @@
         <v>1.66</v>
       </c>
       <c r="Q11">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R11">
         <v>1.24</v>
@@ -3166,7 +3166,7 @@
         <v>4.8</v>
       </c>
       <c r="T11">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U11">
         <v>1.86</v>
@@ -3199,7 +3199,7 @@
         <v>22</v>
       </c>
       <c r="AE11">
-        <v>120</v>
+        <v>370</v>
       </c>
       <c r="AF11">
         <v>13</v>
@@ -3274,7 +3274,7 @@
         <v>22</v>
       </c>
       <c r="BD11">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="BE11">
         <v>8.199999999999999</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -352,7 +352,7 @@
     <t>America MG</t>
   </si>
   <si>
-    <t>2026-07-21 05:00:08</t>
+    <t>2026-07-21 07:07:08</t>
   </si>
 </sst>
 </file>
@@ -946,22 +946,22 @@
         <v>102</v>
       </c>
       <c r="F2">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="G2">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="H2">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="I2">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="J2">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K2">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L2">
         <v>1.44</v>
@@ -973,199 +973,199 @@
         <v>4</v>
       </c>
       <c r="O2">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P2">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q2">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R2">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S2">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T2">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="U2">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="V2">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="X2">
         <v>14.5</v>
       </c>
       <c r="Y2">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Z2">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AA2">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AB2">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC2">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD2">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE2">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AF2">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AI2">
+        <v>46</v>
+      </c>
+      <c r="AJ2">
+        <v>32</v>
+      </c>
+      <c r="AK2">
+        <v>24</v>
+      </c>
+      <c r="AL2">
+        <v>36</v>
+      </c>
+      <c r="AM2">
+        <v>90</v>
+      </c>
+      <c r="AN2">
+        <v>16.5</v>
+      </c>
+      <c r="AO2">
+        <v>42</v>
+      </c>
+      <c r="AP2">
+        <v>13.5</v>
+      </c>
+      <c r="AQ2">
+        <v>13</v>
+      </c>
+      <c r="AR2">
+        <v>25</v>
+      </c>
+      <c r="AS2">
         <v>60</v>
       </c>
-      <c r="AJ2">
-        <v>24</v>
-      </c>
-      <c r="AK2">
-        <v>22</v>
-      </c>
-      <c r="AL2">
-        <v>38</v>
-      </c>
-      <c r="AM2">
-        <v>100</v>
-      </c>
-      <c r="AN2">
-        <v>14.5</v>
-      </c>
-      <c r="AO2">
-        <v>55</v>
-      </c>
-      <c r="AP2">
-        <v>13</v>
-      </c>
-      <c r="AQ2">
+      <c r="AT2">
+        <v>9.4</v>
+      </c>
+      <c r="AU2">
+        <v>7.4</v>
+      </c>
+      <c r="AV2">
         <v>13.5</v>
-      </c>
-      <c r="AR2">
-        <v>28</v>
-      </c>
-      <c r="AS2">
-        <v>65</v>
-      </c>
-      <c r="AT2">
-        <v>8.6</v>
-      </c>
-      <c r="AU2">
-        <v>7.6</v>
-      </c>
-      <c r="AV2">
-        <v>15</v>
       </c>
       <c r="AW2">
         <v>38</v>
       </c>
       <c r="AX2">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AY2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ2">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BA2">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BB2">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BC2">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BD2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE2">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="BF2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BG2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BH2">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BI2">
         <v>3.15</v>
       </c>
       <c r="BJ2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK2">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM2">
+        <v>110</v>
+      </c>
+      <c r="BN2">
+        <v>4.9</v>
+      </c>
+      <c r="BO2">
+        <v>4.6</v>
+      </c>
+      <c r="BP2">
+        <v>16.5</v>
+      </c>
+      <c r="BQ2">
+        <v>15</v>
+      </c>
+      <c r="BR2">
+        <v>32</v>
+      </c>
+      <c r="BS2">
         <v>18</v>
       </c>
-      <c r="BN2">
-        <v>4.7</v>
-      </c>
-      <c r="BO2">
-        <v>4.3</v>
-      </c>
-      <c r="BP2">
-        <v>14.5</v>
-      </c>
-      <c r="BQ2">
-        <v>9.6</v>
-      </c>
-      <c r="BR2">
+      <c r="BT2">
+        <v>6.6</v>
+      </c>
+      <c r="BU2">
+        <v>6.2</v>
+      </c>
+      <c r="BV2">
         <v>28</v>
       </c>
-      <c r="BS2">
-        <v>12</v>
-      </c>
-      <c r="BT2">
-        <v>7.2</v>
-      </c>
-      <c r="BU2">
-        <v>6.6</v>
-      </c>
-      <c r="BV2">
-        <v>34</v>
-      </c>
       <c r="BW2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="BX2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY2">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="BZ2">
         <v>25</v>
       </c>
       <c r="CA2">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="CB2" t="s">
         <v>112</v>
@@ -1188,226 +1188,226 @@
         <v>103</v>
       </c>
       <c r="F3">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="G3">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="H3">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="I3">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="J3">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L3">
         <v>1.61</v>
       </c>
       <c r="M3">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N3">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="O3">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="P3">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Q3">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="R3">
         <v>1.2</v>
       </c>
       <c r="S3">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T3">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="U3">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="V3">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="W3">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="X3">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Y3">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="Z3">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AA3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AB3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC3">
         <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF3">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AG3">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AH3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI3">
         <v>60</v>
       </c>
       <c r="AJ3">
+        <v>140</v>
+      </c>
+      <c r="AK3">
+        <v>90</v>
+      </c>
+      <c r="AL3">
         <v>110</v>
       </c>
-      <c r="AK3">
-        <v>75</v>
-      </c>
-      <c r="AL3">
-        <v>95</v>
-      </c>
       <c r="AM3">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="AN3">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AO3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AP3">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ3">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AR3">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AT3">
         <v>10.5</v>
       </c>
       <c r="AU3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX3">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AY3">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AZ3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB3">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="BC3">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="BD3">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="BE3">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="BF3">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="BG3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BH3">
         <v>2.66</v>
       </c>
       <c r="BI3">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BJ3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BL3">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="BM3">
-        <v>24</v>
+        <v>200</v>
       </c>
       <c r="BN3">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BO3">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BP3">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BQ3">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="BR3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BS3">
         <v>19.5</v>
       </c>
       <c r="BT3">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BU3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV3">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BW3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BX3">
         <v>42</v>
       </c>
       <c r="BY3">
-        <v>16.5</v>
+        <v>24</v>
       </c>
       <c r="BZ3">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="CA3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="CB3" t="s">
         <v>112</v>
@@ -1430,22 +1430,22 @@
         <v>104</v>
       </c>
       <c r="F4">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G4">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="H4">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="I4">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="J4">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K4">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L4">
         <v>1.48</v>
@@ -1463,97 +1463,97 @@
         <v>1.81</v>
       </c>
       <c r="Q4">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R4">
         <v>1.31</v>
       </c>
       <c r="S4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T4">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U4">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V4">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W4">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="X4">
         <v>11.5</v>
       </c>
       <c r="Y4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA4">
         <v>70</v>
       </c>
       <c r="AB4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC4">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE4">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG4">
         <v>11</v>
       </c>
       <c r="AH4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK4">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AL4">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM4">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO4">
+        <v>48</v>
+      </c>
+      <c r="AP4">
+        <v>11</v>
+      </c>
+      <c r="AQ4">
+        <v>11</v>
+      </c>
+      <c r="AR4">
+        <v>21</v>
+      </c>
+      <c r="AS4">
         <v>55</v>
       </c>
-      <c r="AP4">
-        <v>10.5</v>
-      </c>
-      <c r="AQ4">
-        <v>11.5</v>
-      </c>
-      <c r="AR4">
-        <v>22</v>
-      </c>
-      <c r="AS4">
-        <v>50</v>
-      </c>
       <c r="AT4">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV4">
         <v>13.5</v>
@@ -1562,7 +1562,7 @@
         <v>40</v>
       </c>
       <c r="AX4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY4">
         <v>10</v>
@@ -1574,7 +1574,7 @@
         <v>50</v>
       </c>
       <c r="BB4">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BC4">
         <v>23</v>
@@ -1589,19 +1589,19 @@
         <v>20</v>
       </c>
       <c r="BG4">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BH4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI4">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BJ4">
         <v>10</v>
       </c>
       <c r="BK4">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL4">
         <v>140</v>
@@ -1613,43 +1613,43 @@
         <v>5</v>
       </c>
       <c r="BO4">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP4">
         <v>18</v>
       </c>
       <c r="BQ4">
-        <v>9.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="BR4">
         <v>34</v>
       </c>
       <c r="BS4">
-        <v>12</v>
+        <v>18.5</v>
       </c>
       <c r="BT4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU4">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BV4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BW4">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="BX4">
         <v>44</v>
       </c>
       <c r="BY4">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="BZ4">
         <v>32</v>
       </c>
       <c r="CA4">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="CB4" t="s">
         <v>112</v>
@@ -1681,37 +1681,37 @@
         <v>3.7</v>
       </c>
       <c r="I5">
+        <v>3.85</v>
+      </c>
+      <c r="J5">
+        <v>3.8</v>
+      </c>
+      <c r="K5">
         <v>3.9</v>
       </c>
-      <c r="J5">
-        <v>3.75</v>
-      </c>
-      <c r="K5">
-        <v>3.85</v>
-      </c>
       <c r="L5">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M5">
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O5">
         <v>1.2</v>
       </c>
       <c r="P5">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="Q5">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="R5">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S5">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="T5">
         <v>1.57</v>
@@ -1732,115 +1732,115 @@
         <v>21</v>
       </c>
       <c r="Z5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AA5">
         <v>65</v>
       </c>
       <c r="AB5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE5">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AF5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH5">
         <v>14.5</v>
       </c>
       <c r="AI5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ5">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AK5">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL5">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AM5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN5">
         <v>10.5</v>
       </c>
       <c r="AO5">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AP5">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ5">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AT5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU5">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AV5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX5">
         <v>14</v>
       </c>
       <c r="AY5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB5">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC5">
         <v>17</v>
       </c>
       <c r="BD5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE5">
         <v>46</v>
       </c>
       <c r="BF5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BH5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI5">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BJ5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK5">
         <v>7.6</v>
@@ -1861,19 +1861,19 @@
         <v>14</v>
       </c>
       <c r="BQ5">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT5">
         <v>7</v>
       </c>
       <c r="BU5">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BV5">
         <v>24</v>
@@ -1882,16 +1882,16 @@
         <v>10</v>
       </c>
       <c r="BX5">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BY5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ5">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="CA5">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB5" t="s">
         <v>112</v>
@@ -1914,64 +1914,64 @@
         <v>106</v>
       </c>
       <c r="F6">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="H6">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="I6">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="J6">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="K6">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="L6">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="M6">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N6">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="O6">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="P6">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Q6">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="R6">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S6">
-        <v>1.05</v>
+        <v>5.7</v>
       </c>
       <c r="T6">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="U6">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="V6">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="W6">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="Y6">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z6">
         <v>120</v>
@@ -1980,160 +1980,160 @@
         <v>900</v>
       </c>
       <c r="AB6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC6">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD6">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AE6">
-        <v>150</v>
+        <v>260</v>
       </c>
       <c r="AF6">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AG6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH6">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="AI6">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="AJ6">
-        <v>27</v>
+        <v>900</v>
       </c>
       <c r="AK6">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AL6">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="AM6">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="AN6">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AQ6">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AR6">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AS6">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AT6">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AU6">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AV6">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AW6">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX6">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AY6">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AZ6">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BA6">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB6">
         <v>6.2</v>
       </c>
       <c r="BC6">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD6">
+        <v>7</v>
+      </c>
+      <c r="BE6">
+        <v>7.6</v>
+      </c>
+      <c r="BF6">
+        <v>6.4</v>
+      </c>
+      <c r="BG6">
         <v>7.4</v>
       </c>
-      <c r="BE6">
-        <v>8</v>
-      </c>
-      <c r="BF6">
-        <v>6.2</v>
-      </c>
-      <c r="BG6">
-        <v>8</v>
-      </c>
       <c r="BH6">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="BI6">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="BJ6">
         <v>13</v>
       </c>
       <c r="BK6">
-        <v>1.91</v>
+        <v>5.5</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="BN6">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BO6">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BP6">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="BQ6">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="BT6">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BU6">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="CB6" t="s">
         <v>112</v>
@@ -2174,7 +2174,7 @@
         <v>3.1</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="M7">
         <v>1.13</v>
@@ -2243,7 +2243,7 @@
         <v>28</v>
       </c>
       <c r="AI7">
-        <v>140</v>
+        <v>540</v>
       </c>
       <c r="AJ7">
         <v>32</v>
@@ -2252,7 +2252,7 @@
         <v>65</v>
       </c>
       <c r="AL7">
-        <v>160</v>
+        <v>460</v>
       </c>
       <c r="AM7">
         <v>280</v>
@@ -2267,13 +2267,13 @@
         <v>4.4</v>
       </c>
       <c r="AQ7">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AR7">
         <v>7.2</v>
       </c>
       <c r="AS7">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7">
         <v>4</v>
@@ -2285,13 +2285,13 @@
         <v>6.4</v>
       </c>
       <c r="AW7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX7">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AY7">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AZ7">
         <v>7</v>
@@ -2303,13 +2303,13 @@
         <v>7.2</v>
       </c>
       <c r="BC7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BD7">
         <v>8.199999999999999</v>
       </c>
       <c r="BE7">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF7">
         <v>7.4</v>
@@ -2318,64 +2318,64 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="CB7" t="s">
         <v>112</v>
@@ -2401,7 +2401,7 @@
         <v>2.34</v>
       </c>
       <c r="G8">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H8">
         <v>3.7</v>
@@ -2422,34 +2422,34 @@
         <v>1.11</v>
       </c>
       <c r="N8">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O8">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="P8">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Q8">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="R8">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S8">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="T8">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U8">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="V8">
         <v>1.34</v>
       </c>
       <c r="W8">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X8">
         <v>10.5</v>
@@ -2473,37 +2473,37 @@
         <v>17</v>
       </c>
       <c r="AE8">
-        <v>370</v>
+        <v>75</v>
       </c>
       <c r="AF8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG8">
         <v>12</v>
       </c>
       <c r="AH8">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI8">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AJ8">
         <v>40</v>
       </c>
       <c r="AK8">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AL8">
-        <v>380</v>
+        <v>130</v>
       </c>
       <c r="AM8">
         <v>580</v>
       </c>
       <c r="AN8">
+        <v>42</v>
+      </c>
+      <c r="AO8">
         <v>500</v>
-      </c>
-      <c r="AO8">
-        <v>1000</v>
       </c>
       <c r="AP8">
         <v>8</v>
@@ -2515,10 +2515,10 @@
         <v>21</v>
       </c>
       <c r="AS8">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="AT8">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU8">
         <v>6.4</v>
@@ -2527,7 +2527,7 @@
         <v>13.5</v>
       </c>
       <c r="AW8">
-        <v>7.8</v>
+        <v>36</v>
       </c>
       <c r="AX8">
         <v>12</v>
@@ -2536,34 +2536,34 @@
         <v>10</v>
       </c>
       <c r="AZ8">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA8">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="BB8">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="BC8">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="BD8">
-        <v>7.6</v>
+        <v>38</v>
       </c>
       <c r="BE8">
-        <v>8.4</v>
+        <v>36</v>
       </c>
       <c r="BF8">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="BG8">
-        <v>8.199999999999999</v>
+        <v>46</v>
       </c>
       <c r="BH8">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="BI8">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ8">
         <v>11</v>
@@ -2575,7 +2575,7 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BN8">
         <v>5</v>
@@ -2590,34 +2590,34 @@
         <v>9</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT8">
         <v>6.8</v>
       </c>
       <c r="BU8">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CB8" t="s">
         <v>112</v>
@@ -2640,22 +2640,22 @@
         <v>109</v>
       </c>
       <c r="F9">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="G9">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H9">
         <v>3.8</v>
       </c>
       <c r="I9">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J9">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K9">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L9">
         <v>1.42</v>
@@ -2664,49 +2664,49 @@
         <v>1.07</v>
       </c>
       <c r="N9">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O9">
         <v>1.32</v>
       </c>
       <c r="P9">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q9">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R9">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S9">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T9">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U9">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V9">
         <v>1.35</v>
       </c>
       <c r="W9">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="X9">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y9">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA9">
         <v>75</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC9">
         <v>7.8</v>
@@ -2715,13 +2715,13 @@
         <v>15</v>
       </c>
       <c r="AE9">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF9">
         <v>13.5</v>
       </c>
       <c r="AG9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH9">
         <v>17.5</v>
@@ -2733,16 +2733,16 @@
         <v>27</v>
       </c>
       <c r="AK9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL9">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM9">
         <v>95</v>
       </c>
       <c r="AN9">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AO9">
         <v>55</v>
@@ -2790,16 +2790,16 @@
         <v>20</v>
       </c>
       <c r="BD9">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE9">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BF9">
         <v>15.5</v>
       </c>
       <c r="BG9">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="BH9">
         <v>3.45</v>
@@ -2897,7 +2897,7 @@
         <v>3.1</v>
       </c>
       <c r="K10">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L10">
         <v>1.58</v>
@@ -2915,7 +2915,7 @@
         <v>1.55</v>
       </c>
       <c r="Q10">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="R10">
         <v>1.2</v>
@@ -2969,7 +2969,7 @@
         <v>25</v>
       </c>
       <c r="AI10">
-        <v>90</v>
+        <v>460</v>
       </c>
       <c r="AJ10">
         <v>34</v>
@@ -2984,10 +2984,10 @@
         <v>500</v>
       </c>
       <c r="AN10">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO10">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AP10">
         <v>8</v>
@@ -3008,7 +3008,7 @@
         <v>6.4</v>
       </c>
       <c r="AV10">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW10">
         <v>50</v>
@@ -3026,7 +3026,7 @@
         <v>28</v>
       </c>
       <c r="BB10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC10">
         <v>29</v>
@@ -3044,22 +3044,22 @@
         <v>12</v>
       </c>
       <c r="BH10">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BI10">
         <v>2.46</v>
       </c>
       <c r="BJ10">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK10">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN10">
         <v>5.1</v>
@@ -3071,13 +3071,13 @@
         <v>21</v>
       </c>
       <c r="BQ10">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT10">
         <v>7</v>
@@ -3086,22 +3086,22 @@
         <v>4.8</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW10">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="CB10" t="s">
         <v>112</v>
@@ -3130,16 +3130,16 @@
         <v>2.3</v>
       </c>
       <c r="H11">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I11">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J11">
+        <v>3.3</v>
+      </c>
+      <c r="K11">
         <v>3.35</v>
-      </c>
-      <c r="K11">
-        <v>3.4</v>
       </c>
       <c r="L11">
         <v>1.52</v>
@@ -3148,19 +3148,19 @@
         <v>1.1</v>
       </c>
       <c r="N11">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O11">
         <v>1.47</v>
       </c>
       <c r="P11">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q11">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R11">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S11">
         <v>4.8</v>
@@ -3169,121 +3169,121 @@
         <v>2.06</v>
       </c>
       <c r="U11">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="V11">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W11">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X11">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="Y11">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="Z11">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AA11">
-        <v>900</v>
+        <v>90</v>
       </c>
       <c r="AB11">
         <v>8</v>
       </c>
       <c r="AC11">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD11">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AE11">
-        <v>370</v>
+        <v>120</v>
       </c>
       <c r="AF11">
         <v>13</v>
       </c>
       <c r="AG11">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH11">
+        <v>21</v>
+      </c>
+      <c r="AI11">
+        <v>80</v>
+      </c>
+      <c r="AJ11">
+        <v>30</v>
+      </c>
+      <c r="AK11">
         <v>29</v>
       </c>
-      <c r="AI11">
-        <v>85</v>
-      </c>
-      <c r="AJ11">
-        <v>42</v>
-      </c>
-      <c r="AK11">
-        <v>36</v>
-      </c>
       <c r="AL11">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AM11">
-        <v>580</v>
+        <v>160</v>
       </c>
       <c r="AN11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO11">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AP11">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ11">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AR11">
         <v>20</v>
       </c>
       <c r="AS11">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="AT11">
         <v>7.2</v>
       </c>
       <c r="AU11">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV11">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AW11">
-        <v>7.6</v>
+        <v>50</v>
       </c>
       <c r="AX11">
         <v>11.5</v>
       </c>
       <c r="AY11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ11">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BA11">
-        <v>7.8</v>
+        <v>65</v>
       </c>
       <c r="BB11">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BC11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD11">
+        <v>44</v>
+      </c>
+      <c r="BE11">
+        <v>9.6</v>
+      </c>
+      <c r="BF11">
         <v>23</v>
       </c>
-      <c r="BE11">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF11">
-        <v>20</v>
-      </c>
       <c r="BG11">
-        <v>7.8</v>
+        <v>60</v>
       </c>
       <c r="BH11">
         <v>2.92</v>
@@ -3295,7 +3295,7 @@
         <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BL11">
         <v>1000</v>
@@ -3313,13 +3313,13 @@
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BT11">
         <v>6.8</v>
@@ -3328,7 +3328,7 @@
         <v>6</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW11">
         <v>13</v>
@@ -3337,13 +3337,13 @@
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CB11" t="s">
         <v>112</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="117">
   <si>
     <t>League</t>
   </si>
@@ -274,6 +274,9 @@
     <t>Brazilian Serie B</t>
   </si>
   <si>
+    <t>Bolivian Liga de Futbol Profesional</t>
+  </si>
+  <si>
     <t>2026-07-21</t>
   </si>
   <si>
@@ -292,6 +295,9 @@
     <t>22:30:00</t>
   </si>
   <si>
+    <t>23:00:00</t>
+  </si>
+  <si>
     <t>Jeonbuk Motors</t>
   </si>
   <si>
@@ -322,6 +328,9 @@
     <t>Avai</t>
   </si>
   <si>
+    <t>Club Ind. Petrolero</t>
+  </si>
+  <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
@@ -352,7 +361,10 @@
     <t>America MG</t>
   </si>
   <si>
-    <t>2026-07-21 07:07:08</t>
+    <t>Real Potosi</t>
+  </si>
+  <si>
+    <t>2026-07-21 09:14:34</t>
   </si>
 </sst>
 </file>
@@ -684,7 +696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB11"/>
+  <dimension ref="A1:CB12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -934,241 +946,241 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F2">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="G2">
-        <v>2.24</v>
+        <v>3.85</v>
       </c>
       <c r="H2">
-        <v>3.7</v>
+        <v>6.4</v>
       </c>
       <c r="I2">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>3.5</v>
+        <v>1.69</v>
       </c>
       <c r="K2">
-        <v>3.55</v>
+        <v>1.72</v>
       </c>
       <c r="L2">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.07</v>
+        <v>2.16</v>
       </c>
       <c r="N2">
-        <v>4</v>
+        <v>1.17</v>
       </c>
       <c r="O2">
-        <v>1.32</v>
+        <v>6.4</v>
       </c>
       <c r="P2">
-        <v>2.02</v>
+        <v>1.02</v>
       </c>
       <c r="Q2">
-        <v>1.96</v>
+        <v>27</v>
       </c>
       <c r="R2">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="S2">
-        <v>3.45</v>
+        <v>200</v>
       </c>
       <c r="T2">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="U2">
-        <v>2.26</v>
+        <v>1.02</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="W2">
+        <v>1.33</v>
+      </c>
+      <c r="X2">
+        <v>1.92</v>
+      </c>
+      <c r="Y2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z2">
+        <v>140</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>4.6</v>
+      </c>
+      <c r="AC2">
+        <v>23</v>
+      </c>
+      <c r="AD2">
+        <v>280</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>34</v>
+      </c>
+      <c r="AG2">
+        <v>170</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
         <v>1.8</v>
       </c>
-      <c r="X2">
-        <v>14.5</v>
-      </c>
-      <c r="Y2">
-        <v>14</v>
-      </c>
-      <c r="Z2">
+      <c r="AQ2">
+        <v>7.6</v>
+      </c>
+      <c r="AR2">
+        <v>44</v>
+      </c>
+      <c r="AS2">
+        <v>190</v>
+      </c>
+      <c r="AT2">
+        <v>4.1</v>
+      </c>
+      <c r="AU2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV2">
+        <v>120</v>
+      </c>
+      <c r="AW2">
+        <v>170</v>
+      </c>
+      <c r="AX2">
+        <v>20</v>
+      </c>
+      <c r="AY2">
+        <v>75</v>
+      </c>
+      <c r="AZ2">
+        <v>200</v>
+      </c>
+      <c r="BA2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB2">
+        <v>150</v>
+      </c>
+      <c r="BC2">
+        <v>160</v>
+      </c>
+      <c r="BD2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF2">
+        <v>24</v>
+      </c>
+      <c r="BG2">
         <v>27</v>
       </c>
-      <c r="AA2">
-        <v>75</v>
-      </c>
-      <c r="AB2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC2">
-        <v>7.6</v>
-      </c>
-      <c r="AD2">
-        <v>14.5</v>
-      </c>
-      <c r="AE2">
-        <v>46</v>
-      </c>
-      <c r="AF2">
-        <v>14</v>
-      </c>
-      <c r="AG2">
-        <v>10.5</v>
-      </c>
-      <c r="AH2">
-        <v>16.5</v>
-      </c>
-      <c r="AI2">
-        <v>46</v>
-      </c>
-      <c r="AJ2">
-        <v>32</v>
-      </c>
-      <c r="AK2">
-        <v>24</v>
-      </c>
-      <c r="AL2">
-        <v>36</v>
-      </c>
-      <c r="AM2">
-        <v>90</v>
-      </c>
-      <c r="AN2">
-        <v>16.5</v>
-      </c>
-      <c r="AO2">
-        <v>42</v>
-      </c>
-      <c r="AP2">
-        <v>13.5</v>
-      </c>
-      <c r="AQ2">
-        <v>13</v>
-      </c>
-      <c r="AR2">
-        <v>25</v>
-      </c>
-      <c r="AS2">
-        <v>60</v>
-      </c>
-      <c r="AT2">
-        <v>9.4</v>
-      </c>
-      <c r="AU2">
-        <v>7.4</v>
-      </c>
-      <c r="AV2">
-        <v>13.5</v>
-      </c>
-      <c r="AW2">
-        <v>38</v>
-      </c>
-      <c r="AX2">
-        <v>13</v>
-      </c>
-      <c r="AY2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ2">
-        <v>15</v>
-      </c>
-      <c r="BA2">
-        <v>44</v>
-      </c>
-      <c r="BB2">
-        <v>27</v>
-      </c>
-      <c r="BC2">
-        <v>23</v>
-      </c>
-      <c r="BD2">
-        <v>32</v>
-      </c>
-      <c r="BE2">
-        <v>85</v>
-      </c>
-      <c r="BF2">
-        <v>15</v>
-      </c>
-      <c r="BG2">
-        <v>38</v>
-      </c>
       <c r="BH2">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1176,241 +1188,241 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F3">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="G3">
-        <v>4.8</v>
+        <v>12</v>
       </c>
       <c r="H3">
-        <v>2.02</v>
+        <v>4.4</v>
       </c>
       <c r="I3">
-        <v>2.06</v>
+        <v>7.8</v>
       </c>
       <c r="J3">
-        <v>3.35</v>
+        <v>1.32</v>
       </c>
       <c r="K3">
-        <v>3.4</v>
+        <v>1.54</v>
       </c>
       <c r="L3">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>1.58</v>
+      </c>
+      <c r="Q3">
+        <v>2.64</v>
+      </c>
+      <c r="R3">
+        <v>1.07</v>
+      </c>
+      <c r="S3">
+        <v>12.5</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>1.24</v>
+      </c>
+      <c r="W3">
         <v>1.13</v>
       </c>
-      <c r="N3">
-        <v>2.72</v>
-      </c>
-      <c r="O3">
-        <v>1.57</v>
-      </c>
-      <c r="P3">
-        <v>1.57</v>
-      </c>
-      <c r="Q3">
-        <v>2.68</v>
-      </c>
-      <c r="R3">
-        <v>1.2</v>
-      </c>
-      <c r="S3">
+      <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>1.66</v>
+      </c>
+      <c r="AD3">
+        <v>6.2</v>
+      </c>
+      <c r="AE3">
+        <v>970</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>190</v>
+      </c>
+      <c r="AH3">
+        <v>990</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>970</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>1000</v>
+      </c>
+      <c r="AQ3">
+        <v>1000</v>
+      </c>
+      <c r="AR3">
+        <v>1000</v>
+      </c>
+      <c r="AS3">
+        <v>1000</v>
+      </c>
+      <c r="AT3">
+        <v>1000</v>
+      </c>
+      <c r="AU3">
+        <v>1.6</v>
+      </c>
+      <c r="AV3">
+        <v>3.6</v>
+      </c>
+      <c r="AW3">
+        <v>22</v>
+      </c>
+      <c r="AX3">
+        <v>1000</v>
+      </c>
+      <c r="AY3">
         <v>5.7</v>
       </c>
-      <c r="T3">
-        <v>2.26</v>
-      </c>
-      <c r="U3">
-        <v>1.74</v>
-      </c>
-      <c r="V3">
-        <v>1.95</v>
-      </c>
-      <c r="W3">
-        <v>1.26</v>
-      </c>
-      <c r="X3">
-        <v>8.6</v>
-      </c>
-      <c r="Y3">
-        <v>6.4</v>
-      </c>
-      <c r="Z3">
-        <v>10.5</v>
-      </c>
-      <c r="AA3">
-        <v>24</v>
-      </c>
-      <c r="AB3">
-        <v>12</v>
-      </c>
-      <c r="AC3">
+      <c r="AZ3">
+        <v>16.5</v>
+      </c>
+      <c r="BA3">
+        <v>6</v>
+      </c>
+      <c r="BB3">
+        <v>1000</v>
+      </c>
+      <c r="BC3">
         <v>7.6</v>
       </c>
-      <c r="AD3">
-        <v>11</v>
-      </c>
-      <c r="AE3">
+      <c r="BD3">
+        <v>6.2</v>
+      </c>
+      <c r="BE3">
+        <v>6</v>
+      </c>
+      <c r="BF3">
         <v>29</v>
       </c>
-      <c r="AF3">
-        <v>34</v>
-      </c>
-      <c r="AG3">
-        <v>20</v>
-      </c>
-      <c r="AH3">
-        <v>26</v>
-      </c>
-      <c r="AI3">
-        <v>60</v>
-      </c>
-      <c r="AJ3">
-        <v>140</v>
-      </c>
-      <c r="AK3">
-        <v>90</v>
-      </c>
-      <c r="AL3">
-        <v>110</v>
-      </c>
-      <c r="AM3">
-        <v>220</v>
-      </c>
-      <c r="AN3">
-        <v>140</v>
-      </c>
-      <c r="AO3">
-        <v>24</v>
-      </c>
-      <c r="AP3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ3">
-        <v>6</v>
-      </c>
-      <c r="AR3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS3">
-        <v>22</v>
-      </c>
-      <c r="AT3">
-        <v>10.5</v>
-      </c>
-      <c r="AU3">
-        <v>7.2</v>
-      </c>
-      <c r="AV3">
-        <v>10</v>
-      </c>
-      <c r="AW3">
-        <v>25</v>
-      </c>
-      <c r="AX3">
-        <v>30</v>
-      </c>
-      <c r="AY3">
-        <v>18.5</v>
-      </c>
-      <c r="AZ3">
-        <v>24</v>
-      </c>
-      <c r="BA3">
-        <v>55</v>
-      </c>
-      <c r="BB3">
-        <v>60</v>
-      </c>
-      <c r="BC3">
-        <v>75</v>
-      </c>
-      <c r="BD3">
-        <v>85</v>
-      </c>
-      <c r="BE3">
-        <v>140</v>
-      </c>
-      <c r="BF3">
-        <v>110</v>
-      </c>
       <c r="BG3">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="BH3">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1418,124 +1430,124 @@
         <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F4">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="G4">
-        <v>2.46</v>
+        <v>6.6</v>
       </c>
       <c r="H4">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="I4">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>3.3</v>
+        <v>1.57</v>
       </c>
       <c r="K4">
-        <v>3.4</v>
+        <v>1.69</v>
       </c>
       <c r="L4">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="Q4">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="R4">
-        <v>1.31</v>
+        <v>1.1</v>
       </c>
       <c r="S4">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="T4">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="W4">
-        <v>1.7</v>
+        <v>1.18</v>
       </c>
       <c r="X4">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>7.2</v>
+        <v>1.77</v>
       </c>
       <c r="AD4">
-        <v>14.5</v>
+        <v>9.4</v>
       </c>
       <c r="AE4">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="AF4">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>18.5</v>
+        <v>28</v>
       </c>
       <c r="AI4">
-        <v>55</v>
+        <v>320</v>
       </c>
       <c r="AJ4">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="AL4">
-        <v>44</v>
+        <v>340</v>
       </c>
       <c r="AM4">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
         <v>11</v>
@@ -1544,115 +1556,115 @@
         <v>11</v>
       </c>
       <c r="AR4">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AS4">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="AT4">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AU4">
-        <v>6.8</v>
+        <v>1.58</v>
       </c>
       <c r="AV4">
-        <v>13.5</v>
+        <v>4.3</v>
       </c>
       <c r="AW4">
+        <v>7</v>
+      </c>
+      <c r="AX4">
+        <v>11</v>
+      </c>
+      <c r="AY4">
+        <v>4.2</v>
+      </c>
+      <c r="AZ4">
+        <v>11</v>
+      </c>
+      <c r="BA4">
         <v>40</v>
       </c>
-      <c r="AX4">
-        <v>13</v>
-      </c>
-      <c r="AY4">
-        <v>10</v>
-      </c>
-      <c r="AZ4">
-        <v>17</v>
-      </c>
-      <c r="BA4">
-        <v>50</v>
-      </c>
       <c r="BB4">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="BC4">
-        <v>23</v>
+        <v>5.7</v>
       </c>
       <c r="BD4">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="BE4">
-        <v>85</v>
+        <v>6</v>
       </c>
       <c r="BF4">
-        <v>20</v>
+        <v>6.2</v>
       </c>
       <c r="BG4">
-        <v>40</v>
+        <v>6.2</v>
       </c>
       <c r="BH4">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BI4">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="BJ4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BK4">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BL4">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="BM4">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BN4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BO4">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BP4">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BQ4">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BR4">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BS4">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BT4">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BU4">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BV4">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BW4">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BX4">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BY4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BZ4">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="CA4">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1660,91 +1672,91 @@
         <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F5">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G5">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H5">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I5">
+        <v>3.75</v>
+      </c>
+      <c r="J5">
         <v>3.85</v>
       </c>
-      <c r="J5">
-        <v>3.8</v>
-      </c>
       <c r="K5">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L5">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M5">
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O5">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P5">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q5">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R5">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="S5">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="T5">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U5">
         <v>2.62</v>
       </c>
       <c r="V5">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W5">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X5">
         <v>22</v>
       </c>
       <c r="Y5">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA5">
         <v>65</v>
       </c>
       <c r="AB5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE5">
         <v>36</v>
@@ -1756,10 +1768,10 @@
         <v>11</v>
       </c>
       <c r="AH5">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AI5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ5">
         <v>26</v>
@@ -1768,10 +1780,10 @@
         <v>19</v>
       </c>
       <c r="AL5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN5">
         <v>10.5</v>
@@ -1786,7 +1798,7 @@
         <v>18</v>
       </c>
       <c r="AR5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS5">
         <v>55</v>
@@ -1795,10 +1807,10 @@
         <v>12.5</v>
       </c>
       <c r="AU5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW5">
         <v>32</v>
@@ -1819,19 +1831,19 @@
         <v>23</v>
       </c>
       <c r="BC5">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD5">
         <v>24</v>
       </c>
       <c r="BE5">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BF5">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH5">
         <v>4.1</v>
@@ -1849,7 +1861,7 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN5">
         <v>5.3</v>
@@ -1861,7 +1873,7 @@
         <v>14</v>
       </c>
       <c r="BQ5">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BR5">
         <v>22</v>
@@ -1873,28 +1885,28 @@
         <v>7</v>
       </c>
       <c r="BU5">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BV5">
         <v>24</v>
       </c>
       <c r="BW5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX5">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BY5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ5">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="CA5">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB5" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1902,52 +1914,52 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F6">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G6">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="H6">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I6">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J6">
-        <v>2.82</v>
+        <v>2.98</v>
       </c>
       <c r="K6">
         <v>3.25</v>
       </c>
       <c r="L6">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="M6">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N6">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="O6">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="P6">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Q6">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="R6">
         <v>1.17</v>
@@ -1956,19 +1968,19 @@
         <v>5.7</v>
       </c>
       <c r="T6">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="U6">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V6">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W6">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="X6">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>11.5</v>
@@ -1980,28 +1992,28 @@
         <v>900</v>
       </c>
       <c r="AB6">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AC6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD6">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="AE6">
         <v>260</v>
       </c>
       <c r="AF6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH6">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AI6">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AJ6">
         <v>900</v>
@@ -2010,7 +2022,7 @@
         <v>65</v>
       </c>
       <c r="AL6">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="AM6">
         <v>280</v>
@@ -2022,121 +2034,121 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AQ6">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AR6">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AS6">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AT6">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AU6">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AV6">
+        <v>7.2</v>
+      </c>
+      <c r="AW6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX6">
         <v>5.7</v>
       </c>
-      <c r="AW6">
-        <v>7.2</v>
-      </c>
-      <c r="AX6">
-        <v>4.8</v>
-      </c>
       <c r="AY6">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="AZ6">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BA6">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BB6">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC6">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BD6">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="BE6">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF6">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BG6">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH6">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BI6">
+        <v>2.22</v>
+      </c>
+      <c r="BJ6">
+        <v>12.5</v>
+      </c>
+      <c r="BK6">
+        <v>6.6</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
         <v>2.2</v>
       </c>
-      <c r="BJ6">
-        <v>13</v>
-      </c>
-      <c r="BK6">
-        <v>5.5</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>2.08</v>
-      </c>
       <c r="BN6">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BO6">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="BP6">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="BT6">
         <v>7.8</v>
       </c>
       <c r="BU6">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="CB6" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2144,118 +2156,118 @@
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F7">
-        <v>2.12</v>
+        <v>1.64</v>
       </c>
       <c r="G7">
-        <v>2.38</v>
+        <v>3.3</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>2.68</v>
       </c>
       <c r="I7">
-        <v>4.9</v>
+        <v>400</v>
       </c>
       <c r="J7">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="K7">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="L7">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N7">
-        <v>2.4</v>
+        <v>1.25</v>
       </c>
       <c r="O7">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="P7">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="Q7">
-        <v>2.46</v>
+        <v>1.02</v>
       </c>
       <c r="R7">
         <v>1.18</v>
       </c>
       <c r="S7">
-        <v>4.7</v>
+        <v>1.52</v>
       </c>
       <c r="T7">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="U7">
-        <v>1.67</v>
+        <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="W7">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="X7">
-        <v>8.4</v>
+        <v>950</v>
       </c>
       <c r="Y7">
-        <v>11.5</v>
+        <v>950</v>
       </c>
       <c r="Z7">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="AA7">
         <v>900</v>
       </c>
       <c r="AB7">
-        <v>7</v>
+        <v>950</v>
       </c>
       <c r="AC7">
-        <v>7.6</v>
+        <v>15</v>
       </c>
       <c r="AD7">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AE7">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="AF7">
-        <v>12.5</v>
+        <v>34</v>
       </c>
       <c r="AG7">
-        <v>12.5</v>
+        <v>950</v>
       </c>
       <c r="AH7">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AI7">
         <v>540</v>
       </c>
       <c r="AJ7">
-        <v>32</v>
+        <v>900</v>
       </c>
       <c r="AK7">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="AL7">
         <v>460</v>
       </c>
       <c r="AM7">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
         <v>1000</v>
@@ -2264,121 +2276,121 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AQ7">
-        <v>5.8</v>
+        <v>1.68</v>
       </c>
       <c r="AR7">
-        <v>7.2</v>
+        <v>1.79</v>
       </c>
       <c r="AS7">
-        <v>8.800000000000001</v>
+        <v>1.82</v>
       </c>
       <c r="AT7">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="AU7">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="AV7">
-        <v>6.4</v>
+        <v>1.78</v>
       </c>
       <c r="AW7">
-        <v>8.6</v>
+        <v>1.82</v>
       </c>
       <c r="AX7">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="AY7">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AZ7">
-        <v>7</v>
+        <v>1.8</v>
       </c>
       <c r="BA7">
-        <v>8.800000000000001</v>
+        <v>1.82</v>
       </c>
       <c r="BB7">
-        <v>7.2</v>
+        <v>1.79</v>
       </c>
       <c r="BC7">
-        <v>7.4</v>
+        <v>1.78</v>
       </c>
       <c r="BD7">
-        <v>8.199999999999999</v>
+        <v>1.82</v>
       </c>
       <c r="BE7">
-        <v>9.199999999999999</v>
+        <v>1.84</v>
       </c>
       <c r="BF7">
-        <v>7.4</v>
+        <v>1.83</v>
       </c>
       <c r="BG7">
-        <v>8.800000000000001</v>
+        <v>1.83</v>
       </c>
       <c r="BH7">
-        <v>2.7</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>2.16</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>2.14</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.95</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>2.06</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>2.1</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2386,16 +2398,16 @@
         <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F8">
         <v>2.34</v>
@@ -2404,46 +2416,46 @@
         <v>2.42</v>
       </c>
       <c r="H8">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I8">
         <v>3.95</v>
       </c>
       <c r="J8">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K8">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L8">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="M8">
         <v>1.11</v>
       </c>
       <c r="N8">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="O8">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P8">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q8">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="R8">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S8">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="T8">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U8">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V8">
         <v>1.34</v>
@@ -2461,10 +2473,10 @@
         <v>28</v>
       </c>
       <c r="AA8">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AB8">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AC8">
         <v>7.4</v>
@@ -2476,7 +2488,7 @@
         <v>75</v>
       </c>
       <c r="AF8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG8">
         <v>12</v>
@@ -2488,28 +2500,28 @@
         <v>160</v>
       </c>
       <c r="AJ8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK8">
         <v>42</v>
       </c>
       <c r="AL8">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="AM8">
         <v>580</v>
       </c>
       <c r="AN8">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AO8">
         <v>500</v>
       </c>
       <c r="AP8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ8">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR8">
         <v>21</v>
@@ -2527,7 +2539,7 @@
         <v>13.5</v>
       </c>
       <c r="AW8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AX8">
         <v>12</v>
@@ -2536,46 +2548,46 @@
         <v>10</v>
       </c>
       <c r="AZ8">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA8">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BB8">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BC8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE8">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="BF8">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BG8">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BH8">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BI8">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BJ8">
         <v>11</v>
       </c>
       <c r="BK8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN8">
         <v>5</v>
@@ -2587,10 +2599,10 @@
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR8">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
         <v>11.5</v>
@@ -2602,25 +2614,25 @@
         <v>6</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CB8" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2628,28 +2640,28 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F9">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G9">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H9">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I9">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J9">
         <v>3.6</v>
@@ -2658,13 +2670,13 @@
         <v>3.65</v>
       </c>
       <c r="L9">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M9">
         <v>1.07</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O9">
         <v>1.32</v>
@@ -2676,13 +2688,13 @@
         <v>1.98</v>
       </c>
       <c r="R9">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S9">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T9">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U9">
         <v>2.2</v>
@@ -2691,25 +2703,25 @@
         <v>1.35</v>
       </c>
       <c r="W9">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X9">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y9">
         <v>14.5</v>
       </c>
       <c r="Z9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA9">
         <v>75</v>
       </c>
       <c r="AB9">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC9">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD9">
         <v>15</v>
@@ -2718,10 +2730,10 @@
         <v>44</v>
       </c>
       <c r="AF9">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH9">
         <v>17.5</v>
@@ -2730,7 +2742,7 @@
         <v>55</v>
       </c>
       <c r="AJ9">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK9">
         <v>22</v>
@@ -2742,7 +2754,7 @@
         <v>95</v>
       </c>
       <c r="AN9">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AO9">
         <v>55</v>
@@ -2751,28 +2763,28 @@
         <v>13</v>
       </c>
       <c r="AQ9">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS9">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AT9">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU9">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV9">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW9">
         <v>40</v>
       </c>
       <c r="AX9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY9">
         <v>10</v>
@@ -2793,76 +2805,76 @@
         <v>32</v>
       </c>
       <c r="BE9">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BF9">
         <v>15.5</v>
       </c>
       <c r="BG9">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH9">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>3.1</v>
+        <v>1.21</v>
       </c>
       <c r="BJ9">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>15</v>
+        <v>1.04</v>
       </c>
       <c r="BN9">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>4.5</v>
+        <v>1.37</v>
       </c>
       <c r="BP9">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BR9">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT9">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV9">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX9">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2870,16 +2882,16 @@
         <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E10" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F10">
         <v>2.34</v>
@@ -2891,7 +2903,7 @@
         <v>3.75</v>
       </c>
       <c r="I10">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J10">
         <v>3.1</v>
@@ -2900,7 +2912,7 @@
         <v>3.15</v>
       </c>
       <c r="L10">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M10">
         <v>1.13</v>
@@ -2912,7 +2924,7 @@
         <v>1.55</v>
       </c>
       <c r="P10">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q10">
         <v>2.72</v>
@@ -2921,7 +2933,7 @@
         <v>1.2</v>
       </c>
       <c r="S10">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T10">
         <v>2.16</v>
@@ -2951,7 +2963,7 @@
         <v>7.6</v>
       </c>
       <c r="AC10">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD10">
         <v>17</v>
@@ -2963,13 +2975,13 @@
         <v>13</v>
       </c>
       <c r="AG10">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI10">
-        <v>460</v>
+        <v>190</v>
       </c>
       <c r="AJ10">
         <v>34</v>
@@ -2987,10 +2999,10 @@
         <v>34</v>
       </c>
       <c r="AO10">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP10">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ10">
         <v>9.4</v>
@@ -2999,7 +3011,7 @@
         <v>21</v>
       </c>
       <c r="AS10">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AT10">
         <v>6.8</v>
@@ -3008,7 +3020,7 @@
         <v>6.4</v>
       </c>
       <c r="AV10">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW10">
         <v>50</v>
@@ -3023,10 +3035,10 @@
         <v>22</v>
       </c>
       <c r="BA10">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="BB10">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BC10">
         <v>29</v>
@@ -3035,13 +3047,13 @@
         <v>50</v>
       </c>
       <c r="BE10">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="BF10">
         <v>30</v>
       </c>
       <c r="BG10">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="BH10">
         <v>2.76</v>
@@ -3083,7 +3095,7 @@
         <v>7</v>
       </c>
       <c r="BU10">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV10">
         <v>40</v>
@@ -3104,7 +3116,7 @@
         <v>10.5</v>
       </c>
       <c r="CB10" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3112,19 +3124,19 @@
         <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F11">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G11">
         <v>2.3</v>
@@ -3136,79 +3148,79 @@
         <v>3.9</v>
       </c>
       <c r="J11">
+        <v>3.25</v>
+      </c>
+      <c r="K11">
         <v>3.3</v>
       </c>
-      <c r="K11">
-        <v>3.35</v>
-      </c>
       <c r="L11">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M11">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N11">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O11">
         <v>1.47</v>
       </c>
       <c r="P11">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q11">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R11">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S11">
         <v>4.8</v>
       </c>
       <c r="T11">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U11">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V11">
         <v>1.34</v>
       </c>
       <c r="W11">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X11">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y11">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z11">
         <v>26</v>
       </c>
       <c r="AA11">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB11">
         <v>8</v>
       </c>
       <c r="AC11">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AD11">
         <v>16.5</v>
       </c>
       <c r="AE11">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AF11">
         <v>13</v>
       </c>
       <c r="AG11">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI11">
         <v>80</v>
@@ -3223,31 +3235,31 @@
         <v>55</v>
       </c>
       <c r="AM11">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN11">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AO11">
         <v>75</v>
       </c>
       <c r="AP11">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AQ11">
         <v>10.5</v>
       </c>
       <c r="AR11">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AS11">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="AT11">
         <v>7.2</v>
       </c>
       <c r="AU11">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV11">
         <v>14.5</v>
@@ -3268,16 +3280,16 @@
         <v>65</v>
       </c>
       <c r="BB11">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="BC11">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BD11">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE11">
-        <v>9.6</v>
+        <v>28</v>
       </c>
       <c r="BF11">
         <v>23</v>
@@ -3286,22 +3298,22 @@
         <v>60</v>
       </c>
       <c r="BH11">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BI11">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BJ11">
         <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>5</v>
+        <v>16.5</v>
       </c>
       <c r="BN11">
         <v>4.9</v>
@@ -3310,16 +3322,16 @@
         <v>4.4</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ11">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BT11">
         <v>6.8</v>
@@ -3328,25 +3340,267 @@
         <v>6</v>
       </c>
       <c r="BV11">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="BW11">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CB11" t="s">
-        <v>112</v>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12" t="s">
+        <v>104</v>
+      </c>
+      <c r="E12" t="s">
+        <v>115</v>
+      </c>
+      <c r="F12">
+        <v>1.04</v>
+      </c>
+      <c r="G12">
+        <v>1000</v>
+      </c>
+      <c r="H12">
+        <v>1.04</v>
+      </c>
+      <c r="I12">
+        <v>1000</v>
+      </c>
+      <c r="J12">
+        <v>1.01</v>
+      </c>
+      <c r="K12">
+        <v>950</v>
+      </c>
+      <c r="L12">
+        <v>1.28</v>
+      </c>
+      <c r="M12">
+        <v>1.01</v>
+      </c>
+      <c r="N12">
+        <v>1.57</v>
+      </c>
+      <c r="O12">
+        <v>1.19</v>
+      </c>
+      <c r="P12">
+        <v>1.57</v>
+      </c>
+      <c r="Q12">
+        <v>1.19</v>
+      </c>
+      <c r="R12">
+        <v>1.22</v>
+      </c>
+      <c r="S12">
+        <v>1.01</v>
+      </c>
+      <c r="T12">
+        <v>1.01</v>
+      </c>
+      <c r="U12">
+        <v>1.01</v>
+      </c>
+      <c r="V12">
+        <v>1.01</v>
+      </c>
+      <c r="W12">
+        <v>1.01</v>
+      </c>
+      <c r="X12">
+        <v>1000</v>
+      </c>
+      <c r="Y12">
+        <v>1000</v>
+      </c>
+      <c r="Z12">
+        <v>1000</v>
+      </c>
+      <c r="AA12">
+        <v>1000</v>
+      </c>
+      <c r="AB12">
+        <v>1000</v>
+      </c>
+      <c r="AC12">
+        <v>1000</v>
+      </c>
+      <c r="AD12">
+        <v>1000</v>
+      </c>
+      <c r="AE12">
+        <v>1000</v>
+      </c>
+      <c r="AF12">
+        <v>1000</v>
+      </c>
+      <c r="AG12">
+        <v>1000</v>
+      </c>
+      <c r="AH12">
+        <v>1000</v>
+      </c>
+      <c r="AI12">
+        <v>1000</v>
+      </c>
+      <c r="AJ12">
+        <v>1000</v>
+      </c>
+      <c r="AK12">
+        <v>1000</v>
+      </c>
+      <c r="AL12">
+        <v>1000</v>
+      </c>
+      <c r="AM12">
+        <v>1000</v>
+      </c>
+      <c r="AN12">
+        <v>1000</v>
+      </c>
+      <c r="AO12">
+        <v>1000</v>
+      </c>
+      <c r="AP12">
+        <v>1.03</v>
+      </c>
+      <c r="AQ12">
+        <v>1.03</v>
+      </c>
+      <c r="AR12">
+        <v>1.03</v>
+      </c>
+      <c r="AS12">
+        <v>1.03</v>
+      </c>
+      <c r="AT12">
+        <v>1.03</v>
+      </c>
+      <c r="AU12">
+        <v>1.03</v>
+      </c>
+      <c r="AV12">
+        <v>1.03</v>
+      </c>
+      <c r="AW12">
+        <v>1.03</v>
+      </c>
+      <c r="AX12">
+        <v>1.03</v>
+      </c>
+      <c r="AY12">
+        <v>1.03</v>
+      </c>
+      <c r="AZ12">
+        <v>1.03</v>
+      </c>
+      <c r="BA12">
+        <v>1.03</v>
+      </c>
+      <c r="BB12">
+        <v>1.03</v>
+      </c>
+      <c r="BC12">
+        <v>1.03</v>
+      </c>
+      <c r="BD12">
+        <v>1.03</v>
+      </c>
+      <c r="BE12">
+        <v>1.03</v>
+      </c>
+      <c r="BF12">
+        <v>1.01</v>
+      </c>
+      <c r="BG12">
+        <v>1.01</v>
+      </c>
+      <c r="BH12">
+        <v>1000</v>
+      </c>
+      <c r="BI12">
+        <v>1.01</v>
+      </c>
+      <c r="BJ12">
+        <v>1000</v>
+      </c>
+      <c r="BK12">
+        <v>1.01</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>1.01</v>
+      </c>
+      <c r="BN12">
+        <v>1000</v>
+      </c>
+      <c r="BO12">
+        <v>1.01</v>
+      </c>
+      <c r="BP12">
+        <v>1000</v>
+      </c>
+      <c r="BQ12">
+        <v>1.01</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
+        <v>1.01</v>
+      </c>
+      <c r="BT12">
+        <v>1000</v>
+      </c>
+      <c r="BU12">
+        <v>1.01</v>
+      </c>
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
+        <v>1.01</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
+        <v>1.01</v>
+      </c>
+      <c r="BZ12">
+        <v>1000</v>
+      </c>
+      <c r="CA12">
+        <v>1.01</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -340,7 +340,7 @@
     <t>Real Potosi</t>
   </si>
   <si>
-    <t>2026-07-21 11:21:35</t>
+    <t>2026-07-21 13:28:27</t>
   </si>
 </sst>
 </file>
@@ -934,127 +934,127 @@
         <v>100</v>
       </c>
       <c r="F2">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G2">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="H2">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="I2">
+        <v>3.95</v>
+      </c>
+      <c r="J2">
         <v>3.8</v>
       </c>
-      <c r="J2">
-        <v>3.85</v>
-      </c>
       <c r="K2">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L2">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M2">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N2">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="O2">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P2">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="Q2">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="R2">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="S2">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="T2">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="U2">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W2">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="X2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA2">
         <v>65</v>
       </c>
       <c r="AB2">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AC2">
         <v>9</v>
       </c>
       <c r="AD2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF2">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG2">
         <v>11</v>
       </c>
       <c r="AH2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ2">
         <v>25</v>
       </c>
       <c r="AK2">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AL2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AM2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN2">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AO2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AP2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS2">
         <v>55</v>
       </c>
       <c r="AT2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU2">
         <v>8.4</v>
@@ -1066,10 +1066,10 @@
         <v>32</v>
       </c>
       <c r="AX2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ2">
         <v>13</v>
@@ -1081,10 +1081,10 @@
         <v>22</v>
       </c>
       <c r="BC2">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE2">
         <v>46</v>
@@ -1093,67 +1093,67 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BH2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI2">
         <v>3.9</v>
       </c>
       <c r="BJ2">
+        <v>8.6</v>
+      </c>
+      <c r="BK2">
+        <v>6.6</v>
+      </c>
+      <c r="BL2">
+        <v>80</v>
+      </c>
+      <c r="BM2">
+        <v>19.5</v>
+      </c>
+      <c r="BN2">
+        <v>5.1</v>
+      </c>
+      <c r="BO2">
+        <v>4.8</v>
+      </c>
+      <c r="BP2">
+        <v>13</v>
+      </c>
+      <c r="BQ2">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BK2">
-        <v>7.6</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>13.5</v>
-      </c>
-      <c r="BN2">
-        <v>5.3</v>
-      </c>
-      <c r="BO2">
-        <v>4.7</v>
-      </c>
-      <c r="BP2">
-        <v>14</v>
-      </c>
-      <c r="BQ2">
-        <v>10</v>
       </c>
       <c r="BR2">
         <v>22</v>
       </c>
       <c r="BS2">
+        <v>11.5</v>
+      </c>
+      <c r="BT2">
+        <v>7.2</v>
+      </c>
+      <c r="BU2">
+        <v>6.6</v>
+      </c>
+      <c r="BV2">
+        <v>25</v>
+      </c>
+      <c r="BW2">
+        <v>13.5</v>
+      </c>
+      <c r="BX2">
+        <v>30</v>
+      </c>
+      <c r="BY2">
+        <v>16</v>
+      </c>
+      <c r="BZ2">
+        <v>15.5</v>
+      </c>
+      <c r="CA2">
         <v>9.6</v>
-      </c>
-      <c r="BT2">
-        <v>7</v>
-      </c>
-      <c r="BU2">
-        <v>6.2</v>
-      </c>
-      <c r="BV2">
-        <v>24</v>
-      </c>
-      <c r="BW2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BX2">
-        <v>29</v>
-      </c>
-      <c r="BY2">
-        <v>10.5</v>
-      </c>
-      <c r="BZ2">
-        <v>16</v>
-      </c>
-      <c r="CA2">
-        <v>9.4</v>
       </c>
       <c r="CB2" t="s">
         <v>108</v>
@@ -1176,43 +1176,43 @@
         <v>101</v>
       </c>
       <c r="F3">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G3">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I3">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J3">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K3">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L3">
         <v>1.65</v>
       </c>
       <c r="M3">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N3">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="O3">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="P3">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q3">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="R3">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S3">
         <v>6.2</v>
@@ -1224,43 +1224,43 @@
         <v>1.66</v>
       </c>
       <c r="V3">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W3">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X3">
         <v>8</v>
       </c>
       <c r="Y3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z3">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="AA3">
         <v>900</v>
       </c>
       <c r="AB3">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC3">
         <v>7.4</v>
       </c>
       <c r="AD3">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AE3">
-        <v>260</v>
+        <v>700</v>
       </c>
       <c r="AF3">
+        <v>11.5</v>
+      </c>
+      <c r="AG3">
         <v>12</v>
       </c>
-      <c r="AG3">
-        <v>12.5</v>
-      </c>
       <c r="AH3">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="AI3">
         <v>440</v>
@@ -1269,13 +1269,13 @@
         <v>900</v>
       </c>
       <c r="AK3">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="AL3">
         <v>160</v>
       </c>
       <c r="AM3">
-        <v>280</v>
+        <v>500</v>
       </c>
       <c r="AN3">
         <v>1000</v>
@@ -1284,64 +1284,64 @@
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ3">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AR3">
-        <v>8.6</v>
+        <v>15</v>
       </c>
       <c r="AS3">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AT3">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AU3">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="AV3">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX3">
         <v>10</v>
       </c>
-      <c r="AX3">
-        <v>5.9</v>
-      </c>
       <c r="AY3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AZ3">
-        <v>8.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BA3">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BB3">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="BC3">
-        <v>8.6</v>
+        <v>15</v>
       </c>
       <c r="BD3">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE3">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF3">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG3">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BH3">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BI3">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BJ3">
         <v>12.5</v>
@@ -1353,49 +1353,49 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>2.2</v>
+        <v>13.5</v>
       </c>
       <c r="BN3">
         <v>4.7</v>
       </c>
       <c r="BO3">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.99</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>2.12</v>
+        <v>11</v>
       </c>
       <c r="BT3">
         <v>7.8</v>
       </c>
       <c r="BU3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>2.12</v>
+        <v>11.5</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>2.16</v>
+        <v>12</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>2.12</v>
+        <v>11.5</v>
       </c>
       <c r="CB3" t="s">
         <v>108</v>
@@ -1418,25 +1418,25 @@
         <v>102</v>
       </c>
       <c r="F4">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G4">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I4">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="J4">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K4">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L4">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M4">
         <v>1.14</v>
@@ -1454,22 +1454,22 @@
         <v>2.78</v>
       </c>
       <c r="R4">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S4">
         <v>5.9</v>
       </c>
       <c r="T4">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U4">
         <v>1.7</v>
       </c>
       <c r="V4">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W4">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X4">
         <v>8.199999999999999</v>
@@ -1478,22 +1478,22 @@
         <v>12</v>
       </c>
       <c r="Z4">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AA4">
         <v>900</v>
       </c>
       <c r="AB4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE4">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="AF4">
         <v>12</v>
@@ -1502,25 +1502,25 @@
         <v>12</v>
       </c>
       <c r="AH4">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AI4">
         <v>540</v>
       </c>
       <c r="AJ4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK4">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AL4">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AM4">
         <v>280</v>
       </c>
       <c r="AN4">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO4">
         <v>1000</v>
@@ -1529,13 +1529,13 @@
         <v>7</v>
       </c>
       <c r="AQ4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR4">
         <v>23</v>
       </c>
       <c r="AS4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT4">
         <v>5.8</v>
@@ -1544,7 +1544,7 @@
         <v>6.4</v>
       </c>
       <c r="AV4">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AW4">
         <v>46</v>
@@ -1559,28 +1559,28 @@
         <v>22</v>
       </c>
       <c r="BA4">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="BB4">
+        <v>20</v>
+      </c>
+      <c r="BC4">
         <v>22</v>
       </c>
-      <c r="BC4">
+      <c r="BD4">
+        <v>46</v>
+      </c>
+      <c r="BE4">
+        <v>11.5</v>
+      </c>
+      <c r="BF4">
         <v>23</v>
       </c>
-      <c r="BD4">
-        <v>44</v>
-      </c>
-      <c r="BE4">
-        <v>10.5</v>
-      </c>
-      <c r="BF4">
-        <v>25</v>
-      </c>
       <c r="BG4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH4">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BI4">
         <v>2.26</v>
@@ -1595,49 +1595,49 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>2.24</v>
+        <v>14</v>
       </c>
       <c r="BN4">
         <v>4.6</v>
       </c>
       <c r="BO4">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP4">
         <v>18.5</v>
       </c>
       <c r="BQ4">
-        <v>2.02</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>2.16</v>
+        <v>11</v>
       </c>
       <c r="BT4">
         <v>7.8</v>
       </c>
       <c r="BU4">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>2.16</v>
+        <v>11.5</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>2.2</v>
+        <v>12.5</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>2.16</v>
+        <v>11.5</v>
       </c>
       <c r="CB4" t="s">
         <v>108</v>
@@ -1660,79 +1660,79 @@
         <v>103</v>
       </c>
       <c r="F5">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G5">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="H5">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="I5">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K5">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L5">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="M5">
         <v>1.11</v>
       </c>
       <c r="N5">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="O5">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="P5">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="Q5">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R5">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T5">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="U5">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="V5">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W5">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X5">
         <v>10.5</v>
       </c>
       <c r="Y5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z5">
         <v>27</v>
       </c>
       <c r="AA5">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="AB5">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AC5">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AD5">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE5">
         <v>75</v>
@@ -1741,40 +1741,40 @@
         <v>15</v>
       </c>
       <c r="AG5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH5">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AI5">
         <v>160</v>
       </c>
       <c r="AJ5">
+        <v>36</v>
+      </c>
+      <c r="AK5">
         <v>40</v>
       </c>
-      <c r="AK5">
-        <v>44</v>
-      </c>
       <c r="AL5">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM5">
         <v>580</v>
       </c>
       <c r="AN5">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AO5">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AP5">
         <v>8.800000000000001</v>
       </c>
       <c r="AQ5">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS5">
         <v>55</v>
@@ -1786,28 +1786,28 @@
         <v>6.4</v>
       </c>
       <c r="AV5">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW5">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AX5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY5">
         <v>10</v>
       </c>
       <c r="AZ5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA5">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD5">
         <v>36</v>
@@ -1816,13 +1816,13 @@
         <v>65</v>
       </c>
       <c r="BF5">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BG5">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BH5">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BI5">
         <v>2.64</v>
@@ -1837,19 +1837,19 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>17.5</v>
+        <v>2.44</v>
       </c>
       <c r="BN5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP5">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BR5">
         <v>1000</v>
@@ -1858,7 +1858,7 @@
         <v>13</v>
       </c>
       <c r="BT5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU5">
         <v>5</v>
@@ -1867,13 +1867,13 @@
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
@@ -1902,7 +1902,7 @@
         <v>104</v>
       </c>
       <c r="F6">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G6">
         <v>2.06</v>
@@ -1917,37 +1917,37 @@
         <v>3.7</v>
       </c>
       <c r="K6">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L6">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M6">
         <v>1.07</v>
       </c>
       <c r="N6">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O6">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P6">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="Q6">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="R6">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S6">
         <v>3.5</v>
       </c>
       <c r="T6">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U6">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V6">
         <v>1.31</v>
@@ -1956,28 +1956,28 @@
         <v>1.94</v>
       </c>
       <c r="X6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y6">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z6">
         <v>30</v>
       </c>
       <c r="AA6">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB6">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC6">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE6">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF6">
         <v>12.5</v>
@@ -1992,40 +1992,40 @@
         <v>55</v>
       </c>
       <c r="AJ6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK6">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL6">
         <v>36</v>
       </c>
       <c r="AM6">
-        <v>190</v>
+        <v>95</v>
       </c>
       <c r="AN6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO6">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AP6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AS6">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AT6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV6">
         <v>15.5</v>
@@ -2049,40 +2049,40 @@
         <v>21</v>
       </c>
       <c r="BC6">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD6">
         <v>32</v>
       </c>
       <c r="BE6">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="BF6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG6">
         <v>46</v>
       </c>
       <c r="BH6">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BI6">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ6">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK6">
         <v>6.6</v>
       </c>
       <c r="BL6">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BM6">
         <v>90</v>
       </c>
       <c r="BN6">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO6">
         <v>4.4</v>
@@ -2094,31 +2094,31 @@
         <v>9.6</v>
       </c>
       <c r="BR6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT6">
         <v>7.2</v>
       </c>
       <c r="BU6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV6">
         <v>32</v>
       </c>
       <c r="BW6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BX6">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BZ6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA6">
         <v>11.5</v>
@@ -2144,19 +2144,19 @@
         <v>105</v>
       </c>
       <c r="F7">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="G7">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="H7">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J7">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K7">
         <v>3.2</v>
@@ -2174,7 +2174,7 @@
         <v>1.55</v>
       </c>
       <c r="P7">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q7">
         <v>2.7</v>
@@ -2186,31 +2186,31 @@
         <v>5.7</v>
       </c>
       <c r="T7">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U7">
         <v>1.8</v>
       </c>
       <c r="V7">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W7">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Y7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA7">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AB7">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC7">
         <v>7.2</v>
@@ -2219,7 +2219,7 @@
         <v>17.5</v>
       </c>
       <c r="AE7">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF7">
         <v>13</v>
@@ -2228,16 +2228,16 @@
         <v>12</v>
       </c>
       <c r="AH7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI7">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ7">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL7">
         <v>65</v>
@@ -2246,7 +2246,7 @@
         <v>500</v>
       </c>
       <c r="AN7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO7">
         <v>95</v>
@@ -2255,43 +2255,43 @@
         <v>7.8</v>
       </c>
       <c r="AQ7">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AR7">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AS7">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AT7">
+        <v>6.6</v>
+      </c>
+      <c r="AU7">
         <v>6.8</v>
       </c>
-      <c r="AU7">
-        <v>6.4</v>
-      </c>
       <c r="AV7">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW7">
         <v>50</v>
       </c>
       <c r="AX7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7">
         <v>22</v>
       </c>
       <c r="BA7">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BB7">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BC7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BD7">
         <v>50</v>
@@ -2300,13 +2300,13 @@
         <v>28</v>
       </c>
       <c r="BF7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BG7">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="BH7">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BI7">
         <v>2.5</v>
@@ -2321,7 +2321,7 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN7">
         <v>4.9</v>
@@ -2330,16 +2330,16 @@
         <v>4.3</v>
       </c>
       <c r="BP7">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ7">
-        <v>9.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT7">
         <v>7</v>
@@ -2348,16 +2348,16 @@
         <v>5.9</v>
       </c>
       <c r="BV7">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BW7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
@@ -2389,19 +2389,19 @@
         <v>2.26</v>
       </c>
       <c r="G8">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H8">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="I8">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J8">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K8">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L8">
         <v>1.53</v>
@@ -2416,13 +2416,13 @@
         <v>1.48</v>
       </c>
       <c r="P8">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q8">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S8">
         <v>4.8</v>
@@ -2434,13 +2434,13 @@
         <v>1.9</v>
       </c>
       <c r="V8">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W8">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y8">
         <v>11.5</v>
@@ -2449,7 +2449,7 @@
         <v>26</v>
       </c>
       <c r="AA8">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AB8">
         <v>7.8</v>
@@ -2464,7 +2464,7 @@
         <v>60</v>
       </c>
       <c r="AF8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG8">
         <v>11.5</v>
@@ -2485,7 +2485,7 @@
         <v>55</v>
       </c>
       <c r="AM8">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="AN8">
         <v>27</v>
@@ -2527,28 +2527,28 @@
         <v>19.5</v>
       </c>
       <c r="BA8">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="BB8">
         <v>26</v>
       </c>
       <c r="BC8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD8">
         <v>46</v>
       </c>
       <c r="BE8">
-        <v>18.5</v>
+        <v>28</v>
       </c>
       <c r="BF8">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BG8">
         <v>60</v>
       </c>
       <c r="BH8">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BI8">
         <v>2.46</v>
@@ -2563,28 +2563,28 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BN8">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO8">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BP8">
         <v>18.5</v>
       </c>
       <c r="BQ8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BR8">
         <v>38</v>
       </c>
       <c r="BS8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT8">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU8">
         <v>5.2</v>
@@ -2599,13 +2599,13 @@
         <v>55</v>
       </c>
       <c r="BY8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ8">
         <v>38</v>
       </c>
       <c r="CA8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CB8" t="s">
         <v>108</v>
@@ -2628,22 +2628,22 @@
         <v>107</v>
       </c>
       <c r="F9">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="G9">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="H9">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="I9">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="J9">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K9">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L9">
         <v>1.3</v>
@@ -2652,202 +2652,202 @@
         <v>1.03</v>
       </c>
       <c r="N9">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O9">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P9">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q9">
         <v>1.64</v>
       </c>
       <c r="R9">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S9">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T9">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="U9">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="V9">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="W9">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AQ9">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>36</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="CB9" t="s">
         <v>108</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -340,7 +340,7 @@
     <t>Real Potosi</t>
   </si>
   <si>
-    <t>2026-07-21 13:28:27</t>
+    <t>2026-07-21 15:35:26</t>
   </si>
 </sst>
 </file>
@@ -934,226 +934,226 @@
         <v>100</v>
       </c>
       <c r="F2">
-        <v>2.04</v>
+        <v>15.5</v>
       </c>
       <c r="G2">
-        <v>2.06</v>
+        <v>17.5</v>
       </c>
       <c r="H2">
+        <v>1.43</v>
+      </c>
+      <c r="I2">
+        <v>1.44</v>
+      </c>
+      <c r="J2">
+        <v>4.1</v>
+      </c>
+      <c r="K2">
+        <v>4.2</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>2.82</v>
+      </c>
+      <c r="W2">
+        <v>1.07</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>1000</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>2.42</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>4.2</v>
+      </c>
+      <c r="AN2">
+        <v>15.5</v>
+      </c>
+      <c r="AO2">
+        <v>4.4</v>
+      </c>
+      <c r="AP2">
+        <v>1000</v>
+      </c>
+      <c r="AQ2">
+        <v>1000</v>
+      </c>
+      <c r="AR2">
+        <v>1000</v>
+      </c>
+      <c r="AS2">
+        <v>1000</v>
+      </c>
+      <c r="AT2">
+        <v>1000</v>
+      </c>
+      <c r="AU2">
+        <v>17.5</v>
+      </c>
+      <c r="AV2">
+        <v>1000</v>
+      </c>
+      <c r="AW2">
+        <v>1000</v>
+      </c>
+      <c r="AX2">
+        <v>1000</v>
+      </c>
+      <c r="AY2">
+        <v>17.5</v>
+      </c>
+      <c r="AZ2">
+        <v>1000</v>
+      </c>
+      <c r="BA2">
+        <v>2.24</v>
+      </c>
+      <c r="BB2">
+        <v>1000</v>
+      </c>
+      <c r="BC2">
+        <v>17.5</v>
+      </c>
+      <c r="BD2">
+        <v>17.5</v>
+      </c>
+      <c r="BE2">
+        <v>4</v>
+      </c>
+      <c r="BF2">
+        <v>12.5</v>
+      </c>
+      <c r="BG2">
         <v>3.85</v>
       </c>
-      <c r="I2">
-        <v>3.95</v>
-      </c>
-      <c r="J2">
-        <v>3.8</v>
-      </c>
-      <c r="K2">
-        <v>3.95</v>
-      </c>
-      <c r="L2">
-        <v>1.32</v>
-      </c>
-      <c r="M2">
-        <v>1.04</v>
-      </c>
-      <c r="N2">
-        <v>5.6</v>
-      </c>
-      <c r="O2">
-        <v>1.2</v>
-      </c>
-      <c r="P2">
-        <v>2.52</v>
-      </c>
-      <c r="Q2">
-        <v>1.63</v>
-      </c>
-      <c r="R2">
-        <v>1.61</v>
-      </c>
-      <c r="S2">
-        <v>2.58</v>
-      </c>
-      <c r="T2">
-        <v>1.57</v>
-      </c>
-      <c r="U2">
-        <v>2.68</v>
-      </c>
-      <c r="V2">
-        <v>1.34</v>
-      </c>
-      <c r="W2">
-        <v>1.92</v>
-      </c>
-      <c r="X2">
-        <v>23</v>
-      </c>
-      <c r="Y2">
-        <v>22</v>
-      </c>
-      <c r="Z2">
-        <v>30</v>
-      </c>
-      <c r="AA2">
-        <v>65</v>
-      </c>
-      <c r="AB2">
-        <v>13</v>
-      </c>
-      <c r="AC2">
-        <v>9</v>
-      </c>
-      <c r="AD2">
-        <v>15.5</v>
-      </c>
-      <c r="AE2">
-        <v>38</v>
-      </c>
-      <c r="AF2">
-        <v>15.5</v>
-      </c>
-      <c r="AG2">
-        <v>11</v>
-      </c>
-      <c r="AH2">
-        <v>14</v>
-      </c>
-      <c r="AI2">
-        <v>40</v>
-      </c>
-      <c r="AJ2">
-        <v>25</v>
-      </c>
-      <c r="AK2">
-        <v>19</v>
-      </c>
-      <c r="AL2">
-        <v>28</v>
-      </c>
-      <c r="AM2">
-        <v>60</v>
-      </c>
-      <c r="AN2">
-        <v>10.5</v>
-      </c>
-      <c r="AO2">
-        <v>28</v>
-      </c>
-      <c r="AP2">
-        <v>20</v>
-      </c>
-      <c r="AQ2">
-        <v>20</v>
-      </c>
-      <c r="AR2">
-        <v>27</v>
-      </c>
-      <c r="AS2">
-        <v>55</v>
-      </c>
-      <c r="AT2">
-        <v>12.5</v>
-      </c>
-      <c r="AU2">
-        <v>8.4</v>
-      </c>
-      <c r="AV2">
-        <v>14</v>
-      </c>
-      <c r="AW2">
-        <v>32</v>
-      </c>
-      <c r="AX2">
-        <v>14</v>
-      </c>
-      <c r="AY2">
-        <v>10</v>
-      </c>
-      <c r="AZ2">
-        <v>13</v>
-      </c>
-      <c r="BA2">
-        <v>34</v>
-      </c>
-      <c r="BB2">
-        <v>22</v>
-      </c>
-      <c r="BC2">
-        <v>17</v>
-      </c>
-      <c r="BD2">
-        <v>23</v>
-      </c>
-      <c r="BE2">
-        <v>46</v>
-      </c>
-      <c r="BF2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG2">
-        <v>25</v>
-      </c>
       <c r="BH2">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>108</v>
@@ -1176,226 +1176,226 @@
         <v>101</v>
       </c>
       <c r="F3">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="G3">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="H3">
+        <v>5.4</v>
+      </c>
+      <c r="I3">
+        <v>5.9</v>
+      </c>
+      <c r="J3">
+        <v>2.44</v>
+      </c>
+      <c r="K3">
+        <v>2.64</v>
+      </c>
+      <c r="L3">
+        <v>3.65</v>
+      </c>
+      <c r="M3">
+        <v>1.35</v>
+      </c>
+      <c r="N3">
+        <v>1.69</v>
+      </c>
+      <c r="O3">
+        <v>2.42</v>
+      </c>
+      <c r="P3">
+        <v>1.2</v>
+      </c>
+      <c r="Q3">
+        <v>5.6</v>
+      </c>
+      <c r="R3">
+        <v>1.04</v>
+      </c>
+      <c r="S3">
+        <v>19</v>
+      </c>
+      <c r="T3">
+        <v>3.75</v>
+      </c>
+      <c r="U3">
+        <v>1.31</v>
+      </c>
+      <c r="V3">
+        <v>1.2</v>
+      </c>
+      <c r="W3">
+        <v>1.68</v>
+      </c>
+      <c r="X3">
+        <v>4</v>
+      </c>
+      <c r="Y3">
+        <v>10.5</v>
+      </c>
+      <c r="Z3">
+        <v>55</v>
+      </c>
+      <c r="AA3">
+        <v>280</v>
+      </c>
+      <c r="AB3">
         <v>4.6</v>
       </c>
-      <c r="I3">
+      <c r="AC3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD3">
+        <v>44</v>
+      </c>
+      <c r="AE3">
+        <v>280</v>
+      </c>
+      <c r="AF3">
+        <v>12.5</v>
+      </c>
+      <c r="AG3">
+        <v>22</v>
+      </c>
+      <c r="AH3">
+        <v>990</v>
+      </c>
+      <c r="AI3">
+        <v>600</v>
+      </c>
+      <c r="AJ3">
+        <v>60</v>
+      </c>
+      <c r="AK3">
+        <v>85</v>
+      </c>
+      <c r="AL3">
+        <v>290</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>130</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>3.7</v>
+      </c>
+      <c r="AQ3">
+        <v>8</v>
+      </c>
+      <c r="AR3">
+        <v>30</v>
+      </c>
+      <c r="AS3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT3">
+        <v>4.1</v>
+      </c>
+      <c r="AU3">
+        <v>7.8</v>
+      </c>
+      <c r="AV3">
+        <v>30</v>
+      </c>
+      <c r="AW3">
+        <v>140</v>
+      </c>
+      <c r="AX3">
+        <v>10.5</v>
+      </c>
+      <c r="AY3">
+        <v>17</v>
+      </c>
+      <c r="AZ3">
+        <v>60</v>
+      </c>
+      <c r="BA3">
+        <v>190</v>
+      </c>
+      <c r="BB3">
+        <v>27</v>
+      </c>
+      <c r="BC3">
+        <v>60</v>
+      </c>
+      <c r="BD3">
+        <v>170</v>
+      </c>
+      <c r="BE3">
+        <v>12.5</v>
+      </c>
+      <c r="BF3">
+        <v>80</v>
+      </c>
+      <c r="BG3">
+        <v>9.4</v>
+      </c>
+      <c r="BH3">
+        <v>1.41</v>
+      </c>
+      <c r="BI3">
+        <v>1.32</v>
+      </c>
+      <c r="BJ3">
+        <v>950</v>
+      </c>
+      <c r="BK3">
+        <v>11</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BN3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO3">
         <v>5.2</v>
       </c>
-      <c r="J3">
-        <v>3.05</v>
-      </c>
-      <c r="K3">
-        <v>3.15</v>
-      </c>
-      <c r="L3">
-        <v>1.65</v>
-      </c>
-      <c r="M3">
-        <v>1.14</v>
-      </c>
-      <c r="N3">
-        <v>2.48</v>
-      </c>
-      <c r="O3">
-        <v>1.6</v>
-      </c>
-      <c r="P3">
-        <v>1.48</v>
-      </c>
-      <c r="Q3">
-        <v>2.82</v>
-      </c>
-      <c r="R3">
-        <v>1.16</v>
-      </c>
-      <c r="S3">
-        <v>6.2</v>
-      </c>
-      <c r="T3">
-        <v>2.26</v>
-      </c>
-      <c r="U3">
-        <v>1.66</v>
-      </c>
-      <c r="V3">
-        <v>1.23</v>
-      </c>
-      <c r="W3">
-        <v>1.86</v>
-      </c>
-      <c r="X3">
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>7.6</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT3">
+        <v>15.5</v>
+      </c>
+      <c r="BU3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
         <v>8</v>
       </c>
-      <c r="Y3">
-        <v>12</v>
-      </c>
-      <c r="Z3">
-        <v>50</v>
-      </c>
-      <c r="AA3">
-        <v>900</v>
-      </c>
-      <c r="AB3">
-        <v>7.2</v>
-      </c>
-      <c r="AC3">
-        <v>7.4</v>
-      </c>
-      <c r="AD3">
-        <v>36</v>
-      </c>
-      <c r="AE3">
-        <v>700</v>
-      </c>
-      <c r="AF3">
-        <v>11.5</v>
-      </c>
-      <c r="AG3">
-        <v>12</v>
-      </c>
-      <c r="AH3">
-        <v>46</v>
-      </c>
-      <c r="AI3">
-        <v>440</v>
-      </c>
-      <c r="AJ3">
-        <v>900</v>
-      </c>
-      <c r="AK3">
-        <v>46</v>
-      </c>
-      <c r="AL3">
-        <v>160</v>
-      </c>
-      <c r="AM3">
-        <v>500</v>
-      </c>
-      <c r="AN3">
-        <v>1000</v>
-      </c>
-      <c r="AO3">
-        <v>1000</v>
-      </c>
-      <c r="AP3">
-        <v>6.8</v>
-      </c>
-      <c r="AQ3">
-        <v>10</v>
-      </c>
-      <c r="AR3">
-        <v>15</v>
-      </c>
-      <c r="AS3">
-        <v>9.4</v>
-      </c>
-      <c r="AT3">
-        <v>5.5</v>
-      </c>
-      <c r="AU3">
-        <v>6.4</v>
-      </c>
-      <c r="AV3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX3">
-        <v>10</v>
-      </c>
-      <c r="AY3">
-        <v>10</v>
-      </c>
-      <c r="AZ3">
-        <v>12.5</v>
-      </c>
-      <c r="BA3">
-        <v>9.4</v>
-      </c>
-      <c r="BB3">
-        <v>13.5</v>
-      </c>
-      <c r="BC3">
-        <v>15</v>
-      </c>
-      <c r="BD3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF3">
-        <v>7.8</v>
-      </c>
-      <c r="BG3">
-        <v>9.6</v>
-      </c>
-      <c r="BH3">
-        <v>2.6</v>
-      </c>
-      <c r="BI3">
-        <v>2.2</v>
-      </c>
-      <c r="BJ3">
-        <v>12.5</v>
-      </c>
-      <c r="BK3">
-        <v>6.6</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>13.5</v>
-      </c>
-      <c r="BN3">
-        <v>4.7</v>
-      </c>
-      <c r="BO3">
-        <v>3.7</v>
-      </c>
-      <c r="BP3">
-        <v>1000</v>
-      </c>
-      <c r="BQ3">
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
         <v>8.199999999999999</v>
       </c>
-      <c r="BR3">
-        <v>1000</v>
-      </c>
-      <c r="BS3">
-        <v>11</v>
-      </c>
-      <c r="BT3">
-        <v>7.8</v>
-      </c>
-      <c r="BU3">
-        <v>6</v>
-      </c>
-      <c r="BV3">
-        <v>1000</v>
-      </c>
-      <c r="BW3">
-        <v>11.5</v>
-      </c>
-      <c r="BX3">
-        <v>1000</v>
-      </c>
-      <c r="BY3">
-        <v>12</v>
-      </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB3" t="s">
         <v>108</v>
@@ -1418,226 +1418,226 @@
         <v>102</v>
       </c>
       <c r="F4">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="G4">
-        <v>2.22</v>
+        <v>990</v>
       </c>
       <c r="H4">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="I4">
-        <v>5.1</v>
+        <v>980</v>
       </c>
       <c r="J4">
-        <v>2.96</v>
+        <v>1.02</v>
       </c>
       <c r="K4">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="L4">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N4">
-        <v>2.5</v>
+        <v>1.02</v>
       </c>
       <c r="O4">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="P4">
-        <v>1.49</v>
+        <v>1.02</v>
       </c>
       <c r="Q4">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="R4">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="S4">
-        <v>5.9</v>
+        <v>1.02</v>
       </c>
       <c r="T4">
-        <v>2.24</v>
+        <v>1.11</v>
       </c>
       <c r="U4">
-        <v>1.7</v>
+        <v>1.11</v>
       </c>
       <c r="V4">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="W4">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD4">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE4">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH4">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI4">
-        <v>540</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AL4">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR4">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU4">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV4">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AW4">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BA4">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BD4">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
-        <v>2.66</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>14</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
         <v>108</v>
@@ -1660,22 +1660,22 @@
         <v>103</v>
       </c>
       <c r="F5">
+        <v>2.28</v>
+      </c>
+      <c r="G5">
         <v>2.34</v>
-      </c>
-      <c r="G5">
-        <v>2.38</v>
       </c>
       <c r="H5">
         <v>3.8</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J5">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K5">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L5">
         <v>1.54</v>
@@ -1693,16 +1693,16 @@
         <v>1.67</v>
       </c>
       <c r="Q5">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="R5">
         <v>1.25</v>
       </c>
       <c r="S5">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T5">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="U5">
         <v>1.93</v>
@@ -1711,133 +1711,133 @@
         <v>1.33</v>
       </c>
       <c r="W5">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y5">
         <v>12</v>
       </c>
       <c r="Z5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA5">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="AB5">
         <v>8</v>
       </c>
       <c r="AC5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE5">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AF5">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AG5">
         <v>11.5</v>
       </c>
       <c r="AH5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI5">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AJ5">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK5">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AL5">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM5">
-        <v>580</v>
+        <v>170</v>
       </c>
       <c r="AN5">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AO5">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AP5">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AS5">
         <v>55</v>
       </c>
       <c r="AT5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV5">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW5">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AX5">
         <v>11.5</v>
       </c>
       <c r="AY5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB5">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BC5">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BD5">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BE5">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="BF5">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BG5">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BH5">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BI5">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="BJ5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>2.44</v>
+        <v>3.9</v>
       </c>
       <c r="BN5">
         <v>4.9</v>
@@ -1849,25 +1849,25 @@
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BT5">
         <v>6.8</v>
       </c>
       <c r="BU5">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX5">
         <v>1000</v>
@@ -1876,10 +1876,10 @@
         <v>14.5</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="CB5" t="s">
         <v>108</v>
@@ -1902,7 +1902,7 @@
         <v>104</v>
       </c>
       <c r="F6">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G6">
         <v>2.06</v>
@@ -1914,10 +1914,10 @@
         <v>4.2</v>
       </c>
       <c r="J6">
+        <v>3.65</v>
+      </c>
+      <c r="K6">
         <v>3.7</v>
-      </c>
-      <c r="K6">
-        <v>3.8</v>
       </c>
       <c r="L6">
         <v>1.41</v>
@@ -1926,28 +1926,28 @@
         <v>1.07</v>
       </c>
       <c r="N6">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O6">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P6">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Q6">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="R6">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S6">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="T6">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="U6">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V6">
         <v>1.31</v>
@@ -1959,25 +1959,25 @@
         <v>15</v>
       </c>
       <c r="Y6">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA6">
         <v>75</v>
       </c>
       <c r="AB6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC6">
         <v>8</v>
       </c>
       <c r="AD6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE6">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF6">
         <v>12.5</v>
@@ -1986,7 +1986,7 @@
         <v>10.5</v>
       </c>
       <c r="AH6">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AI6">
         <v>55</v>
@@ -1995,16 +1995,16 @@
         <v>23</v>
       </c>
       <c r="AK6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL6">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM6">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AN6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO6">
         <v>48</v>
@@ -2013,25 +2013,25 @@
         <v>14</v>
       </c>
       <c r="AQ6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS6">
         <v>65</v>
       </c>
       <c r="AT6">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU6">
         <v>7.8</v>
       </c>
       <c r="AV6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AX6">
         <v>11.5</v>
@@ -2040,28 +2040,28 @@
         <v>10</v>
       </c>
       <c r="AZ6">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA6">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BB6">
         <v>21</v>
       </c>
       <c r="BC6">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE6">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BF6">
         <v>13.5</v>
       </c>
       <c r="BG6">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BH6">
         <v>3.5</v>
@@ -2147,10 +2147,10 @@
         <v>2.24</v>
       </c>
       <c r="G7">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H7">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I7">
         <v>4.2</v>
@@ -2168,13 +2168,13 @@
         <v>1.13</v>
       </c>
       <c r="N7">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O7">
         <v>1.55</v>
       </c>
       <c r="P7">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q7">
         <v>2.7</v>
@@ -2195,19 +2195,19 @@
         <v>1.31</v>
       </c>
       <c r="W7">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X7">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y7">
         <v>11.5</v>
       </c>
       <c r="Z7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AA7">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB7">
         <v>7.2</v>
@@ -2231,7 +2231,7 @@
         <v>25</v>
       </c>
       <c r="AI7">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ7">
         <v>30</v>
@@ -2252,13 +2252,13 @@
         <v>95</v>
       </c>
       <c r="AP7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ7">
         <v>10.5</v>
       </c>
       <c r="AR7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS7">
         <v>85</v>
@@ -2297,16 +2297,16 @@
         <v>50</v>
       </c>
       <c r="BE7">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BF7">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BG7">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="BH7">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BI7">
         <v>2.5</v>
@@ -2321,7 +2321,7 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>15.5</v>
+        <v>34</v>
       </c>
       <c r="BN7">
         <v>4.9</v>
@@ -2333,13 +2333,13 @@
         <v>20</v>
       </c>
       <c r="BQ7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT7">
         <v>7</v>
@@ -2348,10 +2348,10 @@
         <v>5.9</v>
       </c>
       <c r="BV7">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BW7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX7">
         <v>65</v>
@@ -2389,10 +2389,10 @@
         <v>2.26</v>
       </c>
       <c r="G8">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H8">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="I8">
         <v>4</v>
@@ -2401,7 +2401,7 @@
         <v>3.2</v>
       </c>
       <c r="K8">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L8">
         <v>1.53</v>
@@ -2416,10 +2416,10 @@
         <v>1.48</v>
       </c>
       <c r="P8">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q8">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R8">
         <v>1.25</v>
@@ -2440,7 +2440,7 @@
         <v>1.76</v>
       </c>
       <c r="X8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Y8">
         <v>11.5</v>
@@ -2473,7 +2473,7 @@
         <v>21</v>
       </c>
       <c r="AI8">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ8">
         <v>30</v>
@@ -2527,28 +2527,28 @@
         <v>19.5</v>
       </c>
       <c r="BA8">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BB8">
         <v>26</v>
       </c>
       <c r="BC8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD8">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BE8">
         <v>28</v>
       </c>
       <c r="BF8">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BG8">
         <v>60</v>
       </c>
       <c r="BH8">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="BI8">
         <v>2.46</v>
@@ -2593,16 +2593,16 @@
         <v>36</v>
       </c>
       <c r="BW8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX8">
         <v>55</v>
       </c>
       <c r="BY8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="CA8">
         <v>12</v>
@@ -2628,10 +2628,10 @@
         <v>107</v>
       </c>
       <c r="F9">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G9">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="H9">
         <v>3.3</v>
@@ -2640,22 +2640,22 @@
         <v>3.45</v>
       </c>
       <c r="J9">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K9">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L9">
         <v>1.3</v>
       </c>
       <c r="M9">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N9">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="O9">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P9">
         <v>2.42</v>
@@ -2664,7 +2664,7 @@
         <v>1.64</v>
       </c>
       <c r="R9">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S9">
         <v>2.6</v>
@@ -2679,7 +2679,7 @@
         <v>1.41</v>
       </c>
       <c r="W9">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="X9">
         <v>26</v>
@@ -2688,7 +2688,7 @@
         <v>18</v>
       </c>
       <c r="Z9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA9">
         <v>55</v>
@@ -2721,16 +2721,16 @@
         <v>29</v>
       </c>
       <c r="AK9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM9">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AN9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO9">
         <v>23</v>
@@ -2745,7 +2745,7 @@
         <v>21</v>
       </c>
       <c r="AS9">
-        <v>8.4</v>
+        <v>38</v>
       </c>
       <c r="AT9">
         <v>12</v>
@@ -2757,7 +2757,7 @@
         <v>12</v>
       </c>
       <c r="AW9">
-        <v>7.8</v>
+        <v>26</v>
       </c>
       <c r="AX9">
         <v>14.5</v>
@@ -2769,16 +2769,16 @@
         <v>13</v>
       </c>
       <c r="BA9">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BB9">
         <v>21</v>
       </c>
       <c r="BC9">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BD9">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE9">
         <v>36</v>
@@ -2793,10 +2793,10 @@
         <v>4.4</v>
       </c>
       <c r="BI9">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ9">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK9">
         <v>6.6</v>
@@ -2805,13 +2805,13 @@
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="BN9">
         <v>5.6</v>
       </c>
       <c r="BO9">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP9">
         <v>15</v>
@@ -2820,7 +2820,7 @@
         <v>11</v>
       </c>
       <c r="BR9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS9">
         <v>17</v>
@@ -2829,22 +2829,22 @@
         <v>7.2</v>
       </c>
       <c r="BU9">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BW9">
         <v>17</v>
       </c>
       <c r="BX9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BY9">
         <v>21</v>
       </c>
       <c r="BZ9">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CA9">
         <v>12.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="99">
   <si>
     <t>League</t>
   </si>
@@ -256,12 +256,6 @@
     <t>SnapshotTS</t>
   </si>
   <si>
-    <t>Swedish Superettan</t>
-  </si>
-  <si>
-    <t>Moroccan Botola Pro 1</t>
-  </si>
-  <si>
     <t>Ecuadorian Serie A</t>
   </si>
   <si>
@@ -277,12 +271,6 @@
     <t>2026-07-21</t>
   </si>
   <si>
-    <t>17:00:00</t>
-  </si>
-  <si>
-    <t>18:00:00</t>
-  </si>
-  <si>
     <t>21:30:00</t>
   </si>
   <si>
@@ -292,15 +280,6 @@
     <t>23:00:00</t>
   </si>
   <si>
-    <t>Falkenbergs</t>
-  </si>
-  <si>
-    <t>Union de Touarga</t>
-  </si>
-  <si>
-    <t>Olympique Dcheira</t>
-  </si>
-  <si>
     <t>Libertad FC</t>
   </si>
   <si>
@@ -313,16 +292,7 @@
     <t>Avai</t>
   </si>
   <si>
-    <t>Club Ind. Petrolero</t>
-  </si>
-  <si>
-    <t>Helsingborgs</t>
-  </si>
-  <si>
-    <t>Jeunesse Massira</t>
-  </si>
-  <si>
-    <t>US Amal Tiznit</t>
+    <t>Club Independiente Petrolero</t>
   </si>
   <si>
     <t>Delfin</t>
@@ -340,7 +310,7 @@
     <t>Real Potosi</t>
   </si>
   <si>
-    <t>2026-07-21 15:35:26</t>
+    <t>2026-07-21 17:42:25</t>
   </si>
 </sst>
 </file>
@@ -672,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -922,241 +892,241 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F2">
-        <v>15.5</v>
+        <v>2.38</v>
       </c>
       <c r="G2">
-        <v>17.5</v>
+        <v>2.44</v>
       </c>
       <c r="H2">
-        <v>1.43</v>
+        <v>3.6</v>
       </c>
       <c r="I2">
-        <v>1.44</v>
+        <v>3.75</v>
       </c>
       <c r="J2">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="K2">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V2">
-        <v>2.82</v>
+        <v>1.37</v>
       </c>
       <c r="W2">
-        <v>1.07</v>
+        <v>1.69</v>
       </c>
       <c r="X2">
+        <v>9.6</v>
+      </c>
+      <c r="Y2">
+        <v>11</v>
+      </c>
+      <c r="Z2">
+        <v>24</v>
+      </c>
+      <c r="AA2">
+        <v>170</v>
+      </c>
+      <c r="AB2">
+        <v>8</v>
+      </c>
+      <c r="AC2">
+        <v>7.2</v>
+      </c>
+      <c r="AD2">
+        <v>16</v>
+      </c>
+      <c r="AE2">
+        <v>55</v>
+      </c>
+      <c r="AF2">
+        <v>14</v>
+      </c>
+      <c r="AG2">
+        <v>12</v>
+      </c>
+      <c r="AH2">
+        <v>21</v>
+      </c>
+      <c r="AI2">
+        <v>160</v>
+      </c>
+      <c r="AJ2">
+        <v>34</v>
+      </c>
+      <c r="AK2">
+        <v>32</v>
+      </c>
+      <c r="AL2">
+        <v>55</v>
+      </c>
+      <c r="AM2">
+        <v>580</v>
+      </c>
+      <c r="AN2">
+        <v>32</v>
+      </c>
+      <c r="AO2">
+        <v>70</v>
+      </c>
+      <c r="AP2">
+        <v>8.6</v>
+      </c>
+      <c r="AQ2">
+        <v>10</v>
+      </c>
+      <c r="AR2">
+        <v>22</v>
+      </c>
+      <c r="AS2">
+        <v>46</v>
+      </c>
+      <c r="AT2">
+        <v>7.2</v>
+      </c>
+      <c r="AU2">
+        <v>6.6</v>
+      </c>
+      <c r="AV2">
+        <v>14.5</v>
+      </c>
+      <c r="AW2">
+        <v>42</v>
+      </c>
+      <c r="AX2">
+        <v>12</v>
+      </c>
+      <c r="AY2">
+        <v>10.5</v>
+      </c>
+      <c r="AZ2">
+        <v>18.5</v>
+      </c>
+      <c r="BA2">
+        <v>60</v>
+      </c>
+      <c r="BB2">
+        <v>27</v>
+      </c>
+      <c r="BC2">
+        <v>26</v>
+      </c>
+      <c r="BD2">
+        <v>46</v>
+      </c>
+      <c r="BE2">
+        <v>28</v>
+      </c>
+      <c r="BF2">
+        <v>27</v>
+      </c>
+      <c r="BG2">
+        <v>55</v>
+      </c>
+      <c r="BH2">
+        <v>2.84</v>
+      </c>
+      <c r="BI2">
+        <v>2.66</v>
+      </c>
+      <c r="BJ2">
+        <v>10.5</v>
+      </c>
+      <c r="BK2">
+        <v>7</v>
+      </c>
+      <c r="BL2">
         <v>1000</v>
       </c>
-      <c r="Y2">
+      <c r="BM2">
+        <v>19.5</v>
+      </c>
+      <c r="BN2">
+        <v>5</v>
+      </c>
+      <c r="BO2">
+        <v>4.5</v>
+      </c>
+      <c r="BP2">
+        <v>19.5</v>
+      </c>
+      <c r="BQ2">
+        <v>10</v>
+      </c>
+      <c r="BR2">
+        <v>40</v>
+      </c>
+      <c r="BS2">
+        <v>14</v>
+      </c>
+      <c r="BT2">
+        <v>6.6</v>
+      </c>
+      <c r="BU2">
+        <v>5.1</v>
+      </c>
+      <c r="BV2">
+        <v>34</v>
+      </c>
+      <c r="BW2">
+        <v>13.5</v>
+      </c>
+      <c r="BX2">
         <v>1000</v>
       </c>
-      <c r="Z2">
-        <v>1000</v>
-      </c>
-      <c r="AA2">
-        <v>1000</v>
-      </c>
-      <c r="AB2">
-        <v>1000</v>
-      </c>
-      <c r="AC2">
-        <v>1000</v>
-      </c>
-      <c r="AD2">
-        <v>1000</v>
-      </c>
-      <c r="AE2">
-        <v>1000</v>
-      </c>
-      <c r="AF2">
-        <v>1000</v>
-      </c>
-      <c r="AG2">
-        <v>1000</v>
-      </c>
-      <c r="AH2">
-        <v>1000</v>
-      </c>
-      <c r="AI2">
-        <v>2.42</v>
-      </c>
-      <c r="AJ2">
-        <v>1000</v>
-      </c>
-      <c r="AK2">
-        <v>1000</v>
-      </c>
-      <c r="AL2">
-        <v>1000</v>
-      </c>
-      <c r="AM2">
-        <v>4.2</v>
-      </c>
-      <c r="AN2">
-        <v>15.5</v>
-      </c>
-      <c r="AO2">
-        <v>4.4</v>
-      </c>
-      <c r="AP2">
-        <v>1000</v>
-      </c>
-      <c r="AQ2">
-        <v>1000</v>
-      </c>
-      <c r="AR2">
-        <v>1000</v>
-      </c>
-      <c r="AS2">
-        <v>1000</v>
-      </c>
-      <c r="AT2">
-        <v>1000</v>
-      </c>
-      <c r="AU2">
-        <v>17.5</v>
-      </c>
-      <c r="AV2">
-        <v>1000</v>
-      </c>
-      <c r="AW2">
-        <v>1000</v>
-      </c>
-      <c r="AX2">
-        <v>1000</v>
-      </c>
-      <c r="AY2">
-        <v>17.5</v>
-      </c>
-      <c r="AZ2">
-        <v>1000</v>
-      </c>
-      <c r="BA2">
-        <v>2.24</v>
-      </c>
-      <c r="BB2">
-        <v>1000</v>
-      </c>
-      <c r="BC2">
-        <v>17.5</v>
-      </c>
-      <c r="BD2">
-        <v>17.5</v>
-      </c>
-      <c r="BE2">
-        <v>4</v>
-      </c>
-      <c r="BF2">
-        <v>12.5</v>
-      </c>
-      <c r="BG2">
-        <v>3.85</v>
-      </c>
-      <c r="BH2">
-        <v>0</v>
-      </c>
-      <c r="BI2">
-        <v>0</v>
-      </c>
-      <c r="BJ2">
-        <v>0</v>
-      </c>
-      <c r="BK2">
-        <v>0</v>
-      </c>
-      <c r="BL2">
-        <v>0</v>
-      </c>
-      <c r="BM2">
-        <v>0</v>
-      </c>
-      <c r="BN2">
-        <v>0</v>
-      </c>
-      <c r="BO2">
-        <v>0</v>
-      </c>
-      <c r="BP2">
-        <v>0</v>
-      </c>
-      <c r="BQ2">
-        <v>0</v>
-      </c>
-      <c r="BR2">
-        <v>0</v>
-      </c>
-      <c r="BS2">
-        <v>0</v>
-      </c>
-      <c r="BT2">
-        <v>0</v>
-      </c>
-      <c r="BU2">
-        <v>0</v>
-      </c>
-      <c r="BV2">
-        <v>0</v>
-      </c>
-      <c r="BW2">
-        <v>0</v>
-      </c>
-      <c r="BX2">
-        <v>0</v>
-      </c>
       <c r="BY2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BZ2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="CA2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="CB2" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1164,483 +1134,483 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" t="s">
         <v>86</v>
       </c>
-      <c r="C3" t="s">
-        <v>88</v>
-      </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="F3">
-        <v>2.26</v>
+        <v>1.94</v>
       </c>
       <c r="G3">
-        <v>2.44</v>
+        <v>1.95</v>
       </c>
       <c r="H3">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="I3">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="J3">
-        <v>2.44</v>
+        <v>3.8</v>
       </c>
       <c r="K3">
-        <v>2.64</v>
+        <v>3.85</v>
       </c>
       <c r="L3">
-        <v>3.65</v>
+        <v>1.4</v>
       </c>
       <c r="M3">
-        <v>1.35</v>
+        <v>1.07</v>
       </c>
       <c r="N3">
-        <v>1.69</v>
+        <v>4.2</v>
       </c>
       <c r="O3">
-        <v>2.42</v>
+        <v>1.29</v>
       </c>
       <c r="P3">
-        <v>1.2</v>
+        <v>2.06</v>
       </c>
       <c r="Q3">
-        <v>5.6</v>
+        <v>1.93</v>
       </c>
       <c r="R3">
-        <v>1.04</v>
+        <v>1.41</v>
       </c>
       <c r="S3">
-        <v>19</v>
+        <v>3.3</v>
       </c>
       <c r="T3">
-        <v>3.75</v>
+        <v>1.82</v>
       </c>
       <c r="U3">
-        <v>1.31</v>
+        <v>2.2</v>
       </c>
       <c r="V3">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="W3">
-        <v>1.68</v>
+        <v>2.04</v>
       </c>
       <c r="X3">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="Y3">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="Z3">
+        <v>36</v>
+      </c>
+      <c r="AA3">
+        <v>100</v>
+      </c>
+      <c r="AB3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC3">
+        <v>8.4</v>
+      </c>
+      <c r="AD3">
+        <v>17</v>
+      </c>
+      <c r="AE3">
         <v>55</v>
       </c>
-      <c r="AA3">
-        <v>280</v>
-      </c>
-      <c r="AB3">
-        <v>4.6</v>
-      </c>
-      <c r="AC3">
+      <c r="AF3">
+        <v>11.5</v>
+      </c>
+      <c r="AG3">
         <v>9.800000000000001</v>
       </c>
-      <c r="AD3">
-        <v>44</v>
-      </c>
-      <c r="AE3">
-        <v>280</v>
-      </c>
-      <c r="AF3">
-        <v>12.5</v>
-      </c>
-      <c r="AG3">
-        <v>22</v>
-      </c>
       <c r="AH3">
-        <v>990</v>
+        <v>17.5</v>
       </c>
       <c r="AI3">
-        <v>600</v>
+        <v>60</v>
       </c>
       <c r="AJ3">
+        <v>21</v>
+      </c>
+      <c r="AK3">
+        <v>18.5</v>
+      </c>
+      <c r="AL3">
+        <v>32</v>
+      </c>
+      <c r="AM3">
+        <v>85</v>
+      </c>
+      <c r="AN3">
+        <v>14</v>
+      </c>
+      <c r="AO3">
         <v>60</v>
       </c>
-      <c r="AK3">
+      <c r="AP3">
+        <v>15</v>
+      </c>
+      <c r="AQ3">
+        <v>16.5</v>
+      </c>
+      <c r="AR3">
+        <v>34</v>
+      </c>
+      <c r="AS3">
         <v>85</v>
       </c>
-      <c r="AL3">
-        <v>290</v>
-      </c>
-      <c r="AM3">
+      <c r="AT3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU3">
+        <v>8</v>
+      </c>
+      <c r="AV3">
+        <v>16</v>
+      </c>
+      <c r="AW3">
+        <v>50</v>
+      </c>
+      <c r="AX3">
+        <v>11</v>
+      </c>
+      <c r="AY3">
+        <v>9.6</v>
+      </c>
+      <c r="AZ3">
+        <v>16.5</v>
+      </c>
+      <c r="BA3">
+        <v>50</v>
+      </c>
+      <c r="BB3">
+        <v>19.5</v>
+      </c>
+      <c r="BC3">
+        <v>17.5</v>
+      </c>
+      <c r="BD3">
+        <v>30</v>
+      </c>
+      <c r="BE3">
+        <v>75</v>
+      </c>
+      <c r="BF3">
+        <v>13</v>
+      </c>
+      <c r="BG3">
+        <v>48</v>
+      </c>
+      <c r="BH3">
+        <v>3.8</v>
+      </c>
+      <c r="BI3">
+        <v>3.15</v>
+      </c>
+      <c r="BJ3">
         <v>1000</v>
       </c>
-      <c r="AN3">
-        <v>130</v>
-      </c>
-      <c r="AO3">
-        <v>1000</v>
-      </c>
-      <c r="AP3">
-        <v>3.7</v>
-      </c>
-      <c r="AQ3">
-        <v>8</v>
-      </c>
-      <c r="AR3">
-        <v>30</v>
-      </c>
-      <c r="AS3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT3">
-        <v>4.1</v>
-      </c>
-      <c r="AU3">
-        <v>7.8</v>
-      </c>
-      <c r="AV3">
-        <v>30</v>
-      </c>
-      <c r="AW3">
-        <v>140</v>
-      </c>
-      <c r="AX3">
-        <v>10.5</v>
-      </c>
-      <c r="AY3">
-        <v>17</v>
-      </c>
-      <c r="AZ3">
-        <v>60</v>
-      </c>
-      <c r="BA3">
-        <v>190</v>
-      </c>
-      <c r="BB3">
-        <v>27</v>
-      </c>
-      <c r="BC3">
-        <v>60</v>
-      </c>
-      <c r="BD3">
-        <v>170</v>
-      </c>
-      <c r="BE3">
-        <v>12.5</v>
-      </c>
-      <c r="BF3">
-        <v>80</v>
-      </c>
-      <c r="BG3">
-        <v>9.4</v>
-      </c>
-      <c r="BH3">
-        <v>1.41</v>
-      </c>
-      <c r="BI3">
-        <v>1.32</v>
-      </c>
-      <c r="BJ3">
-        <v>950</v>
-      </c>
       <c r="BK3">
-        <v>11</v>
+        <v>3.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>8.199999999999999</v>
+        <v>90</v>
       </c>
       <c r="BN3">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>7.6</v>
+        <v>3.7</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>8.199999999999999</v>
+        <v>2.78</v>
       </c>
       <c r="BT3">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>8</v>
+        <v>2.78</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>8.199999999999999</v>
+        <v>2.78</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>8.199999999999999</v>
+        <v>2.78</v>
       </c>
       <c r="CB3" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" t="s">
         <v>86</v>
       </c>
-      <c r="C4" t="s">
-        <v>88</v>
-      </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="F4">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="G4">
-        <v>990</v>
+        <v>2.28</v>
       </c>
       <c r="H4">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="I4">
-        <v>980</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>1.02</v>
+        <v>3.25</v>
       </c>
       <c r="K4">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="M4">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="N4">
-        <v>1.02</v>
+        <v>2.74</v>
       </c>
       <c r="O4">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="P4">
-        <v>1.02</v>
+        <v>1.58</v>
       </c>
       <c r="Q4">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="R4">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="S4">
-        <v>1.02</v>
+        <v>5.7</v>
       </c>
       <c r="T4">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="U4">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="V4">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>80</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>75</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>80</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="CB4" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1648,37 +1618,37 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" t="s">
         <v>86</v>
       </c>
-      <c r="C5" t="s">
-        <v>89</v>
-      </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F5">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G5">
         <v>2.34</v>
       </c>
       <c r="H5">
+        <v>3.75</v>
+      </c>
+      <c r="I5">
         <v>3.8</v>
       </c>
-      <c r="I5">
-        <v>4.1</v>
-      </c>
       <c r="J5">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K5">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L5">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M5">
         <v>1.11</v>
@@ -1687,52 +1657,52 @@
         <v>3</v>
       </c>
       <c r="O5">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P5">
         <v>1.67</v>
       </c>
       <c r="Q5">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R5">
         <v>1.25</v>
       </c>
       <c r="S5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T5">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U5">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="V5">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W5">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA5">
         <v>80</v>
       </c>
       <c r="AB5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE5">
         <v>55</v>
@@ -1741,16 +1711,16 @@
         <v>13.5</v>
       </c>
       <c r="AG5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH5">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AI5">
         <v>75</v>
       </c>
       <c r="AJ5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK5">
         <v>29</v>
@@ -1759,13 +1729,13 @@
         <v>55</v>
       </c>
       <c r="AM5">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AN5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO5">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AP5">
         <v>9.199999999999999</v>
@@ -1777,22 +1747,22 @@
         <v>22</v>
       </c>
       <c r="AS5">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AT5">
         <v>7.2</v>
       </c>
       <c r="AU5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW5">
         <v>48</v>
       </c>
       <c r="AX5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY5">
         <v>10.5</v>
@@ -1801,76 +1771,76 @@
         <v>19.5</v>
       </c>
       <c r="BA5">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BB5">
+        <v>28</v>
+      </c>
+      <c r="BC5">
         <v>27</v>
       </c>
-      <c r="BC5">
+      <c r="BD5">
+        <v>46</v>
+      </c>
+      <c r="BE5">
+        <v>110</v>
+      </c>
+      <c r="BF5">
         <v>25</v>
       </c>
-      <c r="BD5">
-        <v>40</v>
-      </c>
-      <c r="BE5">
-        <v>100</v>
-      </c>
-      <c r="BF5">
-        <v>23</v>
-      </c>
       <c r="BG5">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BH5">
         <v>2.88</v>
       </c>
       <c r="BI5">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BJ5">
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>3.9</v>
+        <v>18.5</v>
       </c>
       <c r="BN5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO5">
         <v>4.4</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ5">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS5">
         <v>13.5</v>
       </c>
       <c r="BT5">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU5">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW5">
         <v>13</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY5">
         <v>14.5</v>
@@ -1882,7 +1852,7 @@
         <v>13.5</v>
       </c>
       <c r="CB5" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1890,967 +1860,241 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F6">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="G6">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="H6">
+        <v>3.3</v>
+      </c>
+      <c r="I6">
+        <v>3.55</v>
+      </c>
+      <c r="J6">
+        <v>3.75</v>
+      </c>
+      <c r="K6">
         <v>4.1</v>
       </c>
-      <c r="I6">
-        <v>4.2</v>
-      </c>
-      <c r="J6">
-        <v>3.65</v>
-      </c>
-      <c r="K6">
-        <v>3.7</v>
-      </c>
       <c r="L6">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="M6">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="N6">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="O6">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="P6">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="Q6">
-        <v>1.89</v>
+        <v>1.63</v>
       </c>
       <c r="R6">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="S6">
-        <v>3.3</v>
+        <v>2.58</v>
       </c>
       <c r="T6">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="U6">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="V6">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="W6">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="X6">
+        <v>24</v>
+      </c>
+      <c r="Y6">
+        <v>18.5</v>
+      </c>
+      <c r="Z6">
+        <v>27</v>
+      </c>
+      <c r="AA6">
+        <v>70</v>
+      </c>
+      <c r="AB6">
+        <v>14.5</v>
+      </c>
+      <c r="AC6">
+        <v>9.6</v>
+      </c>
+      <c r="AD6">
         <v>15</v>
       </c>
-      <c r="Y6">
-        <v>16.5</v>
-      </c>
-      <c r="Z6">
-        <v>32</v>
-      </c>
-      <c r="AA6">
-        <v>75</v>
-      </c>
-      <c r="AB6">
-        <v>9.6</v>
-      </c>
-      <c r="AC6">
+      <c r="AE6">
+        <v>36</v>
+      </c>
+      <c r="AF6">
+        <v>17</v>
+      </c>
+      <c r="AG6">
+        <v>12</v>
+      </c>
+      <c r="AH6">
+        <v>16</v>
+      </c>
+      <c r="AI6">
+        <v>38</v>
+      </c>
+      <c r="AJ6">
+        <v>28</v>
+      </c>
+      <c r="AK6">
+        <v>22</v>
+      </c>
+      <c r="AL6">
+        <v>30</v>
+      </c>
+      <c r="AM6">
+        <v>70</v>
+      </c>
+      <c r="AN6">
+        <v>12</v>
+      </c>
+      <c r="AO6">
+        <v>26</v>
+      </c>
+      <c r="AP6">
+        <v>19</v>
+      </c>
+      <c r="AQ6">
+        <v>15</v>
+      </c>
+      <c r="AR6">
+        <v>21</v>
+      </c>
+      <c r="AS6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT6">
+        <v>11.5</v>
+      </c>
+      <c r="AU6">
         <v>8</v>
       </c>
-      <c r="AD6">
-        <v>15.5</v>
-      </c>
-      <c r="AE6">
-        <v>46</v>
-      </c>
-      <c r="AF6">
-        <v>12.5</v>
-      </c>
-      <c r="AG6">
-        <v>10.5</v>
-      </c>
-      <c r="AH6">
-        <v>16.5</v>
-      </c>
-      <c r="AI6">
-        <v>55</v>
-      </c>
-      <c r="AJ6">
+      <c r="AV6">
+        <v>12</v>
+      </c>
+      <c r="AW6">
+        <v>27</v>
+      </c>
+      <c r="AX6">
+        <v>14</v>
+      </c>
+      <c r="AY6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ6">
+        <v>13</v>
+      </c>
+      <c r="BA6">
+        <v>27</v>
+      </c>
+      <c r="BB6">
         <v>23</v>
-      </c>
-      <c r="AK6">
-        <v>19</v>
-      </c>
-      <c r="AL6">
-        <v>32</v>
-      </c>
-      <c r="AM6">
-        <v>85</v>
-      </c>
-      <c r="AN6">
-        <v>14</v>
-      </c>
-      <c r="AO6">
-        <v>48</v>
-      </c>
-      <c r="AP6">
-        <v>14</v>
-      </c>
-      <c r="AQ6">
-        <v>16</v>
-      </c>
-      <c r="AR6">
-        <v>28</v>
-      </c>
-      <c r="AS6">
-        <v>65</v>
-      </c>
-      <c r="AT6">
-        <v>9.4</v>
-      </c>
-      <c r="AU6">
-        <v>7.8</v>
-      </c>
-      <c r="AV6">
-        <v>15</v>
-      </c>
-      <c r="AW6">
-        <v>44</v>
-      </c>
-      <c r="AX6">
-        <v>11.5</v>
-      </c>
-      <c r="AY6">
-        <v>10</v>
-      </c>
-      <c r="AZ6">
-        <v>16</v>
-      </c>
-      <c r="BA6">
-        <v>48</v>
-      </c>
-      <c r="BB6">
-        <v>21</v>
       </c>
       <c r="BC6">
         <v>18.5</v>
       </c>
       <c r="BD6">
-        <v>30</v>
+        <v>7.8</v>
       </c>
       <c r="BE6">
+        <v>42</v>
+      </c>
+      <c r="BF6">
+        <v>10</v>
+      </c>
+      <c r="BG6">
+        <v>20</v>
+      </c>
+      <c r="BH6">
+        <v>4.4</v>
+      </c>
+      <c r="BI6">
+        <v>3.55</v>
+      </c>
+      <c r="BJ6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK6">
+        <v>1.04</v>
+      </c>
+      <c r="BL6">
         <v>80</v>
       </c>
-      <c r="BF6">
-        <v>13.5</v>
-      </c>
-      <c r="BG6">
-        <v>40</v>
-      </c>
-      <c r="BH6">
-        <v>3.5</v>
-      </c>
-      <c r="BI6">
-        <v>3.25</v>
-      </c>
-      <c r="BJ6">
-        <v>9.4</v>
-      </c>
-      <c r="BK6">
-        <v>6.6</v>
-      </c>
-      <c r="BL6">
-        <v>110</v>
-      </c>
       <c r="BM6">
-        <v>90</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
+        <v>5.6</v>
+      </c>
+      <c r="BO6">
         <v>4.7</v>
-      </c>
-      <c r="BO6">
-        <v>4.4</v>
       </c>
       <c r="BP6">
         <v>14.5</v>
       </c>
       <c r="BQ6">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BS6">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
         <v>7.2</v>
       </c>
       <c r="BU6">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV6">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BW6">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="BY6">
-        <v>15</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="CA6">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" spans="1:80">
-      <c r="A7" t="s">
-        <v>84</v>
-      </c>
-      <c r="B7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E7" t="s">
-        <v>105</v>
-      </c>
-      <c r="F7">
-        <v>2.24</v>
-      </c>
-      <c r="G7">
-        <v>2.28</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>4.2</v>
-      </c>
-      <c r="J7">
-        <v>3.15</v>
-      </c>
-      <c r="K7">
-        <v>3.2</v>
-      </c>
-      <c r="L7">
-        <v>1.58</v>
-      </c>
-      <c r="M7">
-        <v>1.13</v>
-      </c>
-      <c r="N7">
-        <v>2.74</v>
-      </c>
-      <c r="O7">
-        <v>1.55</v>
-      </c>
-      <c r="P7">
-        <v>1.58</v>
-      </c>
-      <c r="Q7">
-        <v>2.7</v>
-      </c>
-      <c r="R7">
-        <v>1.2</v>
-      </c>
-      <c r="S7">
-        <v>5.7</v>
-      </c>
-      <c r="T7">
-        <v>2.18</v>
-      </c>
-      <c r="U7">
-        <v>1.8</v>
-      </c>
-      <c r="V7">
-        <v>1.31</v>
-      </c>
-      <c r="W7">
-        <v>1.78</v>
-      </c>
-      <c r="X7">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Y7">
-        <v>11.5</v>
-      </c>
-      <c r="Z7">
-        <v>28</v>
-      </c>
-      <c r="AA7">
-        <v>95</v>
-      </c>
-      <c r="AB7">
-        <v>7.2</v>
-      </c>
-      <c r="AC7">
-        <v>7.2</v>
-      </c>
-      <c r="AD7">
-        <v>17.5</v>
-      </c>
-      <c r="AE7">
-        <v>70</v>
-      </c>
-      <c r="AF7">
-        <v>13</v>
-      </c>
-      <c r="AG7">
-        <v>12</v>
-      </c>
-      <c r="AH7">
-        <v>25</v>
-      </c>
-      <c r="AI7">
-        <v>90</v>
-      </c>
-      <c r="AJ7">
-        <v>30</v>
-      </c>
-      <c r="AK7">
-        <v>32</v>
-      </c>
-      <c r="AL7">
-        <v>65</v>
-      </c>
-      <c r="AM7">
-        <v>500</v>
-      </c>
-      <c r="AN7">
-        <v>32</v>
-      </c>
-      <c r="AO7">
-        <v>95</v>
-      </c>
-      <c r="AP7">
-        <v>8</v>
-      </c>
-      <c r="AQ7">
-        <v>10.5</v>
-      </c>
-      <c r="AR7">
-        <v>24</v>
-      </c>
-      <c r="AS7">
-        <v>85</v>
-      </c>
-      <c r="AT7">
-        <v>6.6</v>
-      </c>
-      <c r="AU7">
-        <v>6.8</v>
-      </c>
-      <c r="AV7">
-        <v>16</v>
-      </c>
-      <c r="AW7">
-        <v>50</v>
-      </c>
-      <c r="AX7">
-        <v>11</v>
-      </c>
-      <c r="AY7">
-        <v>10.5</v>
-      </c>
-      <c r="AZ7">
-        <v>22</v>
-      </c>
-      <c r="BA7">
-        <v>75</v>
-      </c>
-      <c r="BB7">
-        <v>27</v>
-      </c>
-      <c r="BC7">
-        <v>28</v>
-      </c>
-      <c r="BD7">
-        <v>50</v>
-      </c>
-      <c r="BE7">
-        <v>36</v>
-      </c>
-      <c r="BF7">
-        <v>27</v>
-      </c>
-      <c r="BG7">
-        <v>15</v>
-      </c>
-      <c r="BH7">
-        <v>2.72</v>
-      </c>
-      <c r="BI7">
-        <v>2.5</v>
-      </c>
-      <c r="BJ7">
-        <v>11.5</v>
-      </c>
-      <c r="BK7">
-        <v>9.4</v>
-      </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
-        <v>34</v>
-      </c>
-      <c r="BN7">
-        <v>4.9</v>
-      </c>
-      <c r="BO7">
-        <v>4.3</v>
-      </c>
-      <c r="BP7">
-        <v>20</v>
-      </c>
-      <c r="BQ7">
-        <v>9</v>
-      </c>
-      <c r="BR7">
-        <v>1000</v>
-      </c>
-      <c r="BS7">
-        <v>11.5</v>
-      </c>
-      <c r="BT7">
-        <v>7</v>
-      </c>
-      <c r="BU7">
-        <v>5.9</v>
-      </c>
-      <c r="BV7">
-        <v>42</v>
-      </c>
-      <c r="BW7">
-        <v>11.5</v>
-      </c>
-      <c r="BX7">
-        <v>65</v>
-      </c>
-      <c r="BY7">
-        <v>13</v>
-      </c>
-      <c r="BZ7">
-        <v>1000</v>
-      </c>
-      <c r="CA7">
-        <v>12</v>
-      </c>
-      <c r="CB7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:80">
-      <c r="A8" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" t="s">
-        <v>86</v>
-      </c>
-      <c r="C8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D8" t="s">
         <v>98</v>
-      </c>
-      <c r="E8" t="s">
-        <v>106</v>
-      </c>
-      <c r="F8">
-        <v>2.26</v>
-      </c>
-      <c r="G8">
-        <v>2.32</v>
-      </c>
-      <c r="H8">
-        <v>3.85</v>
-      </c>
-      <c r="I8">
-        <v>4</v>
-      </c>
-      <c r="J8">
-        <v>3.2</v>
-      </c>
-      <c r="K8">
-        <v>3.25</v>
-      </c>
-      <c r="L8">
-        <v>1.53</v>
-      </c>
-      <c r="M8">
-        <v>1.11</v>
-      </c>
-      <c r="N8">
-        <v>3</v>
-      </c>
-      <c r="O8">
-        <v>1.48</v>
-      </c>
-      <c r="P8">
-        <v>1.68</v>
-      </c>
-      <c r="Q8">
-        <v>2.44</v>
-      </c>
-      <c r="R8">
-        <v>1.25</v>
-      </c>
-      <c r="S8">
-        <v>4.8</v>
-      </c>
-      <c r="T8">
-        <v>2.02</v>
-      </c>
-      <c r="U8">
-        <v>1.9</v>
-      </c>
-      <c r="V8">
-        <v>1.33</v>
-      </c>
-      <c r="W8">
-        <v>1.76</v>
-      </c>
-      <c r="X8">
-        <v>10</v>
-      </c>
-      <c r="Y8">
-        <v>11.5</v>
-      </c>
-      <c r="Z8">
-        <v>26</v>
-      </c>
-      <c r="AA8">
-        <v>100</v>
-      </c>
-      <c r="AB8">
-        <v>7.8</v>
-      </c>
-      <c r="AC8">
-        <v>7.4</v>
-      </c>
-      <c r="AD8">
-        <v>16.5</v>
-      </c>
-      <c r="AE8">
-        <v>60</v>
-      </c>
-      <c r="AF8">
-        <v>12.5</v>
-      </c>
-      <c r="AG8">
-        <v>11.5</v>
-      </c>
-      <c r="AH8">
-        <v>21</v>
-      </c>
-      <c r="AI8">
-        <v>75</v>
-      </c>
-      <c r="AJ8">
-        <v>30</v>
-      </c>
-      <c r="AK8">
-        <v>29</v>
-      </c>
-      <c r="AL8">
-        <v>55</v>
-      </c>
-      <c r="AM8">
-        <v>150</v>
-      </c>
-      <c r="AN8">
-        <v>27</v>
-      </c>
-      <c r="AO8">
-        <v>75</v>
-      </c>
-      <c r="AP8">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ8">
-        <v>10.5</v>
-      </c>
-      <c r="AR8">
-        <v>23</v>
-      </c>
-      <c r="AS8">
-        <v>70</v>
-      </c>
-      <c r="AT8">
-        <v>7.2</v>
-      </c>
-      <c r="AU8">
-        <v>6.8</v>
-      </c>
-      <c r="AV8">
-        <v>15</v>
-      </c>
-      <c r="AW8">
-        <v>50</v>
-      </c>
-      <c r="AX8">
-        <v>11.5</v>
-      </c>
-      <c r="AY8">
-        <v>10.5</v>
-      </c>
-      <c r="AZ8">
-        <v>19.5</v>
-      </c>
-      <c r="BA8">
-        <v>65</v>
-      </c>
-      <c r="BB8">
-        <v>26</v>
-      </c>
-      <c r="BC8">
-        <v>26</v>
-      </c>
-      <c r="BD8">
-        <v>40</v>
-      </c>
-      <c r="BE8">
-        <v>28</v>
-      </c>
-      <c r="BF8">
-        <v>23</v>
-      </c>
-      <c r="BG8">
-        <v>60</v>
-      </c>
-      <c r="BH8">
-        <v>2.86</v>
-      </c>
-      <c r="BI8">
-        <v>2.46</v>
-      </c>
-      <c r="BJ8">
-        <v>11</v>
-      </c>
-      <c r="BK8">
-        <v>7.8</v>
-      </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>16</v>
-      </c>
-      <c r="BN8">
-        <v>5</v>
-      </c>
-      <c r="BO8">
-        <v>3.9</v>
-      </c>
-      <c r="BP8">
-        <v>18.5</v>
-      </c>
-      <c r="BQ8">
-        <v>9</v>
-      </c>
-      <c r="BR8">
-        <v>38</v>
-      </c>
-      <c r="BS8">
-        <v>12</v>
-      </c>
-      <c r="BT8">
-        <v>6.8</v>
-      </c>
-      <c r="BU8">
-        <v>5.2</v>
-      </c>
-      <c r="BV8">
-        <v>36</v>
-      </c>
-      <c r="BW8">
-        <v>12</v>
-      </c>
-      <c r="BX8">
-        <v>55</v>
-      </c>
-      <c r="BY8">
-        <v>13.5</v>
-      </c>
-      <c r="BZ8">
-        <v>40</v>
-      </c>
-      <c r="CA8">
-        <v>12</v>
-      </c>
-      <c r="CB8" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="9" spans="1:80">
-      <c r="A9" t="s">
-        <v>85</v>
-      </c>
-      <c r="B9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D9" t="s">
-        <v>99</v>
-      </c>
-      <c r="E9" t="s">
-        <v>107</v>
-      </c>
-      <c r="F9">
-        <v>2.18</v>
-      </c>
-      <c r="G9">
-        <v>2.26</v>
-      </c>
-      <c r="H9">
-        <v>3.3</v>
-      </c>
-      <c r="I9">
-        <v>3.45</v>
-      </c>
-      <c r="J9">
-        <v>3.8</v>
-      </c>
-      <c r="K9">
-        <v>4.1</v>
-      </c>
-      <c r="L9">
-        <v>1.3</v>
-      </c>
-      <c r="M9">
-        <v>1.04</v>
-      </c>
-      <c r="N9">
-        <v>5.1</v>
-      </c>
-      <c r="O9">
-        <v>1.21</v>
-      </c>
-      <c r="P9">
-        <v>2.42</v>
-      </c>
-      <c r="Q9">
-        <v>1.64</v>
-      </c>
-      <c r="R9">
-        <v>1.56</v>
-      </c>
-      <c r="S9">
-        <v>2.6</v>
-      </c>
-      <c r="T9">
-        <v>1.56</v>
-      </c>
-      <c r="U9">
-        <v>2.46</v>
-      </c>
-      <c r="V9">
-        <v>1.41</v>
-      </c>
-      <c r="W9">
-        <v>1.79</v>
-      </c>
-      <c r="X9">
-        <v>26</v>
-      </c>
-      <c r="Y9">
-        <v>18</v>
-      </c>
-      <c r="Z9">
-        <v>27</v>
-      </c>
-      <c r="AA9">
-        <v>55</v>
-      </c>
-      <c r="AB9">
-        <v>14.5</v>
-      </c>
-      <c r="AC9">
-        <v>9.6</v>
-      </c>
-      <c r="AD9">
-        <v>14.5</v>
-      </c>
-      <c r="AE9">
-        <v>34</v>
-      </c>
-      <c r="AF9">
-        <v>17.5</v>
-      </c>
-      <c r="AG9">
-        <v>12</v>
-      </c>
-      <c r="AH9">
-        <v>16</v>
-      </c>
-      <c r="AI9">
-        <v>38</v>
-      </c>
-      <c r="AJ9">
-        <v>29</v>
-      </c>
-      <c r="AK9">
-        <v>22</v>
-      </c>
-      <c r="AL9">
-        <v>30</v>
-      </c>
-      <c r="AM9">
-        <v>70</v>
-      </c>
-      <c r="AN9">
-        <v>12</v>
-      </c>
-      <c r="AO9">
-        <v>23</v>
-      </c>
-      <c r="AP9">
-        <v>19</v>
-      </c>
-      <c r="AQ9">
-        <v>14.5</v>
-      </c>
-      <c r="AR9">
-        <v>21</v>
-      </c>
-      <c r="AS9">
-        <v>38</v>
-      </c>
-      <c r="AT9">
-        <v>12</v>
-      </c>
-      <c r="AU9">
-        <v>7.8</v>
-      </c>
-      <c r="AV9">
-        <v>12</v>
-      </c>
-      <c r="AW9">
-        <v>26</v>
-      </c>
-      <c r="AX9">
-        <v>14.5</v>
-      </c>
-      <c r="AY9">
-        <v>10</v>
-      </c>
-      <c r="AZ9">
-        <v>13</v>
-      </c>
-      <c r="BA9">
-        <v>27</v>
-      </c>
-      <c r="BB9">
-        <v>21</v>
-      </c>
-      <c r="BC9">
-        <v>18.5</v>
-      </c>
-      <c r="BD9">
-        <v>8</v>
-      </c>
-      <c r="BE9">
-        <v>36</v>
-      </c>
-      <c r="BF9">
-        <v>10</v>
-      </c>
-      <c r="BG9">
-        <v>17</v>
-      </c>
-      <c r="BH9">
-        <v>4.4</v>
-      </c>
-      <c r="BI9">
-        <v>3.5</v>
-      </c>
-      <c r="BJ9">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK9">
-        <v>6.6</v>
-      </c>
-      <c r="BL9">
-        <v>1000</v>
-      </c>
-      <c r="BM9">
-        <v>22</v>
-      </c>
-      <c r="BN9">
-        <v>5.6</v>
-      </c>
-      <c r="BO9">
-        <v>4.4</v>
-      </c>
-      <c r="BP9">
-        <v>15</v>
-      </c>
-      <c r="BQ9">
-        <v>11</v>
-      </c>
-      <c r="BR9">
-        <v>23</v>
-      </c>
-      <c r="BS9">
-        <v>17</v>
-      </c>
-      <c r="BT9">
-        <v>7.2</v>
-      </c>
-      <c r="BU9">
-        <v>5.5</v>
-      </c>
-      <c r="BV9">
-        <v>23</v>
-      </c>
-      <c r="BW9">
-        <v>17</v>
-      </c>
-      <c r="BX9">
-        <v>29</v>
-      </c>
-      <c r="BY9">
-        <v>21</v>
-      </c>
-      <c r="BZ9">
-        <v>16.5</v>
-      </c>
-      <c r="CA9">
-        <v>12.5</v>
-      </c>
-      <c r="CB9" t="s">
-        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-21.xlsx
@@ -310,7 +310,7 @@
     <t>Real Potosi</t>
   </si>
   <si>
-    <t>2026-07-21 17:42:25</t>
+    <t>2026-07-21 19:49:04</t>
   </si>
 </sst>
 </file>
@@ -904,226 +904,226 @@
         <v>93</v>
       </c>
       <c r="F2">
-        <v>2.38</v>
+        <v>3.45</v>
       </c>
       <c r="G2">
-        <v>2.44</v>
+        <v>3.65</v>
       </c>
       <c r="H2">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="I2">
+        <v>4.8</v>
+      </c>
+      <c r="J2">
+        <v>1.97</v>
+      </c>
+      <c r="K2">
+        <v>2.02</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>1.6</v>
+      </c>
+      <c r="N2">
+        <v>1.33</v>
+      </c>
+      <c r="O2">
         <v>3.75</v>
       </c>
-      <c r="J2">
-        <v>3.15</v>
-      </c>
-      <c r="K2">
-        <v>3.2</v>
-      </c>
-      <c r="L2">
-        <v>1.56</v>
-      </c>
-      <c r="M2">
-        <v>1.12</v>
-      </c>
-      <c r="N2">
-        <v>2.96</v>
-      </c>
-      <c r="O2">
-        <v>1.5</v>
-      </c>
       <c r="P2">
-        <v>1.64</v>
+        <v>1.07</v>
       </c>
       <c r="Q2">
-        <v>2.52</v>
+        <v>14</v>
       </c>
       <c r="R2">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="S2">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="T2">
-        <v>2.02</v>
+        <v>6</v>
       </c>
       <c r="U2">
-        <v>1.89</v>
+        <v>1.18</v>
       </c>
       <c r="V2">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="W2">
-        <v>1.69</v>
+        <v>1.38</v>
       </c>
       <c r="X2">
-        <v>9.6</v>
+        <v>2.72</v>
       </c>
       <c r="Y2">
-        <v>11</v>
+        <v>6.4</v>
       </c>
       <c r="Z2">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AA2">
+        <v>270</v>
+      </c>
+      <c r="AB2">
+        <v>5.1</v>
+      </c>
+      <c r="AC2">
+        <v>10.5</v>
+      </c>
+      <c r="AD2">
+        <v>60</v>
+      </c>
+      <c r="AE2">
+        <v>470</v>
+      </c>
+      <c r="AF2">
+        <v>21</v>
+      </c>
+      <c r="AG2">
+        <v>46</v>
+      </c>
+      <c r="AH2">
+        <v>220</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>140</v>
+      </c>
+      <c r="AK2">
+        <v>340</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>2.56</v>
+      </c>
+      <c r="AQ2">
+        <v>6.2</v>
+      </c>
+      <c r="AR2">
+        <v>28</v>
+      </c>
+      <c r="AS2">
+        <v>150</v>
+      </c>
+      <c r="AT2">
+        <v>4.9</v>
+      </c>
+      <c r="AU2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV2">
+        <v>40</v>
+      </c>
+      <c r="AW2">
+        <v>230</v>
+      </c>
+      <c r="AX2">
+        <v>18.5</v>
+      </c>
+      <c r="AY2">
+        <v>32</v>
+      </c>
+      <c r="AZ2">
+        <v>130</v>
+      </c>
+      <c r="BA2">
+        <v>380</v>
+      </c>
+      <c r="BB2">
+        <v>100</v>
+      </c>
+      <c r="BC2">
         <v>170</v>
       </c>
-      <c r="AB2">
-        <v>8</v>
-      </c>
-      <c r="AC2">
-        <v>7.2</v>
-      </c>
-      <c r="AD2">
-        <v>16</v>
-      </c>
-      <c r="AE2">
-        <v>55</v>
-      </c>
-      <c r="AF2">
-        <v>14</v>
-      </c>
-      <c r="AG2">
-        <v>12</v>
-      </c>
-      <c r="AH2">
+      <c r="BD2">
+        <v>16.5</v>
+      </c>
+      <c r="BE2">
         <v>21</v>
       </c>
-      <c r="AI2">
-        <v>160</v>
-      </c>
-      <c r="AJ2">
-        <v>34</v>
-      </c>
-      <c r="AK2">
-        <v>32</v>
-      </c>
-      <c r="AL2">
-        <v>55</v>
-      </c>
-      <c r="AM2">
-        <v>580</v>
-      </c>
-      <c r="AN2">
-        <v>32</v>
-      </c>
-      <c r="AO2">
-        <v>70</v>
-      </c>
-      <c r="AP2">
-        <v>8.6</v>
-      </c>
-      <c r="AQ2">
-        <v>10</v>
-      </c>
-      <c r="AR2">
-        <v>22</v>
-      </c>
-      <c r="AS2">
-        <v>46</v>
-      </c>
-      <c r="AT2">
-        <v>7.2</v>
-      </c>
-      <c r="AU2">
-        <v>6.6</v>
-      </c>
-      <c r="AV2">
-        <v>14.5</v>
-      </c>
-      <c r="AW2">
-        <v>42</v>
-      </c>
-      <c r="AX2">
-        <v>12</v>
-      </c>
-      <c r="AY2">
-        <v>10.5</v>
-      </c>
-      <c r="AZ2">
-        <v>18.5</v>
-      </c>
-      <c r="BA2">
-        <v>60</v>
-      </c>
-      <c r="BB2">
-        <v>27</v>
-      </c>
-      <c r="BC2">
-        <v>26</v>
-      </c>
-      <c r="BD2">
-        <v>46</v>
-      </c>
-      <c r="BE2">
-        <v>28</v>
-      </c>
       <c r="BF2">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="BG2">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="BH2">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>98</v>
@@ -1146,226 +1146,226 @@
         <v>94</v>
       </c>
       <c r="F3">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="G3">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="H3">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="I3">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="J3">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="K3">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="L3">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="M3">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="O3">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="P3">
-        <v>2.06</v>
+        <v>1.64</v>
       </c>
       <c r="Q3">
-        <v>1.93</v>
+        <v>2.5</v>
       </c>
       <c r="R3">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="S3">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="T3">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="U3">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="V3">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="W3">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X3">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="Y3">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Z3">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AA3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
+        <v>7.4</v>
+      </c>
+      <c r="AC3">
+        <v>8</v>
+      </c>
+      <c r="AD3">
+        <v>990</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG3">
+        <v>10.5</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>23</v>
+      </c>
+      <c r="AK3">
+        <v>480</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>22</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>10</v>
+      </c>
+      <c r="AQ3">
+        <v>14</v>
+      </c>
+      <c r="AR3">
+        <v>26</v>
+      </c>
+      <c r="AS3">
+        <v>75</v>
+      </c>
+      <c r="AT3">
+        <v>6.2</v>
+      </c>
+      <c r="AU3">
+        <v>7.2</v>
+      </c>
+      <c r="AV3">
+        <v>17.5</v>
+      </c>
+      <c r="AW3">
+        <v>65</v>
+      </c>
+      <c r="AX3">
+        <v>8.4</v>
+      </c>
+      <c r="AY3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ3">
+        <v>13</v>
+      </c>
+      <c r="BA3">
+        <v>70</v>
+      </c>
+      <c r="BB3">
+        <v>12.5</v>
+      </c>
+      <c r="BC3">
         <v>9.199999999999999</v>
       </c>
-      <c r="AC3">
-        <v>8.4</v>
-      </c>
-      <c r="AD3">
-        <v>17</v>
-      </c>
-      <c r="AE3">
-        <v>55</v>
-      </c>
-      <c r="AF3">
-        <v>11.5</v>
-      </c>
-      <c r="AG3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH3">
-        <v>17.5</v>
-      </c>
-      <c r="AI3">
-        <v>60</v>
-      </c>
-      <c r="AJ3">
-        <v>21</v>
-      </c>
-      <c r="AK3">
-        <v>18.5</v>
-      </c>
-      <c r="AL3">
-        <v>32</v>
-      </c>
-      <c r="AM3">
-        <v>85</v>
-      </c>
-      <c r="AN3">
+      <c r="BD3">
+        <v>40</v>
+      </c>
+      <c r="BE3">
+        <v>130</v>
+      </c>
+      <c r="BF3">
+        <v>16.5</v>
+      </c>
+      <c r="BG3">
+        <v>90</v>
+      </c>
+      <c r="BH3">
+        <v>2.24</v>
+      </c>
+      <c r="BI3">
+        <v>2.16</v>
+      </c>
+      <c r="BJ3">
+        <v>970</v>
+      </c>
+      <c r="BK3">
         <v>14</v>
-      </c>
-      <c r="AO3">
-        <v>60</v>
-      </c>
-      <c r="AP3">
-        <v>15</v>
-      </c>
-      <c r="AQ3">
-        <v>16.5</v>
-      </c>
-      <c r="AR3">
-        <v>34</v>
-      </c>
-      <c r="AS3">
-        <v>85</v>
-      </c>
-      <c r="AT3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU3">
-        <v>8</v>
-      </c>
-      <c r="AV3">
-        <v>16</v>
-      </c>
-      <c r="AW3">
-        <v>50</v>
-      </c>
-      <c r="AX3">
-        <v>11</v>
-      </c>
-      <c r="AY3">
-        <v>9.6</v>
-      </c>
-      <c r="AZ3">
-        <v>16.5</v>
-      </c>
-      <c r="BA3">
-        <v>50</v>
-      </c>
-      <c r="BB3">
-        <v>19.5</v>
-      </c>
-      <c r="BC3">
-        <v>17.5</v>
-      </c>
-      <c r="BD3">
-        <v>30</v>
-      </c>
-      <c r="BE3">
-        <v>75</v>
-      </c>
-      <c r="BF3">
-        <v>13</v>
-      </c>
-      <c r="BG3">
-        <v>48</v>
-      </c>
-      <c r="BH3">
-        <v>3.8</v>
-      </c>
-      <c r="BI3">
-        <v>3.15</v>
-      </c>
-      <c r="BJ3">
-        <v>1000</v>
-      </c>
-      <c r="BK3">
-        <v>3.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>90</v>
+        <v>5.2</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO3">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>3.7</v>
+        <v>11</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>910</v>
       </c>
       <c r="BS3">
-        <v>2.78</v>
+        <v>4.8</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU3">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>2.78</v>
+        <v>5.2</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BY3">
-        <v>2.78</v>
+        <v>5</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="CA3">
-        <v>2.78</v>
+        <v>5.1</v>
       </c>
       <c r="CB3" t="s">
         <v>98</v>
@@ -1388,226 +1388,226 @@
         <v>95</v>
       </c>
       <c r="F4">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="G4">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="H4">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="J4">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="K4">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="L4">
-        <v>1.58</v>
+        <v>2.04</v>
       </c>
       <c r="M4">
+        <v>1.18</v>
+      </c>
+      <c r="N4">
+        <v>2.2</v>
+      </c>
+      <c r="O4">
+        <v>1.8</v>
+      </c>
+      <c r="P4">
+        <v>1.35</v>
+      </c>
+      <c r="Q4">
+        <v>3.75</v>
+      </c>
+      <c r="R4">
         <v>1.12</v>
       </c>
-      <c r="N4">
-        <v>2.74</v>
-      </c>
-      <c r="O4">
-        <v>1.56</v>
-      </c>
-      <c r="P4">
-        <v>1.58</v>
-      </c>
-      <c r="Q4">
-        <v>2.68</v>
-      </c>
-      <c r="R4">
-        <v>1.2</v>
-      </c>
       <c r="S4">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="T4">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="U4">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="V4">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="W4">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="X4">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="Y4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z4">
+        <v>34</v>
+      </c>
+      <c r="AA4">
+        <v>180</v>
+      </c>
+      <c r="AB4">
+        <v>5.5</v>
+      </c>
+      <c r="AC4">
+        <v>7.6</v>
+      </c>
+      <c r="AD4">
+        <v>24</v>
+      </c>
+      <c r="AE4">
+        <v>110</v>
+      </c>
+      <c r="AF4">
         <v>11</v>
       </c>
-      <c r="Z4">
+      <c r="AG4">
+        <v>14</v>
+      </c>
+      <c r="AH4">
+        <v>40</v>
+      </c>
+      <c r="AI4">
+        <v>190</v>
+      </c>
+      <c r="AJ4">
+        <v>40</v>
+      </c>
+      <c r="AK4">
+        <v>50</v>
+      </c>
+      <c r="AL4">
+        <v>140</v>
+      </c>
+      <c r="AM4">
+        <v>510</v>
+      </c>
+      <c r="AN4">
+        <v>65</v>
+      </c>
+      <c r="AO4">
+        <v>260</v>
+      </c>
+      <c r="AP4">
+        <v>5.9</v>
+      </c>
+      <c r="AQ4">
+        <v>8.6</v>
+      </c>
+      <c r="AR4">
         <v>27</v>
       </c>
-      <c r="AA4">
-        <v>95</v>
-      </c>
-      <c r="AB4">
-        <v>7.2</v>
-      </c>
-      <c r="AC4">
-        <v>7.2</v>
-      </c>
-      <c r="AD4">
-        <v>17.5</v>
-      </c>
-      <c r="AE4">
-        <v>70</v>
-      </c>
-      <c r="AF4">
-        <v>12</v>
-      </c>
-      <c r="AG4">
-        <v>12</v>
-      </c>
-      <c r="AH4">
-        <v>25</v>
-      </c>
-      <c r="AI4">
-        <v>90</v>
-      </c>
-      <c r="AJ4">
-        <v>32</v>
-      </c>
-      <c r="AK4">
-        <v>32</v>
-      </c>
-      <c r="AL4">
-        <v>65</v>
-      </c>
-      <c r="AM4">
-        <v>190</v>
-      </c>
-      <c r="AN4">
-        <v>32</v>
-      </c>
-      <c r="AO4">
-        <v>110</v>
-      </c>
-      <c r="AP4">
-        <v>8</v>
-      </c>
-      <c r="AQ4">
-        <v>10</v>
-      </c>
-      <c r="AR4">
-        <v>24</v>
-      </c>
       <c r="AS4">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AT4">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="AU4">
         <v>6.8</v>
       </c>
       <c r="AV4">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AW4">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="AX4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY4">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ4">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="BA4">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="BB4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BC4">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BD4">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="BE4">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="BF4">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BG4">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="BH4">
-        <v>2.72</v>
+        <v>1.96</v>
       </c>
       <c r="BI4">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="BJ4">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="BK4">
-        <v>9.6</v>
+        <v>17.5</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BN4">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO4">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BP4">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="BQ4">
-        <v>8.4</v>
+        <v>25</v>
       </c>
       <c r="BR4">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="BS4">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="BT4">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BU4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BV4">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="BW4">
-        <v>10.5</v>
+        <v>55</v>
       </c>
       <c r="BX4">
-        <v>65</v>
+        <v>190</v>
       </c>
       <c r="BY4">
-        <v>11.5</v>
+        <v>110</v>
       </c>
       <c r="BZ4">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="CA4">
-        <v>10.5</v>
+        <v>100</v>
       </c>
       <c r="CB4" t="s">
         <v>98</v>
@@ -1630,226 +1630,226 @@
         <v>96</v>
       </c>
       <c r="F5">
+        <v>2.36</v>
+      </c>
+      <c r="G5">
+        <v>2.4</v>
+      </c>
+      <c r="H5">
+        <v>4.1</v>
+      </c>
+      <c r="I5">
+        <v>4.3</v>
+      </c>
+      <c r="J5">
+        <v>2.9</v>
+      </c>
+      <c r="K5">
+        <v>2.96</v>
+      </c>
+      <c r="L5">
+        <v>1.89</v>
+      </c>
+      <c r="M5">
+        <v>1.16</v>
+      </c>
+      <c r="N5">
+        <v>2.38</v>
+      </c>
+      <c r="O5">
+        <v>1.69</v>
+      </c>
+      <c r="P5">
+        <v>1.42</v>
+      </c>
+      <c r="Q5">
+        <v>3.3</v>
+      </c>
+      <c r="R5">
+        <v>1.14</v>
+      </c>
+      <c r="S5">
+        <v>7.6</v>
+      </c>
+      <c r="T5">
         <v>2.32</v>
       </c>
-      <c r="G5">
-        <v>2.34</v>
-      </c>
-      <c r="H5">
-        <v>3.75</v>
-      </c>
-      <c r="I5">
-        <v>3.8</v>
-      </c>
-      <c r="J5">
-        <v>3.25</v>
-      </c>
-      <c r="K5">
-        <v>3.35</v>
-      </c>
-      <c r="L5">
-        <v>1.53</v>
-      </c>
-      <c r="M5">
-        <v>1.11</v>
-      </c>
-      <c r="N5">
-        <v>3</v>
-      </c>
-      <c r="O5">
-        <v>1.48</v>
-      </c>
-      <c r="P5">
+      <c r="U5">
+        <v>1.65</v>
+      </c>
+      <c r="V5">
+        <v>1.33</v>
+      </c>
+      <c r="W5">
         <v>1.67</v>
       </c>
-      <c r="Q5">
-        <v>2.44</v>
-      </c>
-      <c r="R5">
-        <v>1.25</v>
-      </c>
-      <c r="S5">
-        <v>4.8</v>
-      </c>
-      <c r="T5">
-        <v>2.04</v>
-      </c>
-      <c r="U5">
-        <v>1.9</v>
-      </c>
-      <c r="V5">
-        <v>1.36</v>
-      </c>
-      <c r="W5">
-        <v>1.75</v>
-      </c>
       <c r="X5">
+        <v>6.8</v>
+      </c>
+      <c r="Y5">
         <v>9.800000000000001</v>
       </c>
-      <c r="Y5">
+      <c r="Z5">
+        <v>30</v>
+      </c>
+      <c r="AA5">
+        <v>130</v>
+      </c>
+      <c r="AB5">
+        <v>6.2</v>
+      </c>
+      <c r="AC5">
+        <v>6.6</v>
+      </c>
+      <c r="AD5">
+        <v>18</v>
+      </c>
+      <c r="AE5">
+        <v>100</v>
+      </c>
+      <c r="AF5">
+        <v>12.5</v>
+      </c>
+      <c r="AG5">
+        <v>12.5</v>
+      </c>
+      <c r="AH5">
+        <v>34</v>
+      </c>
+      <c r="AI5">
+        <v>160</v>
+      </c>
+      <c r="AJ5">
+        <v>46</v>
+      </c>
+      <c r="AK5">
+        <v>48</v>
+      </c>
+      <c r="AL5">
+        <v>100</v>
+      </c>
+      <c r="AM5">
+        <v>320</v>
+      </c>
+      <c r="AN5">
+        <v>55</v>
+      </c>
+      <c r="AO5">
+        <v>170</v>
+      </c>
+      <c r="AP5">
+        <v>6.2</v>
+      </c>
+      <c r="AQ5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR5">
+        <v>24</v>
+      </c>
+      <c r="AS5">
+        <v>85</v>
+      </c>
+      <c r="AT5">
+        <v>5.8</v>
+      </c>
+      <c r="AU5">
+        <v>6.4</v>
+      </c>
+      <c r="AV5">
+        <v>17.5</v>
+      </c>
+      <c r="AW5">
+        <v>70</v>
+      </c>
+      <c r="AX5">
+        <v>11</v>
+      </c>
+      <c r="AY5">
         <v>11.5</v>
       </c>
-      <c r="Z5">
+      <c r="AZ5">
+        <v>27</v>
+      </c>
+      <c r="BA5">
+        <v>110</v>
+      </c>
+      <c r="BB5">
+        <v>32</v>
+      </c>
+      <c r="BC5">
+        <v>36</v>
+      </c>
+      <c r="BD5">
+        <v>85</v>
+      </c>
+      <c r="BE5">
+        <v>240</v>
+      </c>
+      <c r="BF5">
+        <v>40</v>
+      </c>
+      <c r="BG5">
+        <v>100</v>
+      </c>
+      <c r="BH5">
+        <v>2.14</v>
+      </c>
+      <c r="BI5">
+        <v>2.08</v>
+      </c>
+      <c r="BJ5">
+        <v>15.5</v>
+      </c>
+      <c r="BK5">
+        <v>14</v>
+      </c>
+      <c r="BL5">
+        <v>960</v>
+      </c>
+      <c r="BM5">
+        <v>17.5</v>
+      </c>
+      <c r="BN5">
+        <v>5.1</v>
+      </c>
+      <c r="BO5">
+        <v>4.7</v>
+      </c>
+      <c r="BP5">
+        <v>36</v>
+      </c>
+      <c r="BQ5">
         <v>25</v>
       </c>
-      <c r="AA5">
-        <v>80</v>
-      </c>
-      <c r="AB5">
-        <v>7.8</v>
-      </c>
-      <c r="AC5">
-        <v>7.4</v>
-      </c>
-      <c r="AD5">
-        <v>16</v>
-      </c>
-      <c r="AE5">
-        <v>55</v>
-      </c>
-      <c r="AF5">
-        <v>13.5</v>
-      </c>
-      <c r="AG5">
-        <v>11</v>
-      </c>
-      <c r="AH5">
-        <v>21</v>
-      </c>
-      <c r="AI5">
+      <c r="BR5">
+        <v>85</v>
+      </c>
+      <c r="BS5">
+        <v>65</v>
+      </c>
+      <c r="BT5">
+        <v>7</v>
+      </c>
+      <c r="BU5">
+        <v>6.2</v>
+      </c>
+      <c r="BV5">
+        <v>60</v>
+      </c>
+      <c r="BW5">
+        <v>44</v>
+      </c>
+      <c r="BX5">
+        <v>140</v>
+      </c>
+      <c r="BY5">
+        <v>95</v>
+      </c>
+      <c r="BZ5">
+        <v>130</v>
+      </c>
+      <c r="CA5">
         <v>75</v>
-      </c>
-      <c r="AJ5">
-        <v>34</v>
-      </c>
-      <c r="AK5">
-        <v>29</v>
-      </c>
-      <c r="AL5">
-        <v>55</v>
-      </c>
-      <c r="AM5">
-        <v>200</v>
-      </c>
-      <c r="AN5">
-        <v>27</v>
-      </c>
-      <c r="AO5">
-        <v>75</v>
-      </c>
-      <c r="AP5">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ5">
-        <v>10.5</v>
-      </c>
-      <c r="AR5">
-        <v>22</v>
-      </c>
-      <c r="AS5">
-        <v>65</v>
-      </c>
-      <c r="AT5">
-        <v>7.2</v>
-      </c>
-      <c r="AU5">
-        <v>6.8</v>
-      </c>
-      <c r="AV5">
-        <v>14.5</v>
-      </c>
-      <c r="AW5">
-        <v>48</v>
-      </c>
-      <c r="AX5">
-        <v>12</v>
-      </c>
-      <c r="AY5">
-        <v>10.5</v>
-      </c>
-      <c r="AZ5">
-        <v>19.5</v>
-      </c>
-      <c r="BA5">
-        <v>65</v>
-      </c>
-      <c r="BB5">
-        <v>28</v>
-      </c>
-      <c r="BC5">
-        <v>27</v>
-      </c>
-      <c r="BD5">
-        <v>46</v>
-      </c>
-      <c r="BE5">
-        <v>110</v>
-      </c>
-      <c r="BF5">
-        <v>25</v>
-      </c>
-      <c r="BG5">
-        <v>60</v>
-      </c>
-      <c r="BH5">
-        <v>2.88</v>
-      </c>
-      <c r="BI5">
-        <v>2.7</v>
-      </c>
-      <c r="BJ5">
-        <v>10.5</v>
-      </c>
-      <c r="BK5">
-        <v>8.4</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>18.5</v>
-      </c>
-      <c r="BN5">
-        <v>5</v>
-      </c>
-      <c r="BO5">
-        <v>4.4</v>
-      </c>
-      <c r="BP5">
-        <v>19</v>
-      </c>
-      <c r="BQ5">
-        <v>13</v>
-      </c>
-      <c r="BR5">
-        <v>38</v>
-      </c>
-      <c r="BS5">
-        <v>13.5</v>
-      </c>
-      <c r="BT5">
-        <v>6.6</v>
-      </c>
-      <c r="BU5">
-        <v>6</v>
-      </c>
-      <c r="BV5">
-        <v>34</v>
-      </c>
-      <c r="BW5">
-        <v>13</v>
-      </c>
-      <c r="BX5">
-        <v>50</v>
-      </c>
-      <c r="BY5">
-        <v>14.5</v>
-      </c>
-      <c r="BZ5">
-        <v>40</v>
-      </c>
-      <c r="CA5">
-        <v>13.5</v>
       </c>
       <c r="CB5" t="s">
         <v>98</v>
@@ -1872,40 +1872,40 @@
         <v>97</v>
       </c>
       <c r="F6">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="G6">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="H6">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="I6">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="J6">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K6">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L6">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M6">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N6">
         <v>5.3</v>
       </c>
       <c r="O6">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P6">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q6">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="R6">
         <v>1.58</v>
@@ -1914,43 +1914,43 @@
         <v>2.58</v>
       </c>
       <c r="T6">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U6">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="V6">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W6">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="X6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y6">
+        <v>21</v>
+      </c>
+      <c r="Z6">
+        <v>25</v>
+      </c>
+      <c r="AA6">
+        <v>55</v>
+      </c>
+      <c r="AB6">
+        <v>16</v>
+      </c>
+      <c r="AC6">
+        <v>9.4</v>
+      </c>
+      <c r="AD6">
+        <v>14.5</v>
+      </c>
+      <c r="AE6">
+        <v>32</v>
+      </c>
+      <c r="AF6">
         <v>18.5</v>
-      </c>
-      <c r="Z6">
-        <v>27</v>
-      </c>
-      <c r="AA6">
-        <v>70</v>
-      </c>
-      <c r="AB6">
-        <v>14.5</v>
-      </c>
-      <c r="AC6">
-        <v>9.6</v>
-      </c>
-      <c r="AD6">
-        <v>15</v>
-      </c>
-      <c r="AE6">
-        <v>36</v>
-      </c>
-      <c r="AF6">
-        <v>17</v>
       </c>
       <c r="AG6">
         <v>12</v>
@@ -1959,10 +1959,10 @@
         <v>16</v>
       </c>
       <c r="AI6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ6">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AK6">
         <v>22</v>
@@ -1971,16 +1971,16 @@
         <v>30</v>
       </c>
       <c r="AM6">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AN6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO6">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AP6">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ6">
         <v>15</v>
@@ -1989,109 +1989,109 @@
         <v>21</v>
       </c>
       <c r="AS6">
-        <v>8.800000000000001</v>
+        <v>44</v>
       </c>
       <c r="AT6">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV6">
         <v>12</v>
       </c>
       <c r="AW6">
+        <v>26</v>
+      </c>
+      <c r="AX6">
+        <v>15.5</v>
+      </c>
+      <c r="AY6">
+        <v>10</v>
+      </c>
+      <c r="AZ6">
+        <v>13.5</v>
+      </c>
+      <c r="BA6">
+        <v>30</v>
+      </c>
+      <c r="BB6">
         <v>27</v>
       </c>
-      <c r="AX6">
-        <v>14</v>
-      </c>
-      <c r="AY6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ6">
-        <v>13</v>
-      </c>
-      <c r="BA6">
-        <v>27</v>
-      </c>
-      <c r="BB6">
-        <v>23</v>
-      </c>
       <c r="BC6">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD6">
-        <v>7.8</v>
+        <v>25</v>
       </c>
       <c r="BE6">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BF6">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BG6">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BH6">
         <v>4.4</v>
       </c>
       <c r="BI6">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="BJ6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK6">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL6">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BM6">
-        <v>1.04</v>
+        <v>50</v>
       </c>
       <c r="BN6">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BO6">
         <v>4.7</v>
       </c>
       <c r="BP6">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BQ6">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BS6">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BT6">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU6">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV6">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BX6">
         <v>29</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>15</v>
       </c>
       <c r="BZ6">
         <v>16.5</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="CB6" t="s">
         <v>98</v>
